--- a/packages/rc9_2_2_production/inputs/ready_to_edit/GDI_28HC_24_7_WEEKLY_INPUT.xlsx
+++ b/packages/rc9_2_2_production/inputs/ready_to_edit/GDI_28HC_24_7_WEEKLY_INPUT.xlsx
@@ -10,37 +10,37 @@
     <sheet name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Schedule" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="FT Wise 60 Min" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Shrinkage 60 Min" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Preference" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Fixed Request" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Previous week scheduled" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Language Setup" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Coverage Split" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Shift Library" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="RC9 Universal Setup" sheetId="12" state="hidden" r:id="rId12"/>
-    <sheet name="RC9.1 Release Notes" sheetId="13" state="hidden" r:id="rId13"/>
-    <sheet name="00 START HERE" sheetId="14" state="hidden" r:id="rId14"/>
-    <sheet name="FT Wise 15 Min" sheetId="15" state="hidden" r:id="rId15"/>
-    <sheet name="FT Wise 30 Min" sheetId="16" state="hidden" r:id="rId16"/>
-    <sheet name="Shrinkage 15 Min" sheetId="17" state="hidden" r:id="rId17"/>
-    <sheet name="Shrinkage 30 Min" sheetId="18" state="hidden" r:id="rId18"/>
+    <sheet name="FT Wise 30 Min" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Shrinkage 60 Min" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Shrinkage 30 Min" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Preference" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Fixed Request" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Previous week scheduled" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Language Setup" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Coverage Split" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Shift Library" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="RC9 Universal Setup" sheetId="14" state="hidden" r:id="rId14"/>
+    <sheet name="RC9.1 Release Notes" sheetId="15" state="hidden" r:id="rId15"/>
+    <sheet name="00 START HERE" sheetId="16" state="hidden" r:id="rId16"/>
+    <sheet name="FT Wise 15 Min" sheetId="17" state="hidden" r:id="rId17"/>
+    <sheet name="Shrinkage 15 Min" sheetId="18" state="hidden" r:id="rId18"/>
     <sheet name="Shift Catalog" sheetId="19" state="hidden" r:id="rId19"/>
     <sheet name="Validation Lists" sheetId="20" state="hidden" r:id="rId20"/>
     <sheet name="Engine Defaults" sheetId="21" state="hidden" r:id="rId21"/>
     <sheet name="Input Checks" sheetId="22" state="hidden" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Shrinkage 60 Min'!$A$1:$H$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Preference'!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Language Setup'!$A$1:$I$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Shift Library'!$A$1:$F$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'RC9 Universal Setup'!$A$1:$C$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'RC9.1 Release Notes'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'00 START HERE'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'FT Wise 15 Min'!$A$1:$H$98</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'FT Wise 30 Min'!$A$1:$H$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Shrinkage 15 Min'!$A$1:$H$98</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Shrinkage 30 Min'!$A$1:$H$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'FT Wise 30 Min'!$A$1:$H$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Shrinkage 60 Min'!$A$1:$H$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Shrinkage 30 Min'!$A$1:$H$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Preference'!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Language Setup'!$A$1:$I$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Shift Library'!$A$1:$F$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'RC9 Universal Setup'!$A$1:$C$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'RC9.1 Release Notes'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'00 START HERE'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'FT Wise 15 Min'!$A$1:$H$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Shrinkage 15 Min'!$A$1:$H$98</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Shift Catalog'!$A$1:$D$50</definedName>
   </definedNames>
   <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -376,6 +376,7 @@
     <xf numFmtId="164" fontId="0" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -393,7 +394,6 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1126,14 +1126,14 @@
     <row r="21" ht="32" customHeight="1" s="19">
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>•  Hidden tabs (engine tuning, lists, the demand tabs for other interval sizes, old notes) are kept, not deleted: right-click any tab &gt; Unhide.</t>
+          <t>•  Hidden tabs (engine tuning, lists, unused 15-minute tabs, old notes) are kept, not deleted: right-click any tab &gt; Unhide.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1" s="19">
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>•  Changing Interval Minutes? Unhide the matching FT Wise and Shrinkage tabs and pick them in Instructions.</t>
+          <t>•  30- and 60-minute demand and shrinkage tabs are both here. Switching? Set Interval Minutes and pick the matching tabs in Requirements Source and Shrinkage Source.</t>
         </is>
       </c>
     </row>
@@ -1177,6 +1177,1115 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="19" min="1" max="1"/>
+    <col width="28" customWidth="1" style="19" min="2" max="2"/>
+    <col width="15" customWidth="1" style="19" min="3" max="3"/>
+    <col width="24" customWidth="1" style="19" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" s="19">
+      <c r="A1" s="50" t="inlineStr">
+        <is>
+          <t>Previous Saturday Schedule — Cyclic Carry-in</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="49" t="inlineStr">
+        <is>
+          <t>Slot</t>
+        </is>
+      </c>
+      <c r="B2" s="49" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C2" s="49" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="D2" s="49" t="inlineStr">
+        <is>
+          <t>Previous Saturday Shift</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="54" t="inlineStr">
+        <is>
+          <t>Esraa Abdelhadi</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D3" s="54" t="inlineStr">
+        <is>
+          <t>10:00 - 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="54" t="inlineStr">
+        <is>
+          <t>Seif Eleman</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Bilingual</t>
+        </is>
+      </c>
+      <c r="D4" s="54" t="inlineStr">
+        <is>
+          <t>16:00 - 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="54" t="inlineStr">
+        <is>
+          <t>Mohamed Elsayed</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D5" s="54" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="54" t="inlineStr">
+        <is>
+          <t>Mennatullah Abdelhamid</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D6" s="54" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="54" t="inlineStr">
+        <is>
+          <t>Awni Ali</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+      <c r="D7" s="54" t="inlineStr">
+        <is>
+          <t>19:00 - 04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="54" t="inlineStr">
+        <is>
+          <t>Jana Rabeey</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Bilingual</t>
+        </is>
+      </c>
+      <c r="D8" s="54" t="inlineStr">
+        <is>
+          <t>16:00 - 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="54" t="inlineStr">
+        <is>
+          <t>Wagih Ibrahim</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D9" s="54" t="inlineStr">
+        <is>
+          <t>19:00 - 04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="54" t="inlineStr">
+        <is>
+          <t>Youssef Eltembari</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D10" s="54" t="inlineStr">
+        <is>
+          <t>14:00 - 23:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="54" t="inlineStr">
+        <is>
+          <t>Adam Ahmed</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D11" s="54" t="inlineStr">
+        <is>
+          <t>19:00 - 04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="54" t="inlineStr">
+        <is>
+          <t>Juliana Amgad</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+      <c r="D12" s="54" t="inlineStr">
+        <is>
+          <t>16:00 - 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="54" t="inlineStr">
+        <is>
+          <t>Mazen Moustafa</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D13" s="54" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="54" t="inlineStr">
+        <is>
+          <t>Mohamed Habib</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D14" s="54" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="54" t="inlineStr">
+        <is>
+          <t>Ahmed Ebied</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D15" s="54" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="54" t="inlineStr">
+        <is>
+          <t>Abdelrahman Mahmoud</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D16" s="54" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="54" t="inlineStr">
+        <is>
+          <t>Nourhan Abdelsalam</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D17" s="54" t="inlineStr">
+        <is>
+          <t>19:00 - 04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="54" t="inlineStr">
+        <is>
+          <t>Lujaine Mohamed</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Bilingual</t>
+        </is>
+      </c>
+      <c r="D18" s="54" t="inlineStr">
+        <is>
+          <t>19:00 - 04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="54" t="inlineStr">
+        <is>
+          <t>Aseya Hamdy</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Bilingual</t>
+        </is>
+      </c>
+      <c r="D19" s="54" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="54" t="inlineStr">
+        <is>
+          <t>Mennatullah Abdo</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D20" s="54" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="54" t="inlineStr">
+        <is>
+          <t>Mohamed Kamal</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Bilingual</t>
+        </is>
+      </c>
+      <c r="D21" s="54" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="54" t="inlineStr">
+        <is>
+          <t>Youssef Ali</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D22" s="54" t="inlineStr">
+        <is>
+          <t>19:00 - 04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="54" t="inlineStr">
+        <is>
+          <t>Farida Ahmed</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Bilingual</t>
+        </is>
+      </c>
+      <c r="D23" s="54" t="inlineStr">
+        <is>
+          <t>19:00 - 04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="54" t="inlineStr">
+        <is>
+          <t>Lojaine Khaled</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D24" s="54" t="inlineStr">
+        <is>
+          <t>16:00 - 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="54" t="inlineStr">
+        <is>
+          <t>Shahd Hesham</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D25" s="54" t="inlineStr">
+        <is>
+          <t>16:00 - 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="54" t="inlineStr">
+        <is>
+          <t>Sara Elshannat</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D26" s="54" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="54" t="inlineStr">
+        <is>
+          <t>Kenzie Farid</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D27" s="54" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="54" t="inlineStr">
+        <is>
+          <t>Hazem Yasser</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D28" s="54" t="inlineStr">
+        <is>
+          <t>18:00 - 03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="54" t="inlineStr">
+        <is>
+          <t>Habiba Mahmoud</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Bilingual</t>
+        </is>
+      </c>
+      <c r="D29" s="54" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="54" t="inlineStr">
+        <is>
+          <t>Rana Mohamed</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Bilingual</t>
+        </is>
+      </c>
+      <c r="D30" s="54" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="55" t="inlineStr">
+        <is>
+          <t>Salma Ahmed</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D31" s="55" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D3:D302">
+    <cfRule type="expression" priority="1" dxfId="5">
+      <formula>UPPER(TRIM(D3))="OFF"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="6">
+      <formula>UPPER(TRIM(D3))="LEAVE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation sqref="B3:B302" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Please check this value" error="This name is not on this week's roster. If the person has left, also list them in Instructions &gt; Known Departed Associates." prompt="Pick a name from this week's roster." type="list" errorStyle="warning">
+      <formula1>'Schedule'!$D$3:$D$302</formula1>
+    </dataValidation>
+    <dataValidation sqref="C3:C302" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Please check this value" error="This language is not on the Language Setup tab. Keep it only if that is intended." type="list" errorStyle="warning">
+      <formula1>'Language Setup'!$A$3:$A$42</formula1>
+    </dataValidation>
+    <dataValidation sqref="D3:D302" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Please check this value" error="Not in this week's Shift Library. Keep it only if it really was last Saturday's shift (HH:MM - HH:MM)." prompt="OFF, Leave or a shift from the Shift Library." type="list" errorStyle="warning">
+      <formula1>'Validation Lists'!$C$3:$C$69</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007F7F7F"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="19" min="1" max="1"/>
+    <col width="14" customWidth="1" style="19" min="2" max="3"/>
+    <col width="28" customWidth="1" style="19" min="4" max="4"/>
+    <col width="12" customWidth="1" style="19" min="5" max="5"/>
+    <col width="22" customWidth="1" style="19" min="6" max="6"/>
+    <col width="20" customWidth="1" style="19" min="7" max="7"/>
+    <col width="56" customWidth="1" style="19" min="8" max="8"/>
+    <col width="16" customWidth="1" style="19" min="9" max="9"/>
+    <col width="20" customWidth="1" style="19" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" s="19">
+      <c r="A1" s="50" t="inlineStr">
+        <is>
+          <t>Language / Skill Setup — Directional Coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" s="19">
+      <c r="A2" s="49" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="B2" s="49" t="inlineStr">
+        <is>
+          <t>Coverage Start</t>
+        </is>
+      </c>
+      <c r="C2" s="49" t="inlineStr">
+        <is>
+          <t>Coverage End</t>
+        </is>
+      </c>
+      <c r="D2" s="49" t="inlineStr">
+        <is>
+          <t>Can Cover Languages</t>
+        </is>
+      </c>
+      <c r="E2" s="49" t="inlineStr">
+        <is>
+          <t>Active?</t>
+        </is>
+      </c>
+      <c r="F2" s="49" t="inlineStr">
+        <is>
+          <t>Coverage Group</t>
+        </is>
+      </c>
+      <c r="G2" s="49" t="inlineStr">
+        <is>
+          <t>Minimum Per Interval</t>
+        </is>
+      </c>
+      <c r="H2" s="49" t="inlineStr">
+        <is>
+          <t>Priority / Notes</t>
+        </is>
+      </c>
+      <c r="I2" s="49" t="inlineStr">
+        <is>
+          <t>Cross-skilled?</t>
+        </is>
+      </c>
+      <c r="J2" s="49" t="inlineStr">
+        <is>
+          <t>Coverage Days</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B3" s="56" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="C3" s="56" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>UK, English</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Source language covers itself and English.</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Bilingual</t>
+        </is>
+      </c>
+      <c r="B4" s="56" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C4" s="56" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Bilingual, French, English</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Bilingual/French</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Source language covers itself plus French and English.</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+      <c r="B5" s="56" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C5" s="56" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Bilingual/French</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>French only.</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="B6" s="56" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C6" s="56" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>No minimum-per-interval language requirement.</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="57" t="n"/>
+      <c r="C7" s="57" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="57" t="n"/>
+      <c r="C8" s="57" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="57" t="n"/>
+      <c r="C9" s="57" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="57" t="n"/>
+      <c r="C10" s="57" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="57" t="n"/>
+      <c r="C11" s="57" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="57" t="n"/>
+      <c r="C12" s="57" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="57" t="n"/>
+      <c r="C13" s="57" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="57" t="n"/>
+      <c r="C14" s="57" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="57" t="n"/>
+      <c r="C15" s="57" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="57" t="n"/>
+      <c r="C16" s="57" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="57" t="n"/>
+      <c r="C17" s="57" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="57" t="n"/>
+      <c r="C18" s="57" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="57" t="n"/>
+      <c r="C19" s="57" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="57" t="n"/>
+      <c r="C20" s="57" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="57" t="n"/>
+      <c r="C21" s="57" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="57" t="n"/>
+      <c r="C22" s="57" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="57" t="n"/>
+      <c r="C23" s="57" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="57" t="n"/>
+      <c r="C24" s="57" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="57" t="n"/>
+      <c r="C25" s="57" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="57" t="n"/>
+      <c r="C26" s="57" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="57" t="n"/>
+      <c r="C27" s="57" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="57" t="n"/>
+      <c r="C28" s="57" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="57" t="n"/>
+      <c r="C29" s="57" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="57" t="n"/>
+      <c r="C30" s="57" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="57" t="n"/>
+      <c r="C31" s="57" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="57" t="n"/>
+      <c r="C32" s="57" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="57" t="n"/>
+      <c r="C33" s="57" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="57" t="n"/>
+      <c r="C34" s="57" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="57" t="n"/>
+      <c r="C35" s="57" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="57" t="n"/>
+      <c r="C36" s="57" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="57" t="n"/>
+      <c r="C37" s="57" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="57" t="n"/>
+      <c r="C38" s="57" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="57" t="n"/>
+      <c r="C39" s="57" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="57" t="n"/>
+      <c r="C40" s="57" t="n"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="57" t="n"/>
+      <c r="C41" s="57" t="n"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="57" t="n"/>
+      <c r="C42" s="57" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I6"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <dataValidations count="6">
+    <dataValidation sqref="J3 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid coverage days" error="Choose a listed day or range, or type a supported value such as Sun-Thu." type="list" errorStyle="stop">
+      <formula1>"All,Weekdays,Weekends,Sun-Thu,Mon-Fri,Sun,Mon,Tue,Wed,Thu,Fri,Sat"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B3:B42" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. A time such as 08:00. The window may cross midnight." prompt="A time such as 08:00. The window may cross midnight." type="time" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>0.999988426</formula2>
+    </dataValidation>
+    <dataValidation sqref="C3:C42" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. A time such as 08:00. The window may cross midnight." prompt="A time such as 08:00. The window may cross midnight." type="time" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>0.999988426</formula2>
+    </dataValidation>
+    <dataValidation sqref="E3:E42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." type="list" errorStyle="stop">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G3:G42" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. People of this language needed at all times in the window (whole number)." prompt="People of this language needed at all times in the window (whole number)." type="whole" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>500</formula2>
+    </dataValidation>
+    <dataValidation sqref="I3:I42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." type="list" errorStyle="stop">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
@@ -1208,253 +2317,253 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="57" t="inlineStr">
+      <c r="A4" s="58" t="inlineStr">
         <is>
           <t>Coverage Group</t>
         </is>
       </c>
-      <c r="B4" s="57" t="inlineStr">
+      <c r="B4" s="58" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="C4" s="57" t="inlineStr">
+      <c r="C4" s="58" t="inlineStr">
         <is>
           <t>End</t>
         </is>
       </c>
-      <c r="D4" s="57" t="inlineStr">
+      <c r="D4" s="58" t="inlineStr">
         <is>
           <t>Coverage Ratio</t>
         </is>
       </c>
-      <c r="E4" s="57" t="inlineStr">
+      <c r="E4" s="58" t="inlineStr">
         <is>
           <t>Exclusive?</t>
         </is>
       </c>
-      <c r="F4" s="57" t="inlineStr">
+      <c r="F4" s="58" t="inlineStr">
         <is>
           <t>Active?</t>
         </is>
       </c>
-      <c r="G4" s="57" t="inlineStr">
+      <c r="G4" s="58" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1" s="19">
-      <c r="A5" s="58" t="inlineStr">
+      <c r="A5" s="59" t="inlineStr">
         <is>
           <t>Name from Language Setup's Coverage Group column.</t>
         </is>
       </c>
-      <c r="B5" s="58" t="inlineStr">
+      <c r="B5" s="59" t="inlineStr">
         <is>
           <t>Window opens (e.g. 03:00).</t>
         </is>
       </c>
-      <c r="C5" s="58" t="inlineStr">
+      <c r="C5" s="59" t="inlineStr">
         <is>
           <t>Window closes; may cross midnight (e.g. 16:00).</t>
         </is>
       </c>
-      <c r="D5" s="58" t="inlineStr">
+      <c r="D5" s="59" t="inlineStr">
         <is>
           <t>Blank = the workbook's Minimum Per Interval. 1.0 = full requirement.</t>
         </is>
       </c>
-      <c r="E5" s="58" t="inlineStr">
+      <c r="E5" s="59" t="inlineStr">
         <is>
           <t>Yes = only this group may work these hours at all.</t>
         </is>
       </c>
-      <c r="F5" s="58" t="inlineStr">
+      <c r="F5" s="59" t="inlineStr">
         <is>
           <t>No or blank = row ignored.</t>
         </is>
       </c>
-      <c r="G5" s="58" t="inlineStr"/>
+      <c r="G5" s="59" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="54" t="n"/>
-      <c r="B6" s="59" t="n"/>
-      <c r="C6" s="59" t="n"/>
-      <c r="D6" s="60" t="n"/>
-      <c r="E6" s="54" t="n"/>
-      <c r="F6" s="54" t="n"/>
+      <c r="A6" s="55" t="n"/>
+      <c r="B6" s="60" t="n"/>
+      <c r="C6" s="60" t="n"/>
+      <c r="D6" s="61" t="n"/>
+      <c r="E6" s="55" t="n"/>
+      <c r="F6" s="55" t="n"/>
       <c r="G6" s="24" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="54" t="n"/>
-      <c r="B7" s="59" t="n"/>
-      <c r="C7" s="59" t="n"/>
-      <c r="D7" s="60" t="n"/>
-      <c r="E7" s="54" t="n"/>
-      <c r="F7" s="54" t="n"/>
+      <c r="A7" s="55" t="n"/>
+      <c r="B7" s="60" t="n"/>
+      <c r="C7" s="60" t="n"/>
+      <c r="D7" s="61" t="n"/>
+      <c r="E7" s="55" t="n"/>
+      <c r="F7" s="55" t="n"/>
       <c r="G7" s="24" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="54" t="n"/>
-      <c r="B8" s="59" t="n"/>
-      <c r="C8" s="59" t="n"/>
-      <c r="D8" s="60" t="n"/>
-      <c r="E8" s="54" t="n"/>
-      <c r="F8" s="54" t="n"/>
+      <c r="A8" s="55" t="n"/>
+      <c r="B8" s="60" t="n"/>
+      <c r="C8" s="60" t="n"/>
+      <c r="D8" s="61" t="n"/>
+      <c r="E8" s="55" t="n"/>
+      <c r="F8" s="55" t="n"/>
       <c r="G8" s="24" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="54" t="n"/>
-      <c r="B9" s="59" t="n"/>
-      <c r="C9" s="59" t="n"/>
-      <c r="D9" s="60" t="n"/>
-      <c r="E9" s="54" t="n"/>
-      <c r="F9" s="54" t="n"/>
+      <c r="A9" s="55" t="n"/>
+      <c r="B9" s="60" t="n"/>
+      <c r="C9" s="60" t="n"/>
+      <c r="D9" s="61" t="n"/>
+      <c r="E9" s="55" t="n"/>
+      <c r="F9" s="55" t="n"/>
       <c r="G9" s="24" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="54" t="n"/>
-      <c r="B10" s="59" t="n"/>
-      <c r="C10" s="59" t="n"/>
-      <c r="D10" s="60" t="n"/>
-      <c r="E10" s="54" t="n"/>
-      <c r="F10" s="54" t="n"/>
+      <c r="A10" s="55" t="n"/>
+      <c r="B10" s="60" t="n"/>
+      <c r="C10" s="60" t="n"/>
+      <c r="D10" s="61" t="n"/>
+      <c r="E10" s="55" t="n"/>
+      <c r="F10" s="55" t="n"/>
       <c r="G10" s="24" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="54" t="n"/>
-      <c r="B11" s="59" t="n"/>
-      <c r="C11" s="59" t="n"/>
-      <c r="D11" s="60" t="n"/>
-      <c r="E11" s="54" t="n"/>
-      <c r="F11" s="54" t="n"/>
+      <c r="A11" s="55" t="n"/>
+      <c r="B11" s="60" t="n"/>
+      <c r="C11" s="60" t="n"/>
+      <c r="D11" s="61" t="n"/>
+      <c r="E11" s="55" t="n"/>
+      <c r="F11" s="55" t="n"/>
       <c r="G11" s="24" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="54" t="n"/>
-      <c r="B12" s="59" t="n"/>
-      <c r="C12" s="59" t="n"/>
-      <c r="D12" s="60" t="n"/>
-      <c r="E12" s="54" t="n"/>
-      <c r="F12" s="54" t="n"/>
+      <c r="A12" s="55" t="n"/>
+      <c r="B12" s="60" t="n"/>
+      <c r="C12" s="60" t="n"/>
+      <c r="D12" s="61" t="n"/>
+      <c r="E12" s="55" t="n"/>
+      <c r="F12" s="55" t="n"/>
       <c r="G12" s="24" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="54" t="n"/>
-      <c r="B13" s="59" t="n"/>
-      <c r="C13" s="59" t="n"/>
-      <c r="D13" s="60" t="n"/>
-      <c r="E13" s="54" t="n"/>
-      <c r="F13" s="54" t="n"/>
+      <c r="A13" s="55" t="n"/>
+      <c r="B13" s="60" t="n"/>
+      <c r="C13" s="60" t="n"/>
+      <c r="D13" s="61" t="n"/>
+      <c r="E13" s="55" t="n"/>
+      <c r="F13" s="55" t="n"/>
       <c r="G13" s="24" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="54" t="n"/>
-      <c r="B14" s="59" t="n"/>
-      <c r="C14" s="59" t="n"/>
-      <c r="D14" s="60" t="n"/>
-      <c r="E14" s="54" t="n"/>
-      <c r="F14" s="54" t="n"/>
+      <c r="A14" s="55" t="n"/>
+      <c r="B14" s="60" t="n"/>
+      <c r="C14" s="60" t="n"/>
+      <c r="D14" s="61" t="n"/>
+      <c r="E14" s="55" t="n"/>
+      <c r="F14" s="55" t="n"/>
       <c r="G14" s="24" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="54" t="n"/>
-      <c r="B15" s="59" t="n"/>
-      <c r="C15" s="59" t="n"/>
-      <c r="D15" s="60" t="n"/>
-      <c r="E15" s="54" t="n"/>
-      <c r="F15" s="54" t="n"/>
+      <c r="A15" s="55" t="n"/>
+      <c r="B15" s="60" t="n"/>
+      <c r="C15" s="60" t="n"/>
+      <c r="D15" s="61" t="n"/>
+      <c r="E15" s="55" t="n"/>
+      <c r="F15" s="55" t="n"/>
       <c r="G15" s="24" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="54" t="n"/>
-      <c r="B16" s="59" t="n"/>
-      <c r="C16" s="59" t="n"/>
-      <c r="D16" s="60" t="n"/>
-      <c r="E16" s="54" t="n"/>
-      <c r="F16" s="54" t="n"/>
+      <c r="A16" s="55" t="n"/>
+      <c r="B16" s="60" t="n"/>
+      <c r="C16" s="60" t="n"/>
+      <c r="D16" s="61" t="n"/>
+      <c r="E16" s="55" t="n"/>
+      <c r="F16" s="55" t="n"/>
       <c r="G16" s="24" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="54" t="n"/>
-      <c r="B17" s="59" t="n"/>
-      <c r="C17" s="59" t="n"/>
-      <c r="D17" s="60" t="n"/>
-      <c r="E17" s="54" t="n"/>
-      <c r="F17" s="54" t="n"/>
+      <c r="A17" s="55" t="n"/>
+      <c r="B17" s="60" t="n"/>
+      <c r="C17" s="60" t="n"/>
+      <c r="D17" s="61" t="n"/>
+      <c r="E17" s="55" t="n"/>
+      <c r="F17" s="55" t="n"/>
       <c r="G17" s="24" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="54" t="n"/>
-      <c r="B18" s="59" t="n"/>
-      <c r="C18" s="59" t="n"/>
-      <c r="D18" s="60" t="n"/>
-      <c r="E18" s="54" t="n"/>
-      <c r="F18" s="54" t="n"/>
+      <c r="A18" s="55" t="n"/>
+      <c r="B18" s="60" t="n"/>
+      <c r="C18" s="60" t="n"/>
+      <c r="D18" s="61" t="n"/>
+      <c r="E18" s="55" t="n"/>
+      <c r="F18" s="55" t="n"/>
       <c r="G18" s="24" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="54" t="n"/>
-      <c r="B19" s="59" t="n"/>
-      <c r="C19" s="59" t="n"/>
-      <c r="D19" s="60" t="n"/>
-      <c r="E19" s="54" t="n"/>
-      <c r="F19" s="54" t="n"/>
+      <c r="A19" s="55" t="n"/>
+      <c r="B19" s="60" t="n"/>
+      <c r="C19" s="60" t="n"/>
+      <c r="D19" s="61" t="n"/>
+      <c r="E19" s="55" t="n"/>
+      <c r="F19" s="55" t="n"/>
       <c r="G19" s="24" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="54" t="n"/>
-      <c r="B20" s="59" t="n"/>
-      <c r="C20" s="59" t="n"/>
-      <c r="D20" s="60" t="n"/>
-      <c r="E20" s="54" t="n"/>
-      <c r="F20" s="54" t="n"/>
+      <c r="A20" s="55" t="n"/>
+      <c r="B20" s="60" t="n"/>
+      <c r="C20" s="60" t="n"/>
+      <c r="D20" s="61" t="n"/>
+      <c r="E20" s="55" t="n"/>
+      <c r="F20" s="55" t="n"/>
       <c r="G20" s="24" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="54" t="n"/>
-      <c r="B21" s="59" t="n"/>
-      <c r="C21" s="59" t="n"/>
-      <c r="D21" s="60" t="n"/>
-      <c r="E21" s="54" t="n"/>
-      <c r="F21" s="54" t="n"/>
+      <c r="A21" s="55" t="n"/>
+      <c r="B21" s="60" t="n"/>
+      <c r="C21" s="60" t="n"/>
+      <c r="D21" s="61" t="n"/>
+      <c r="E21" s="55" t="n"/>
+      <c r="F21" s="55" t="n"/>
       <c r="G21" s="24" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="54" t="n"/>
-      <c r="B22" s="59" t="n"/>
-      <c r="C22" s="59" t="n"/>
-      <c r="D22" s="60" t="n"/>
-      <c r="E22" s="54" t="n"/>
-      <c r="F22" s="54" t="n"/>
+      <c r="A22" s="55" t="n"/>
+      <c r="B22" s="60" t="n"/>
+      <c r="C22" s="60" t="n"/>
+      <c r="D22" s="61" t="n"/>
+      <c r="E22" s="55" t="n"/>
+      <c r="F22" s="55" t="n"/>
       <c r="G22" s="24" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="54" t="n"/>
-      <c r="B23" s="59" t="n"/>
-      <c r="C23" s="59" t="n"/>
-      <c r="D23" s="60" t="n"/>
-      <c r="E23" s="54" t="n"/>
-      <c r="F23" s="54" t="n"/>
+      <c r="A23" s="55" t="n"/>
+      <c r="B23" s="60" t="n"/>
+      <c r="C23" s="60" t="n"/>
+      <c r="D23" s="61" t="n"/>
+      <c r="E23" s="55" t="n"/>
+      <c r="F23" s="55" t="n"/>
       <c r="G23" s="24" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="54" t="n"/>
-      <c r="B24" s="59" t="n"/>
-      <c r="C24" s="59" t="n"/>
-      <c r="D24" s="60" t="n"/>
-      <c r="E24" s="54" t="n"/>
-      <c r="F24" s="54" t="n"/>
+      <c r="A24" s="55" t="n"/>
+      <c r="B24" s="60" t="n"/>
+      <c r="C24" s="60" t="n"/>
+      <c r="D24" s="61" t="n"/>
+      <c r="E24" s="55" t="n"/>
+      <c r="F24" s="55" t="n"/>
       <c r="G24" s="24" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="54" t="n"/>
-      <c r="B25" s="59" t="n"/>
-      <c r="C25" s="59" t="n"/>
-      <c r="D25" s="60" t="n"/>
-      <c r="E25" s="54" t="n"/>
-      <c r="F25" s="54" t="n"/>
+      <c r="A25" s="55" t="n"/>
+      <c r="B25" s="60" t="n"/>
+      <c r="C25" s="60" t="n"/>
+      <c r="D25" s="61" t="n"/>
+      <c r="E25" s="55" t="n"/>
+      <c r="F25" s="55" t="n"/>
       <c r="G25" s="24" t="n"/>
     </row>
   </sheetData>
@@ -1483,7 +2592,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007F7F7F"/>
@@ -2329,7 +3438,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BFBFBF"/>
@@ -2618,7 +3727,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BFBFBF"/>
@@ -2841,7 +3950,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BFBFBF"/>
@@ -2987,2180 +4096,6 @@
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00BFBFBF"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H98"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" style="19" min="1" max="1"/>
-    <col width="12" customWidth="1" style="19" min="2" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1" s="19">
-      <c r="A1" s="50" t="inlineStr">
-        <is>
-          <t>FT Wise 15 Min — Full-week requirement input</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="49" t="inlineStr">
-        <is>
-          <t>Interval</t>
-        </is>
-      </c>
-      <c r="B2" s="49" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="C2" s="49" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="D2" s="49" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="E2" s="49" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="F2" s="49" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="G2" s="49" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="H2" s="49" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="B3" s="61" t="n"/>
-      <c r="C3" s="61" t="n"/>
-      <c r="D3" s="61" t="n"/>
-      <c r="E3" s="61" t="n"/>
-      <c r="F3" s="61" t="n"/>
-      <c r="G3" s="61" t="n"/>
-      <c r="H3" s="61" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>00:15</t>
-        </is>
-      </c>
-      <c r="B4" s="61" t="n"/>
-      <c r="C4" s="61" t="n"/>
-      <c r="D4" s="61" t="n"/>
-      <c r="E4" s="61" t="n"/>
-      <c r="F4" s="61" t="n"/>
-      <c r="G4" s="61" t="n"/>
-      <c r="H4" s="61" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
-      <c r="B5" s="61" t="n"/>
-      <c r="C5" s="61" t="n"/>
-      <c r="D5" s="61" t="n"/>
-      <c r="E5" s="61" t="n"/>
-      <c r="F5" s="61" t="n"/>
-      <c r="G5" s="61" t="n"/>
-      <c r="H5" s="61" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>00:45</t>
-        </is>
-      </c>
-      <c r="B6" s="61" t="n"/>
-      <c r="C6" s="61" t="n"/>
-      <c r="D6" s="61" t="n"/>
-      <c r="E6" s="61" t="n"/>
-      <c r="F6" s="61" t="n"/>
-      <c r="G6" s="61" t="n"/>
-      <c r="H6" s="61" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>01:00</t>
-        </is>
-      </c>
-      <c r="B7" s="61" t="n"/>
-      <c r="C7" s="61" t="n"/>
-      <c r="D7" s="61" t="n"/>
-      <c r="E7" s="61" t="n"/>
-      <c r="F7" s="61" t="n"/>
-      <c r="G7" s="61" t="n"/>
-      <c r="H7" s="61" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>01:15</t>
-        </is>
-      </c>
-      <c r="B8" s="61" t="n"/>
-      <c r="C8" s="61" t="n"/>
-      <c r="D8" s="61" t="n"/>
-      <c r="E8" s="61" t="n"/>
-      <c r="F8" s="61" t="n"/>
-      <c r="G8" s="61" t="n"/>
-      <c r="H8" s="61" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>01:30</t>
-        </is>
-      </c>
-      <c r="B9" s="61" t="n"/>
-      <c r="C9" s="61" t="n"/>
-      <c r="D9" s="61" t="n"/>
-      <c r="E9" s="61" t="n"/>
-      <c r="F9" s="61" t="n"/>
-      <c r="G9" s="61" t="n"/>
-      <c r="H9" s="61" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>01:45</t>
-        </is>
-      </c>
-      <c r="B10" s="61" t="n"/>
-      <c r="C10" s="61" t="n"/>
-      <c r="D10" s="61" t="n"/>
-      <c r="E10" s="61" t="n"/>
-      <c r="F10" s="61" t="n"/>
-      <c r="G10" s="61" t="n"/>
-      <c r="H10" s="61" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>02:00</t>
-        </is>
-      </c>
-      <c r="B11" s="61" t="n"/>
-      <c r="C11" s="61" t="n"/>
-      <c r="D11" s="61" t="n"/>
-      <c r="E11" s="61" t="n"/>
-      <c r="F11" s="61" t="n"/>
-      <c r="G11" s="61" t="n"/>
-      <c r="H11" s="61" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>02:15</t>
-        </is>
-      </c>
-      <c r="B12" s="61" t="n"/>
-      <c r="C12" s="61" t="n"/>
-      <c r="D12" s="61" t="n"/>
-      <c r="E12" s="61" t="n"/>
-      <c r="F12" s="61" t="n"/>
-      <c r="G12" s="61" t="n"/>
-      <c r="H12" s="61" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>02:30</t>
-        </is>
-      </c>
-      <c r="B13" s="61" t="n"/>
-      <c r="C13" s="61" t="n"/>
-      <c r="D13" s="61" t="n"/>
-      <c r="E13" s="61" t="n"/>
-      <c r="F13" s="61" t="n"/>
-      <c r="G13" s="61" t="n"/>
-      <c r="H13" s="61" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>02:45</t>
-        </is>
-      </c>
-      <c r="B14" s="61" t="n"/>
-      <c r="C14" s="61" t="n"/>
-      <c r="D14" s="61" t="n"/>
-      <c r="E14" s="61" t="n"/>
-      <c r="F14" s="61" t="n"/>
-      <c r="G14" s="61" t="n"/>
-      <c r="H14" s="61" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>03:00</t>
-        </is>
-      </c>
-      <c r="B15" s="61" t="n"/>
-      <c r="C15" s="61" t="n"/>
-      <c r="D15" s="61" t="n"/>
-      <c r="E15" s="61" t="n"/>
-      <c r="F15" s="61" t="n"/>
-      <c r="G15" s="61" t="n"/>
-      <c r="H15" s="61" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>03:15</t>
-        </is>
-      </c>
-      <c r="B16" s="61" t="n"/>
-      <c r="C16" s="61" t="n"/>
-      <c r="D16" s="61" t="n"/>
-      <c r="E16" s="61" t="n"/>
-      <c r="F16" s="61" t="n"/>
-      <c r="G16" s="61" t="n"/>
-      <c r="H16" s="61" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>03:30</t>
-        </is>
-      </c>
-      <c r="B17" s="61" t="n"/>
-      <c r="C17" s="61" t="n"/>
-      <c r="D17" s="61" t="n"/>
-      <c r="E17" s="61" t="n"/>
-      <c r="F17" s="61" t="n"/>
-      <c r="G17" s="61" t="n"/>
-      <c r="H17" s="61" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>03:45</t>
-        </is>
-      </c>
-      <c r="B18" s="61" t="n"/>
-      <c r="C18" s="61" t="n"/>
-      <c r="D18" s="61" t="n"/>
-      <c r="E18" s="61" t="n"/>
-      <c r="F18" s="61" t="n"/>
-      <c r="G18" s="61" t="n"/>
-      <c r="H18" s="61" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="B19" s="61" t="n"/>
-      <c r="C19" s="61" t="n"/>
-      <c r="D19" s="61" t="n"/>
-      <c r="E19" s="61" t="n"/>
-      <c r="F19" s="61" t="n"/>
-      <c r="G19" s="61" t="n"/>
-      <c r="H19" s="61" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>04:15</t>
-        </is>
-      </c>
-      <c r="B20" s="61" t="n"/>
-      <c r="C20" s="61" t="n"/>
-      <c r="D20" s="61" t="n"/>
-      <c r="E20" s="61" t="n"/>
-      <c r="F20" s="61" t="n"/>
-      <c r="G20" s="61" t="n"/>
-      <c r="H20" s="61" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="B21" s="61" t="n"/>
-      <c r="C21" s="61" t="n"/>
-      <c r="D21" s="61" t="n"/>
-      <c r="E21" s="61" t="n"/>
-      <c r="F21" s="61" t="n"/>
-      <c r="G21" s="61" t="n"/>
-      <c r="H21" s="61" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>04:45</t>
-        </is>
-      </c>
-      <c r="B22" s="61" t="n"/>
-      <c r="C22" s="61" t="n"/>
-      <c r="D22" s="61" t="n"/>
-      <c r="E22" s="61" t="n"/>
-      <c r="F22" s="61" t="n"/>
-      <c r="G22" s="61" t="n"/>
-      <c r="H22" s="61" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="B23" s="61" t="n"/>
-      <c r="C23" s="61" t="n"/>
-      <c r="D23" s="61" t="n"/>
-      <c r="E23" s="61" t="n"/>
-      <c r="F23" s="61" t="n"/>
-      <c r="G23" s="61" t="n"/>
-      <c r="H23" s="61" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>05:15</t>
-        </is>
-      </c>
-      <c r="B24" s="61" t="n"/>
-      <c r="C24" s="61" t="n"/>
-      <c r="D24" s="61" t="n"/>
-      <c r="E24" s="61" t="n"/>
-      <c r="F24" s="61" t="n"/>
-      <c r="G24" s="61" t="n"/>
-      <c r="H24" s="61" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="B25" s="61" t="n"/>
-      <c r="C25" s="61" t="n"/>
-      <c r="D25" s="61" t="n"/>
-      <c r="E25" s="61" t="n"/>
-      <c r="F25" s="61" t="n"/>
-      <c r="G25" s="61" t="n"/>
-      <c r="H25" s="61" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>05:45</t>
-        </is>
-      </c>
-      <c r="B26" s="61" t="n"/>
-      <c r="C26" s="61" t="n"/>
-      <c r="D26" s="61" t="n"/>
-      <c r="E26" s="61" t="n"/>
-      <c r="F26" s="61" t="n"/>
-      <c r="G26" s="61" t="n"/>
-      <c r="H26" s="61" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="B27" s="61" t="n"/>
-      <c r="C27" s="61" t="n"/>
-      <c r="D27" s="61" t="n"/>
-      <c r="E27" s="61" t="n"/>
-      <c r="F27" s="61" t="n"/>
-      <c r="G27" s="61" t="n"/>
-      <c r="H27" s="61" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>06:15</t>
-        </is>
-      </c>
-      <c r="B28" s="61" t="n"/>
-      <c r="C28" s="61" t="n"/>
-      <c r="D28" s="61" t="n"/>
-      <c r="E28" s="61" t="n"/>
-      <c r="F28" s="61" t="n"/>
-      <c r="G28" s="61" t="n"/>
-      <c r="H28" s="61" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>06:30</t>
-        </is>
-      </c>
-      <c r="B29" s="61" t="n"/>
-      <c r="C29" s="61" t="n"/>
-      <c r="D29" s="61" t="n"/>
-      <c r="E29" s="61" t="n"/>
-      <c r="F29" s="61" t="n"/>
-      <c r="G29" s="61" t="n"/>
-      <c r="H29" s="61" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>06:45</t>
-        </is>
-      </c>
-      <c r="B30" s="61" t="n"/>
-      <c r="C30" s="61" t="n"/>
-      <c r="D30" s="61" t="n"/>
-      <c r="E30" s="61" t="n"/>
-      <c r="F30" s="61" t="n"/>
-      <c r="G30" s="61" t="n"/>
-      <c r="H30" s="61" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="B31" s="61" t="n"/>
-      <c r="C31" s="61" t="n"/>
-      <c r="D31" s="61" t="n"/>
-      <c r="E31" s="61" t="n"/>
-      <c r="F31" s="61" t="n"/>
-      <c r="G31" s="61" t="n"/>
-      <c r="H31" s="61" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="B32" s="61" t="n"/>
-      <c r="C32" s="61" t="n"/>
-      <c r="D32" s="61" t="n"/>
-      <c r="E32" s="61" t="n"/>
-      <c r="F32" s="61" t="n"/>
-      <c r="G32" s="61" t="n"/>
-      <c r="H32" s="61" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="B33" s="61" t="n"/>
-      <c r="C33" s="61" t="n"/>
-      <c r="D33" s="61" t="n"/>
-      <c r="E33" s="61" t="n"/>
-      <c r="F33" s="61" t="n"/>
-      <c r="G33" s="61" t="n"/>
-      <c r="H33" s="61" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="B34" s="61" t="n"/>
-      <c r="C34" s="61" t="n"/>
-      <c r="D34" s="61" t="n"/>
-      <c r="E34" s="61" t="n"/>
-      <c r="F34" s="61" t="n"/>
-      <c r="G34" s="61" t="n"/>
-      <c r="H34" s="61" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="B35" s="61" t="n"/>
-      <c r="C35" s="61" t="n"/>
-      <c r="D35" s="61" t="n"/>
-      <c r="E35" s="61" t="n"/>
-      <c r="F35" s="61" t="n"/>
-      <c r="G35" s="61" t="n"/>
-      <c r="H35" s="61" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="B36" s="61" t="n"/>
-      <c r="C36" s="61" t="n"/>
-      <c r="D36" s="61" t="n"/>
-      <c r="E36" s="61" t="n"/>
-      <c r="F36" s="61" t="n"/>
-      <c r="G36" s="61" t="n"/>
-      <c r="H36" s="61" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="B37" s="61" t="n"/>
-      <c r="C37" s="61" t="n"/>
-      <c r="D37" s="61" t="n"/>
-      <c r="E37" s="61" t="n"/>
-      <c r="F37" s="61" t="n"/>
-      <c r="G37" s="61" t="n"/>
-      <c r="H37" s="61" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="B38" s="61" t="n"/>
-      <c r="C38" s="61" t="n"/>
-      <c r="D38" s="61" t="n"/>
-      <c r="E38" s="61" t="n"/>
-      <c r="F38" s="61" t="n"/>
-      <c r="G38" s="61" t="n"/>
-      <c r="H38" s="61" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="B39" s="61" t="n"/>
-      <c r="C39" s="61" t="n"/>
-      <c r="D39" s="61" t="n"/>
-      <c r="E39" s="61" t="n"/>
-      <c r="F39" s="61" t="n"/>
-      <c r="G39" s="61" t="n"/>
-      <c r="H39" s="61" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="B40" s="61" t="n"/>
-      <c r="C40" s="61" t="n"/>
-      <c r="D40" s="61" t="n"/>
-      <c r="E40" s="61" t="n"/>
-      <c r="F40" s="61" t="n"/>
-      <c r="G40" s="61" t="n"/>
-      <c r="H40" s="61" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B41" s="61" t="n"/>
-      <c r="C41" s="61" t="n"/>
-      <c r="D41" s="61" t="n"/>
-      <c r="E41" s="61" t="n"/>
-      <c r="F41" s="61" t="n"/>
-      <c r="G41" s="61" t="n"/>
-      <c r="H41" s="61" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="B42" s="61" t="n"/>
-      <c r="C42" s="61" t="n"/>
-      <c r="D42" s="61" t="n"/>
-      <c r="E42" s="61" t="n"/>
-      <c r="F42" s="61" t="n"/>
-      <c r="G42" s="61" t="n"/>
-      <c r="H42" s="61" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B43" s="61" t="n"/>
-      <c r="C43" s="61" t="n"/>
-      <c r="D43" s="61" t="n"/>
-      <c r="E43" s="61" t="n"/>
-      <c r="F43" s="61" t="n"/>
-      <c r="G43" s="61" t="n"/>
-      <c r="H43" s="61" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B44" s="61" t="n"/>
-      <c r="C44" s="61" t="n"/>
-      <c r="D44" s="61" t="n"/>
-      <c r="E44" s="61" t="n"/>
-      <c r="F44" s="61" t="n"/>
-      <c r="G44" s="61" t="n"/>
-      <c r="H44" s="61" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="B45" s="61" t="n"/>
-      <c r="C45" s="61" t="n"/>
-      <c r="D45" s="61" t="n"/>
-      <c r="E45" s="61" t="n"/>
-      <c r="F45" s="61" t="n"/>
-      <c r="G45" s="61" t="n"/>
-      <c r="H45" s="61" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="B46" s="61" t="n"/>
-      <c r="C46" s="61" t="n"/>
-      <c r="D46" s="61" t="n"/>
-      <c r="E46" s="61" t="n"/>
-      <c r="F46" s="61" t="n"/>
-      <c r="G46" s="61" t="n"/>
-      <c r="H46" s="61" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B47" s="61" t="n"/>
-      <c r="C47" s="61" t="n"/>
-      <c r="D47" s="61" t="n"/>
-      <c r="E47" s="61" t="n"/>
-      <c r="F47" s="61" t="n"/>
-      <c r="G47" s="61" t="n"/>
-      <c r="H47" s="61" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="B48" s="61" t="n"/>
-      <c r="C48" s="61" t="n"/>
-      <c r="D48" s="61" t="n"/>
-      <c r="E48" s="61" t="n"/>
-      <c r="F48" s="61" t="n"/>
-      <c r="G48" s="61" t="n"/>
-      <c r="H48" s="61" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B49" s="61" t="n"/>
-      <c r="C49" s="61" t="n"/>
-      <c r="D49" s="61" t="n"/>
-      <c r="E49" s="61" t="n"/>
-      <c r="F49" s="61" t="n"/>
-      <c r="G49" s="61" t="n"/>
-      <c r="H49" s="61" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="B50" s="61" t="n"/>
-      <c r="C50" s="61" t="n"/>
-      <c r="D50" s="61" t="n"/>
-      <c r="E50" s="61" t="n"/>
-      <c r="F50" s="61" t="n"/>
-      <c r="G50" s="61" t="n"/>
-      <c r="H50" s="61" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B51" s="61" t="n"/>
-      <c r="C51" s="61" t="n"/>
-      <c r="D51" s="61" t="n"/>
-      <c r="E51" s="61" t="n"/>
-      <c r="F51" s="61" t="n"/>
-      <c r="G51" s="61" t="n"/>
-      <c r="H51" s="61" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="B52" s="61" t="n"/>
-      <c r="C52" s="61" t="n"/>
-      <c r="D52" s="61" t="n"/>
-      <c r="E52" s="61" t="n"/>
-      <c r="F52" s="61" t="n"/>
-      <c r="G52" s="61" t="n"/>
-      <c r="H52" s="61" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="B53" s="61" t="n"/>
-      <c r="C53" s="61" t="n"/>
-      <c r="D53" s="61" t="n"/>
-      <c r="E53" s="61" t="n"/>
-      <c r="F53" s="61" t="n"/>
-      <c r="G53" s="61" t="n"/>
-      <c r="H53" s="61" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="B54" s="61" t="n"/>
-      <c r="C54" s="61" t="n"/>
-      <c r="D54" s="61" t="n"/>
-      <c r="E54" s="61" t="n"/>
-      <c r="F54" s="61" t="n"/>
-      <c r="G54" s="61" t="n"/>
-      <c r="H54" s="61" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="B55" s="61" t="n"/>
-      <c r="C55" s="61" t="n"/>
-      <c r="D55" s="61" t="n"/>
-      <c r="E55" s="61" t="n"/>
-      <c r="F55" s="61" t="n"/>
-      <c r="G55" s="61" t="n"/>
-      <c r="H55" s="61" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="B56" s="61" t="n"/>
-      <c r="C56" s="61" t="n"/>
-      <c r="D56" s="61" t="n"/>
-      <c r="E56" s="61" t="n"/>
-      <c r="F56" s="61" t="n"/>
-      <c r="G56" s="61" t="n"/>
-      <c r="H56" s="61" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="B57" s="61" t="n"/>
-      <c r="C57" s="61" t="n"/>
-      <c r="D57" s="61" t="n"/>
-      <c r="E57" s="61" t="n"/>
-      <c r="F57" s="61" t="n"/>
-      <c r="G57" s="61" t="n"/>
-      <c r="H57" s="61" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="B58" s="61" t="n"/>
-      <c r="C58" s="61" t="n"/>
-      <c r="D58" s="61" t="n"/>
-      <c r="E58" s="61" t="n"/>
-      <c r="F58" s="61" t="n"/>
-      <c r="G58" s="61" t="n"/>
-      <c r="H58" s="61" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="B59" s="61" t="n"/>
-      <c r="C59" s="61" t="n"/>
-      <c r="D59" s="61" t="n"/>
-      <c r="E59" s="61" t="n"/>
-      <c r="F59" s="61" t="n"/>
-      <c r="G59" s="61" t="n"/>
-      <c r="H59" s="61" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="B60" s="61" t="n"/>
-      <c r="C60" s="61" t="n"/>
-      <c r="D60" s="61" t="n"/>
-      <c r="E60" s="61" t="n"/>
-      <c r="F60" s="61" t="n"/>
-      <c r="G60" s="61" t="n"/>
-      <c r="H60" s="61" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="B61" s="61" t="n"/>
-      <c r="C61" s="61" t="n"/>
-      <c r="D61" s="61" t="n"/>
-      <c r="E61" s="61" t="n"/>
-      <c r="F61" s="61" t="n"/>
-      <c r="G61" s="61" t="n"/>
-      <c r="H61" s="61" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="B62" s="61" t="n"/>
-      <c r="C62" s="61" t="n"/>
-      <c r="D62" s="61" t="n"/>
-      <c r="E62" s="61" t="n"/>
-      <c r="F62" s="61" t="n"/>
-      <c r="G62" s="61" t="n"/>
-      <c r="H62" s="61" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="B63" s="61" t="n"/>
-      <c r="C63" s="61" t="n"/>
-      <c r="D63" s="61" t="n"/>
-      <c r="E63" s="61" t="n"/>
-      <c r="F63" s="61" t="n"/>
-      <c r="G63" s="61" t="n"/>
-      <c r="H63" s="61" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="B64" s="61" t="n"/>
-      <c r="C64" s="61" t="n"/>
-      <c r="D64" s="61" t="n"/>
-      <c r="E64" s="61" t="n"/>
-      <c r="F64" s="61" t="n"/>
-      <c r="G64" s="61" t="n"/>
-      <c r="H64" s="61" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="B65" s="61" t="n"/>
-      <c r="C65" s="61" t="n"/>
-      <c r="D65" s="61" t="n"/>
-      <c r="E65" s="61" t="n"/>
-      <c r="F65" s="61" t="n"/>
-      <c r="G65" s="61" t="n"/>
-      <c r="H65" s="61" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="B66" s="61" t="n"/>
-      <c r="C66" s="61" t="n"/>
-      <c r="D66" s="61" t="n"/>
-      <c r="E66" s="61" t="n"/>
-      <c r="F66" s="61" t="n"/>
-      <c r="G66" s="61" t="n"/>
-      <c r="H66" s="61" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="B67" s="61" t="n"/>
-      <c r="C67" s="61" t="n"/>
-      <c r="D67" s="61" t="n"/>
-      <c r="E67" s="61" t="n"/>
-      <c r="F67" s="61" t="n"/>
-      <c r="G67" s="61" t="n"/>
-      <c r="H67" s="61" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="B68" s="61" t="n"/>
-      <c r="C68" s="61" t="n"/>
-      <c r="D68" s="61" t="n"/>
-      <c r="E68" s="61" t="n"/>
-      <c r="F68" s="61" t="n"/>
-      <c r="G68" s="61" t="n"/>
-      <c r="H68" s="61" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="B69" s="61" t="n"/>
-      <c r="C69" s="61" t="n"/>
-      <c r="D69" s="61" t="n"/>
-      <c r="E69" s="61" t="n"/>
-      <c r="F69" s="61" t="n"/>
-      <c r="G69" s="61" t="n"/>
-      <c r="H69" s="61" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="B70" s="61" t="n"/>
-      <c r="C70" s="61" t="n"/>
-      <c r="D70" s="61" t="n"/>
-      <c r="E70" s="61" t="n"/>
-      <c r="F70" s="61" t="n"/>
-      <c r="G70" s="61" t="n"/>
-      <c r="H70" s="61" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B71" s="61" t="n"/>
-      <c r="C71" s="61" t="n"/>
-      <c r="D71" s="61" t="n"/>
-      <c r="E71" s="61" t="n"/>
-      <c r="F71" s="61" t="n"/>
-      <c r="G71" s="61" t="n"/>
-      <c r="H71" s="61" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="B72" s="61" t="n"/>
-      <c r="C72" s="61" t="n"/>
-      <c r="D72" s="61" t="n"/>
-      <c r="E72" s="61" t="n"/>
-      <c r="F72" s="61" t="n"/>
-      <c r="G72" s="61" t="n"/>
-      <c r="H72" s="61" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B73" s="61" t="n"/>
-      <c r="C73" s="61" t="n"/>
-      <c r="D73" s="61" t="n"/>
-      <c r="E73" s="61" t="n"/>
-      <c r="F73" s="61" t="n"/>
-      <c r="G73" s="61" t="n"/>
-      <c r="H73" s="61" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B74" s="61" t="n"/>
-      <c r="C74" s="61" t="n"/>
-      <c r="D74" s="61" t="n"/>
-      <c r="E74" s="61" t="n"/>
-      <c r="F74" s="61" t="n"/>
-      <c r="G74" s="61" t="n"/>
-      <c r="H74" s="61" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B75" s="61" t="n"/>
-      <c r="C75" s="61" t="n"/>
-      <c r="D75" s="61" t="n"/>
-      <c r="E75" s="61" t="n"/>
-      <c r="F75" s="61" t="n"/>
-      <c r="G75" s="61" t="n"/>
-      <c r="H75" s="61" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B76" s="61" t="n"/>
-      <c r="C76" s="61" t="n"/>
-      <c r="D76" s="61" t="n"/>
-      <c r="E76" s="61" t="n"/>
-      <c r="F76" s="61" t="n"/>
-      <c r="G76" s="61" t="n"/>
-      <c r="H76" s="61" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B77" s="61" t="n"/>
-      <c r="C77" s="61" t="n"/>
-      <c r="D77" s="61" t="n"/>
-      <c r="E77" s="61" t="n"/>
-      <c r="F77" s="61" t="n"/>
-      <c r="G77" s="61" t="n"/>
-      <c r="H77" s="61" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B78" s="61" t="n"/>
-      <c r="C78" s="61" t="n"/>
-      <c r="D78" s="61" t="n"/>
-      <c r="E78" s="61" t="n"/>
-      <c r="F78" s="61" t="n"/>
-      <c r="G78" s="61" t="n"/>
-      <c r="H78" s="61" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B79" s="61" t="n"/>
-      <c r="C79" s="61" t="n"/>
-      <c r="D79" s="61" t="n"/>
-      <c r="E79" s="61" t="n"/>
-      <c r="F79" s="61" t="n"/>
-      <c r="G79" s="61" t="n"/>
-      <c r="H79" s="61" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B80" s="61" t="n"/>
-      <c r="C80" s="61" t="n"/>
-      <c r="D80" s="61" t="n"/>
-      <c r="E80" s="61" t="n"/>
-      <c r="F80" s="61" t="n"/>
-      <c r="G80" s="61" t="n"/>
-      <c r="H80" s="61" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B81" s="61" t="n"/>
-      <c r="C81" s="61" t="n"/>
-      <c r="D81" s="61" t="n"/>
-      <c r="E81" s="61" t="n"/>
-      <c r="F81" s="61" t="n"/>
-      <c r="G81" s="61" t="n"/>
-      <c r="H81" s="61" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="B82" s="61" t="n"/>
-      <c r="C82" s="61" t="n"/>
-      <c r="D82" s="61" t="n"/>
-      <c r="E82" s="61" t="n"/>
-      <c r="F82" s="61" t="n"/>
-      <c r="G82" s="61" t="n"/>
-      <c r="H82" s="61" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B83" s="61" t="n"/>
-      <c r="C83" s="61" t="n"/>
-      <c r="D83" s="61" t="n"/>
-      <c r="E83" s="61" t="n"/>
-      <c r="F83" s="61" t="n"/>
-      <c r="G83" s="61" t="n"/>
-      <c r="H83" s="61" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="B84" s="61" t="n"/>
-      <c r="C84" s="61" t="n"/>
-      <c r="D84" s="61" t="n"/>
-      <c r="E84" s="61" t="n"/>
-      <c r="F84" s="61" t="n"/>
-      <c r="G84" s="61" t="n"/>
-      <c r="H84" s="61" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="B85" s="61" t="n"/>
-      <c r="C85" s="61" t="n"/>
-      <c r="D85" s="61" t="n"/>
-      <c r="E85" s="61" t="n"/>
-      <c r="F85" s="61" t="n"/>
-      <c r="G85" s="61" t="n"/>
-      <c r="H85" s="61" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="B86" s="61" t="n"/>
-      <c r="C86" s="61" t="n"/>
-      <c r="D86" s="61" t="n"/>
-      <c r="E86" s="61" t="n"/>
-      <c r="F86" s="61" t="n"/>
-      <c r="G86" s="61" t="n"/>
-      <c r="H86" s="61" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="B87" s="61" t="n"/>
-      <c r="C87" s="61" t="n"/>
-      <c r="D87" s="61" t="n"/>
-      <c r="E87" s="61" t="n"/>
-      <c r="F87" s="61" t="n"/>
-      <c r="G87" s="61" t="n"/>
-      <c r="H87" s="61" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>21:15</t>
-        </is>
-      </c>
-      <c r="B88" s="61" t="n"/>
-      <c r="C88" s="61" t="n"/>
-      <c r="D88" s="61" t="n"/>
-      <c r="E88" s="61" t="n"/>
-      <c r="F88" s="61" t="n"/>
-      <c r="G88" s="61" t="n"/>
-      <c r="H88" s="61" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="B89" s="61" t="n"/>
-      <c r="C89" s="61" t="n"/>
-      <c r="D89" s="61" t="n"/>
-      <c r="E89" s="61" t="n"/>
-      <c r="F89" s="61" t="n"/>
-      <c r="G89" s="61" t="n"/>
-      <c r="H89" s="61" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="B90" s="61" t="n"/>
-      <c r="C90" s="61" t="n"/>
-      <c r="D90" s="61" t="n"/>
-      <c r="E90" s="61" t="n"/>
-      <c r="F90" s="61" t="n"/>
-      <c r="G90" s="61" t="n"/>
-      <c r="H90" s="61" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B91" s="61" t="n"/>
-      <c r="C91" s="61" t="n"/>
-      <c r="D91" s="61" t="n"/>
-      <c r="E91" s="61" t="n"/>
-      <c r="F91" s="61" t="n"/>
-      <c r="G91" s="61" t="n"/>
-      <c r="H91" s="61" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>22:15</t>
-        </is>
-      </c>
-      <c r="B92" s="61" t="n"/>
-      <c r="C92" s="61" t="n"/>
-      <c r="D92" s="61" t="n"/>
-      <c r="E92" s="61" t="n"/>
-      <c r="F92" s="61" t="n"/>
-      <c r="G92" s="61" t="n"/>
-      <c r="H92" s="61" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="B93" s="61" t="n"/>
-      <c r="C93" s="61" t="n"/>
-      <c r="D93" s="61" t="n"/>
-      <c r="E93" s="61" t="n"/>
-      <c r="F93" s="61" t="n"/>
-      <c r="G93" s="61" t="n"/>
-      <c r="H93" s="61" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>22:45</t>
-        </is>
-      </c>
-      <c r="B94" s="61" t="n"/>
-      <c r="C94" s="61" t="n"/>
-      <c r="D94" s="61" t="n"/>
-      <c r="E94" s="61" t="n"/>
-      <c r="F94" s="61" t="n"/>
-      <c r="G94" s="61" t="n"/>
-      <c r="H94" s="61" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="B95" s="61" t="n"/>
-      <c r="C95" s="61" t="n"/>
-      <c r="D95" s="61" t="n"/>
-      <c r="E95" s="61" t="n"/>
-      <c r="F95" s="61" t="n"/>
-      <c r="G95" s="61" t="n"/>
-      <c r="H95" s="61" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
-      <c r="B96" s="61" t="n"/>
-      <c r="C96" s="61" t="n"/>
-      <c r="D96" s="61" t="n"/>
-      <c r="E96" s="61" t="n"/>
-      <c r="F96" s="61" t="n"/>
-      <c r="G96" s="61" t="n"/>
-      <c r="H96" s="61" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="B97" s="61" t="n"/>
-      <c r="C97" s="61" t="n"/>
-      <c r="D97" s="61" t="n"/>
-      <c r="E97" s="61" t="n"/>
-      <c r="F97" s="61" t="n"/>
-      <c r="G97" s="61" t="n"/>
-      <c r="H97" s="61" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>23:45</t>
-        </is>
-      </c>
-      <c r="B98" s="61" t="n"/>
-      <c r="C98" s="61" t="n"/>
-      <c r="D98" s="61" t="n"/>
-      <c r="E98" s="61" t="n"/>
-      <c r="F98" s="61" t="n"/>
-      <c r="G98" s="61" t="n"/>
-      <c r="H98" s="61" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:H98"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="B3:H98" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Required FTE for this interval. 0 or more; blank = no demand." prompt="Required FTE for this interval. 0 or more; blank = no demand." type="decimal" errorStyle="stop" operator="between">
-      <formula1>0</formula1>
-      <formula2>100000</formula2>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00BFBFBF"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H50"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" style="19" min="1" max="1"/>
-    <col width="12" customWidth="1" style="19" min="2" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1" s="19">
-      <c r="A1" s="50" t="inlineStr">
-        <is>
-          <t>FT Wise 30 Min — Full-week requirement input</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="49" t="inlineStr">
-        <is>
-          <t>Interval</t>
-        </is>
-      </c>
-      <c r="B2" s="49" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="C2" s="49" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="D2" s="49" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="E2" s="49" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="F2" s="49" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="G2" s="49" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="H2" s="49" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="B3" s="61" t="n"/>
-      <c r="C3" s="61" t="n"/>
-      <c r="D3" s="61" t="n"/>
-      <c r="E3" s="61" t="n"/>
-      <c r="F3" s="61" t="n"/>
-      <c r="G3" s="61" t="n"/>
-      <c r="H3" s="61" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
-      <c r="B4" s="61" t="n"/>
-      <c r="C4" s="61" t="n"/>
-      <c r="D4" s="61" t="n"/>
-      <c r="E4" s="61" t="n"/>
-      <c r="F4" s="61" t="n"/>
-      <c r="G4" s="61" t="n"/>
-      <c r="H4" s="61" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>01:00</t>
-        </is>
-      </c>
-      <c r="B5" s="61" t="n"/>
-      <c r="C5" s="61" t="n"/>
-      <c r="D5" s="61" t="n"/>
-      <c r="E5" s="61" t="n"/>
-      <c r="F5" s="61" t="n"/>
-      <c r="G5" s="61" t="n"/>
-      <c r="H5" s="61" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>01:30</t>
-        </is>
-      </c>
-      <c r="B6" s="61" t="n"/>
-      <c r="C6" s="61" t="n"/>
-      <c r="D6" s="61" t="n"/>
-      <c r="E6" s="61" t="n"/>
-      <c r="F6" s="61" t="n"/>
-      <c r="G6" s="61" t="n"/>
-      <c r="H6" s="61" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>02:00</t>
-        </is>
-      </c>
-      <c r="B7" s="61" t="n"/>
-      <c r="C7" s="61" t="n"/>
-      <c r="D7" s="61" t="n"/>
-      <c r="E7" s="61" t="n"/>
-      <c r="F7" s="61" t="n"/>
-      <c r="G7" s="61" t="n"/>
-      <c r="H7" s="61" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>02:30</t>
-        </is>
-      </c>
-      <c r="B8" s="61" t="n"/>
-      <c r="C8" s="61" t="n"/>
-      <c r="D8" s="61" t="n"/>
-      <c r="E8" s="61" t="n"/>
-      <c r="F8" s="61" t="n"/>
-      <c r="G8" s="61" t="n"/>
-      <c r="H8" s="61" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>03:00</t>
-        </is>
-      </c>
-      <c r="B9" s="61" t="n"/>
-      <c r="C9" s="61" t="n"/>
-      <c r="D9" s="61" t="n"/>
-      <c r="E9" s="61" t="n"/>
-      <c r="F9" s="61" t="n"/>
-      <c r="G9" s="61" t="n"/>
-      <c r="H9" s="61" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>03:30</t>
-        </is>
-      </c>
-      <c r="B10" s="61" t="n"/>
-      <c r="C10" s="61" t="n"/>
-      <c r="D10" s="61" t="n"/>
-      <c r="E10" s="61" t="n"/>
-      <c r="F10" s="61" t="n"/>
-      <c r="G10" s="61" t="n"/>
-      <c r="H10" s="61" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="B11" s="61" t="n"/>
-      <c r="C11" s="61" t="n"/>
-      <c r="D11" s="61" t="n"/>
-      <c r="E11" s="61" t="n"/>
-      <c r="F11" s="61" t="n"/>
-      <c r="G11" s="61" t="n"/>
-      <c r="H11" s="61" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="B12" s="61" t="n"/>
-      <c r="C12" s="61" t="n"/>
-      <c r="D12" s="61" t="n"/>
-      <c r="E12" s="61" t="n"/>
-      <c r="F12" s="61" t="n"/>
-      <c r="G12" s="61" t="n"/>
-      <c r="H12" s="61" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="B13" s="61" t="n"/>
-      <c r="C13" s="61" t="n"/>
-      <c r="D13" s="61" t="n"/>
-      <c r="E13" s="61" t="n"/>
-      <c r="F13" s="61" t="n"/>
-      <c r="G13" s="61" t="n"/>
-      <c r="H13" s="61" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="B14" s="61" t="n"/>
-      <c r="C14" s="61" t="n"/>
-      <c r="D14" s="61" t="n"/>
-      <c r="E14" s="61" t="n"/>
-      <c r="F14" s="61" t="n"/>
-      <c r="G14" s="61" t="n"/>
-      <c r="H14" s="61" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="B15" s="61" t="n"/>
-      <c r="C15" s="61" t="n"/>
-      <c r="D15" s="61" t="n"/>
-      <c r="E15" s="61" t="n"/>
-      <c r="F15" s="61" t="n"/>
-      <c r="G15" s="61" t="n"/>
-      <c r="H15" s="61" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>06:30</t>
-        </is>
-      </c>
-      <c r="B16" s="61" t="n"/>
-      <c r="C16" s="61" t="n"/>
-      <c r="D16" s="61" t="n"/>
-      <c r="E16" s="61" t="n"/>
-      <c r="F16" s="61" t="n"/>
-      <c r="G16" s="61" t="n"/>
-      <c r="H16" s="61" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="B17" s="61" t="n"/>
-      <c r="C17" s="61" t="n"/>
-      <c r="D17" s="61" t="n"/>
-      <c r="E17" s="61" t="n"/>
-      <c r="F17" s="61" t="n"/>
-      <c r="G17" s="61" t="n"/>
-      <c r="H17" s="61" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="B18" s="61" t="n"/>
-      <c r="C18" s="61" t="n"/>
-      <c r="D18" s="61" t="n"/>
-      <c r="E18" s="61" t="n"/>
-      <c r="F18" s="61" t="n"/>
-      <c r="G18" s="61" t="n"/>
-      <c r="H18" s="61" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="B19" s="61" t="n"/>
-      <c r="C19" s="61" t="n"/>
-      <c r="D19" s="61" t="n"/>
-      <c r="E19" s="61" t="n"/>
-      <c r="F19" s="61" t="n"/>
-      <c r="G19" s="61" t="n"/>
-      <c r="H19" s="61" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="B20" s="61" t="n"/>
-      <c r="C20" s="61" t="n"/>
-      <c r="D20" s="61" t="n"/>
-      <c r="E20" s="61" t="n"/>
-      <c r="F20" s="61" t="n"/>
-      <c r="G20" s="61" t="n"/>
-      <c r="H20" s="61" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="B21" s="61" t="n"/>
-      <c r="C21" s="61" t="n"/>
-      <c r="D21" s="61" t="n"/>
-      <c r="E21" s="61" t="n"/>
-      <c r="F21" s="61" t="n"/>
-      <c r="G21" s="61" t="n"/>
-      <c r="H21" s="61" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B22" s="61" t="n"/>
-      <c r="C22" s="61" t="n"/>
-      <c r="D22" s="61" t="n"/>
-      <c r="E22" s="61" t="n"/>
-      <c r="F22" s="61" t="n"/>
-      <c r="G22" s="61" t="n"/>
-      <c r="H22" s="61" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B23" s="61" t="n"/>
-      <c r="C23" s="61" t="n"/>
-      <c r="D23" s="61" t="n"/>
-      <c r="E23" s="61" t="n"/>
-      <c r="F23" s="61" t="n"/>
-      <c r="G23" s="61" t="n"/>
-      <c r="H23" s="61" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="B24" s="61" t="n"/>
-      <c r="C24" s="61" t="n"/>
-      <c r="D24" s="61" t="n"/>
-      <c r="E24" s="61" t="n"/>
-      <c r="F24" s="61" t="n"/>
-      <c r="G24" s="61" t="n"/>
-      <c r="H24" s="61" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B25" s="61" t="n"/>
-      <c r="C25" s="61" t="n"/>
-      <c r="D25" s="61" t="n"/>
-      <c r="E25" s="61" t="n"/>
-      <c r="F25" s="61" t="n"/>
-      <c r="G25" s="61" t="n"/>
-      <c r="H25" s="61" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B26" s="61" t="n"/>
-      <c r="C26" s="61" t="n"/>
-      <c r="D26" s="61" t="n"/>
-      <c r="E26" s="61" t="n"/>
-      <c r="F26" s="61" t="n"/>
-      <c r="G26" s="61" t="n"/>
-      <c r="H26" s="61" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B27" s="61" t="n"/>
-      <c r="C27" s="61" t="n"/>
-      <c r="D27" s="61" t="n"/>
-      <c r="E27" s="61" t="n"/>
-      <c r="F27" s="61" t="n"/>
-      <c r="G27" s="61" t="n"/>
-      <c r="H27" s="61" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="B28" s="61" t="n"/>
-      <c r="C28" s="61" t="n"/>
-      <c r="D28" s="61" t="n"/>
-      <c r="E28" s="61" t="n"/>
-      <c r="F28" s="61" t="n"/>
-      <c r="G28" s="61" t="n"/>
-      <c r="H28" s="61" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="B29" s="61" t="n"/>
-      <c r="C29" s="61" t="n"/>
-      <c r="D29" s="61" t="n"/>
-      <c r="E29" s="61" t="n"/>
-      <c r="F29" s="61" t="n"/>
-      <c r="G29" s="61" t="n"/>
-      <c r="H29" s="61" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="B30" s="61" t="n"/>
-      <c r="C30" s="61" t="n"/>
-      <c r="D30" s="61" t="n"/>
-      <c r="E30" s="61" t="n"/>
-      <c r="F30" s="61" t="n"/>
-      <c r="G30" s="61" t="n"/>
-      <c r="H30" s="61" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="B31" s="61" t="n"/>
-      <c r="C31" s="61" t="n"/>
-      <c r="D31" s="61" t="n"/>
-      <c r="E31" s="61" t="n"/>
-      <c r="F31" s="61" t="n"/>
-      <c r="G31" s="61" t="n"/>
-      <c r="H31" s="61" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="B32" s="61" t="n"/>
-      <c r="C32" s="61" t="n"/>
-      <c r="D32" s="61" t="n"/>
-      <c r="E32" s="61" t="n"/>
-      <c r="F32" s="61" t="n"/>
-      <c r="G32" s="61" t="n"/>
-      <c r="H32" s="61" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="B33" s="61" t="n"/>
-      <c r="C33" s="61" t="n"/>
-      <c r="D33" s="61" t="n"/>
-      <c r="E33" s="61" t="n"/>
-      <c r="F33" s="61" t="n"/>
-      <c r="G33" s="61" t="n"/>
-      <c r="H33" s="61" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="B34" s="61" t="n"/>
-      <c r="C34" s="61" t="n"/>
-      <c r="D34" s="61" t="n"/>
-      <c r="E34" s="61" t="n"/>
-      <c r="F34" s="61" t="n"/>
-      <c r="G34" s="61" t="n"/>
-      <c r="H34" s="61" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="B35" s="61" t="n"/>
-      <c r="C35" s="61" t="n"/>
-      <c r="D35" s="61" t="n"/>
-      <c r="E35" s="61" t="n"/>
-      <c r="F35" s="61" t="n"/>
-      <c r="G35" s="61" t="n"/>
-      <c r="H35" s="61" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="B36" s="61" t="n"/>
-      <c r="C36" s="61" t="n"/>
-      <c r="D36" s="61" t="n"/>
-      <c r="E36" s="61" t="n"/>
-      <c r="F36" s="61" t="n"/>
-      <c r="G36" s="61" t="n"/>
-      <c r="H36" s="61" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B37" s="61" t="n"/>
-      <c r="C37" s="61" t="n"/>
-      <c r="D37" s="61" t="n"/>
-      <c r="E37" s="61" t="n"/>
-      <c r="F37" s="61" t="n"/>
-      <c r="G37" s="61" t="n"/>
-      <c r="H37" s="61" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B38" s="61" t="n"/>
-      <c r="C38" s="61" t="n"/>
-      <c r="D38" s="61" t="n"/>
-      <c r="E38" s="61" t="n"/>
-      <c r="F38" s="61" t="n"/>
-      <c r="G38" s="61" t="n"/>
-      <c r="H38" s="61" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B39" s="61" t="n"/>
-      <c r="C39" s="61" t="n"/>
-      <c r="D39" s="61" t="n"/>
-      <c r="E39" s="61" t="n"/>
-      <c r="F39" s="61" t="n"/>
-      <c r="G39" s="61" t="n"/>
-      <c r="H39" s="61" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B40" s="61" t="n"/>
-      <c r="C40" s="61" t="n"/>
-      <c r="D40" s="61" t="n"/>
-      <c r="E40" s="61" t="n"/>
-      <c r="F40" s="61" t="n"/>
-      <c r="G40" s="61" t="n"/>
-      <c r="H40" s="61" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B41" s="61" t="n"/>
-      <c r="C41" s="61" t="n"/>
-      <c r="D41" s="61" t="n"/>
-      <c r="E41" s="61" t="n"/>
-      <c r="F41" s="61" t="n"/>
-      <c r="G41" s="61" t="n"/>
-      <c r="H41" s="61" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B42" s="61" t="n"/>
-      <c r="C42" s="61" t="n"/>
-      <c r="D42" s="61" t="n"/>
-      <c r="E42" s="61" t="n"/>
-      <c r="F42" s="61" t="n"/>
-      <c r="G42" s="61" t="n"/>
-      <c r="H42" s="61" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B43" s="61" t="n"/>
-      <c r="C43" s="61" t="n"/>
-      <c r="D43" s="61" t="n"/>
-      <c r="E43" s="61" t="n"/>
-      <c r="F43" s="61" t="n"/>
-      <c r="G43" s="61" t="n"/>
-      <c r="H43" s="61" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="B44" s="61" t="n"/>
-      <c r="C44" s="61" t="n"/>
-      <c r="D44" s="61" t="n"/>
-      <c r="E44" s="61" t="n"/>
-      <c r="F44" s="61" t="n"/>
-      <c r="G44" s="61" t="n"/>
-      <c r="H44" s="61" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="B45" s="61" t="n"/>
-      <c r="C45" s="61" t="n"/>
-      <c r="D45" s="61" t="n"/>
-      <c r="E45" s="61" t="n"/>
-      <c r="F45" s="61" t="n"/>
-      <c r="G45" s="61" t="n"/>
-      <c r="H45" s="61" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="B46" s="61" t="n"/>
-      <c r="C46" s="61" t="n"/>
-      <c r="D46" s="61" t="n"/>
-      <c r="E46" s="61" t="n"/>
-      <c r="F46" s="61" t="n"/>
-      <c r="G46" s="61" t="n"/>
-      <c r="H46" s="61" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B47" s="61" t="n"/>
-      <c r="C47" s="61" t="n"/>
-      <c r="D47" s="61" t="n"/>
-      <c r="E47" s="61" t="n"/>
-      <c r="F47" s="61" t="n"/>
-      <c r="G47" s="61" t="n"/>
-      <c r="H47" s="61" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="B48" s="61" t="n"/>
-      <c r="C48" s="61" t="n"/>
-      <c r="D48" s="61" t="n"/>
-      <c r="E48" s="61" t="n"/>
-      <c r="F48" s="61" t="n"/>
-      <c r="G48" s="61" t="n"/>
-      <c r="H48" s="61" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="B49" s="61" t="n"/>
-      <c r="C49" s="61" t="n"/>
-      <c r="D49" s="61" t="n"/>
-      <c r="E49" s="61" t="n"/>
-      <c r="F49" s="61" t="n"/>
-      <c r="G49" s="61" t="n"/>
-      <c r="H49" s="61" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="B50" s="61" t="n"/>
-      <c r="C50" s="61" t="n"/>
-      <c r="D50" s="61" t="n"/>
-      <c r="E50" s="61" t="n"/>
-      <c r="F50" s="61" t="n"/>
-      <c r="G50" s="61" t="n"/>
-      <c r="H50" s="61" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:H50"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="B3:H50" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Required FTE for this interval. 0 or more; blank = no demand." prompt="Required FTE for this interval. 0 or more; blank = no demand." type="decimal" errorStyle="stop" operator="between">
-      <formula1>0</formula1>
-      <formula2>100000</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -5183,7 +4118,7 @@
     <row r="1" ht="24" customHeight="1" s="19">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>Shrinkage 15 Min — Matching shrinkage grid</t>
+          <t>FT Wise 15 Min — Full-week requirement input</t>
         </is>
       </c>
     </row>
@@ -6579,9 +5514,9 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B3:H98" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Shrinkage as a ratio (0.08) or percent (8%). Below 100%." prompt="Shrinkage as a ratio (0.08) or percent (8%). Below 100%." type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="B3:H98" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Required FTE for this interval. 0 or more; blank = no demand." prompt="Required FTE for this interval. 0 or more; blank = no demand." type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
-      <formula2>0.9999</formula2>
+      <formula2>100000</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6596,7 +5531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="19" min="1" max="1"/>
@@ -6606,7 +5541,7 @@
     <row r="1" ht="24" customHeight="1" s="19">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>Shrinkage 30 Min — Matching shrinkage grid</t>
+          <t>Shrinkage 15 Min — Matching shrinkage grid</t>
         </is>
       </c>
     </row>
@@ -6658,679 +5593,1351 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="B3" s="52" t="n"/>
-      <c r="C3" s="52" t="n"/>
-      <c r="D3" s="52" t="n"/>
-      <c r="E3" s="52" t="n"/>
-      <c r="F3" s="52" t="n"/>
-      <c r="G3" s="52" t="n"/>
-      <c r="H3" s="52" t="n"/>
+      <c r="B3" s="53" t="n"/>
+      <c r="C3" s="53" t="n"/>
+      <c r="D3" s="53" t="n"/>
+      <c r="E3" s="53" t="n"/>
+      <c r="F3" s="53" t="n"/>
+      <c r="G3" s="53" t="n"/>
+      <c r="H3" s="53" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>00:30</t>
-        </is>
-      </c>
-      <c r="B4" s="52" t="n"/>
-      <c r="C4" s="52" t="n"/>
-      <c r="D4" s="52" t="n"/>
-      <c r="E4" s="52" t="n"/>
-      <c r="F4" s="52" t="n"/>
-      <c r="G4" s="52" t="n"/>
-      <c r="H4" s="52" t="n"/>
+          <t>00:15</t>
+        </is>
+      </c>
+      <c r="B4" s="53" t="n"/>
+      <c r="C4" s="53" t="n"/>
+      <c r="D4" s="53" t="n"/>
+      <c r="E4" s="53" t="n"/>
+      <c r="F4" s="53" t="n"/>
+      <c r="G4" s="53" t="n"/>
+      <c r="H4" s="53" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
-        </is>
-      </c>
-      <c r="B5" s="52" t="n"/>
-      <c r="C5" s="52" t="n"/>
-      <c r="D5" s="52" t="n"/>
-      <c r="E5" s="52" t="n"/>
-      <c r="F5" s="52" t="n"/>
-      <c r="G5" s="52" t="n"/>
-      <c r="H5" s="52" t="n"/>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="B5" s="53" t="n"/>
+      <c r="C5" s="53" t="n"/>
+      <c r="D5" s="53" t="n"/>
+      <c r="E5" s="53" t="n"/>
+      <c r="F5" s="53" t="n"/>
+      <c r="G5" s="53" t="n"/>
+      <c r="H5" s="53" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>01:30</t>
-        </is>
-      </c>
-      <c r="B6" s="52" t="n"/>
-      <c r="C6" s="52" t="n"/>
-      <c r="D6" s="52" t="n"/>
-      <c r="E6" s="52" t="n"/>
-      <c r="F6" s="52" t="n"/>
-      <c r="G6" s="52" t="n"/>
-      <c r="H6" s="52" t="n"/>
+          <t>00:45</t>
+        </is>
+      </c>
+      <c r="B6" s="53" t="n"/>
+      <c r="C6" s="53" t="n"/>
+      <c r="D6" s="53" t="n"/>
+      <c r="E6" s="53" t="n"/>
+      <c r="F6" s="53" t="n"/>
+      <c r="G6" s="53" t="n"/>
+      <c r="H6" s="53" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>02:00</t>
-        </is>
-      </c>
-      <c r="B7" s="52" t="n"/>
-      <c r="C7" s="52" t="n"/>
-      <c r="D7" s="52" t="n"/>
-      <c r="E7" s="52" t="n"/>
-      <c r="F7" s="52" t="n"/>
-      <c r="G7" s="52" t="n"/>
-      <c r="H7" s="52" t="n"/>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="B7" s="53" t="n"/>
+      <c r="C7" s="53" t="n"/>
+      <c r="D7" s="53" t="n"/>
+      <c r="E7" s="53" t="n"/>
+      <c r="F7" s="53" t="n"/>
+      <c r="G7" s="53" t="n"/>
+      <c r="H7" s="53" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>02:30</t>
-        </is>
-      </c>
-      <c r="B8" s="52" t="n"/>
-      <c r="C8" s="52" t="n"/>
-      <c r="D8" s="52" t="n"/>
-      <c r="E8" s="52" t="n"/>
-      <c r="F8" s="52" t="n"/>
-      <c r="G8" s="52" t="n"/>
-      <c r="H8" s="52" t="n"/>
+          <t>01:15</t>
+        </is>
+      </c>
+      <c r="B8" s="53" t="n"/>
+      <c r="C8" s="53" t="n"/>
+      <c r="D8" s="53" t="n"/>
+      <c r="E8" s="53" t="n"/>
+      <c r="F8" s="53" t="n"/>
+      <c r="G8" s="53" t="n"/>
+      <c r="H8" s="53" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
-        </is>
-      </c>
-      <c r="B9" s="52" t="n"/>
-      <c r="C9" s="52" t="n"/>
-      <c r="D9" s="52" t="n"/>
-      <c r="E9" s="52" t="n"/>
-      <c r="F9" s="52" t="n"/>
-      <c r="G9" s="52" t="n"/>
-      <c r="H9" s="52" t="n"/>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="B9" s="53" t="n"/>
+      <c r="C9" s="53" t="n"/>
+      <c r="D9" s="53" t="n"/>
+      <c r="E9" s="53" t="n"/>
+      <c r="F9" s="53" t="n"/>
+      <c r="G9" s="53" t="n"/>
+      <c r="H9" s="53" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>03:30</t>
-        </is>
-      </c>
-      <c r="B10" s="52" t="n"/>
-      <c r="C10" s="52" t="n"/>
-      <c r="D10" s="52" t="n"/>
-      <c r="E10" s="52" t="n"/>
-      <c r="F10" s="52" t="n"/>
-      <c r="G10" s="52" t="n"/>
-      <c r="H10" s="52" t="n"/>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="B10" s="53" t="n"/>
+      <c r="C10" s="53" t="n"/>
+      <c r="D10" s="53" t="n"/>
+      <c r="E10" s="53" t="n"/>
+      <c r="F10" s="53" t="n"/>
+      <c r="G10" s="53" t="n"/>
+      <c r="H10" s="53" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="B11" s="52" t="n"/>
-      <c r="C11" s="52" t="n"/>
-      <c r="D11" s="52" t="n"/>
-      <c r="E11" s="52" t="n"/>
-      <c r="F11" s="52" t="n"/>
-      <c r="G11" s="52" t="n"/>
-      <c r="H11" s="52" t="n"/>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="B11" s="53" t="n"/>
+      <c r="C11" s="53" t="n"/>
+      <c r="D11" s="53" t="n"/>
+      <c r="E11" s="53" t="n"/>
+      <c r="F11" s="53" t="n"/>
+      <c r="G11" s="53" t="n"/>
+      <c r="H11" s="53" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="B12" s="52" t="n"/>
-      <c r="C12" s="52" t="n"/>
-      <c r="D12" s="52" t="n"/>
-      <c r="E12" s="52" t="n"/>
-      <c r="F12" s="52" t="n"/>
-      <c r="G12" s="52" t="n"/>
-      <c r="H12" s="52" t="n"/>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="B12" s="53" t="n"/>
+      <c r="C12" s="53" t="n"/>
+      <c r="D12" s="53" t="n"/>
+      <c r="E12" s="53" t="n"/>
+      <c r="F12" s="53" t="n"/>
+      <c r="G12" s="53" t="n"/>
+      <c r="H12" s="53" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="B13" s="52" t="n"/>
-      <c r="C13" s="52" t="n"/>
-      <c r="D13" s="52" t="n"/>
-      <c r="E13" s="52" t="n"/>
-      <c r="F13" s="52" t="n"/>
-      <c r="G13" s="52" t="n"/>
-      <c r="H13" s="52" t="n"/>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="B13" s="53" t="n"/>
+      <c r="C13" s="53" t="n"/>
+      <c r="D13" s="53" t="n"/>
+      <c r="E13" s="53" t="n"/>
+      <c r="F13" s="53" t="n"/>
+      <c r="G13" s="53" t="n"/>
+      <c r="H13" s="53" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="B14" s="52" t="n"/>
-      <c r="C14" s="52" t="n"/>
-      <c r="D14" s="52" t="n"/>
-      <c r="E14" s="52" t="n"/>
-      <c r="F14" s="52" t="n"/>
-      <c r="G14" s="52" t="n"/>
-      <c r="H14" s="52" t="n"/>
+          <t>02:45</t>
+        </is>
+      </c>
+      <c r="B14" s="53" t="n"/>
+      <c r="C14" s="53" t="n"/>
+      <c r="D14" s="53" t="n"/>
+      <c r="E14" s="53" t="n"/>
+      <c r="F14" s="53" t="n"/>
+      <c r="G14" s="53" t="n"/>
+      <c r="H14" s="53" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="B15" s="52" t="n"/>
-      <c r="C15" s="52" t="n"/>
-      <c r="D15" s="52" t="n"/>
-      <c r="E15" s="52" t="n"/>
-      <c r="F15" s="52" t="n"/>
-      <c r="G15" s="52" t="n"/>
-      <c r="H15" s="52" t="n"/>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="B15" s="53" t="n"/>
+      <c r="C15" s="53" t="n"/>
+      <c r="D15" s="53" t="n"/>
+      <c r="E15" s="53" t="n"/>
+      <c r="F15" s="53" t="n"/>
+      <c r="G15" s="53" t="n"/>
+      <c r="H15" s="53" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
-        </is>
-      </c>
-      <c r="B16" s="52" t="n"/>
-      <c r="C16" s="52" t="n"/>
-      <c r="D16" s="52" t="n"/>
-      <c r="E16" s="52" t="n"/>
-      <c r="F16" s="52" t="n"/>
-      <c r="G16" s="52" t="n"/>
-      <c r="H16" s="52" t="n"/>
+          <t>03:15</t>
+        </is>
+      </c>
+      <c r="B16" s="53" t="n"/>
+      <c r="C16" s="53" t="n"/>
+      <c r="D16" s="53" t="n"/>
+      <c r="E16" s="53" t="n"/>
+      <c r="F16" s="53" t="n"/>
+      <c r="G16" s="53" t="n"/>
+      <c r="H16" s="53" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="B17" s="52" t="n"/>
-      <c r="C17" s="52" t="n"/>
-      <c r="D17" s="52" t="n"/>
-      <c r="E17" s="52" t="n"/>
-      <c r="F17" s="52" t="n"/>
-      <c r="G17" s="52" t="n"/>
-      <c r="H17" s="52" t="n"/>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="B17" s="53" t="n"/>
+      <c r="C17" s="53" t="n"/>
+      <c r="D17" s="53" t="n"/>
+      <c r="E17" s="53" t="n"/>
+      <c r="F17" s="53" t="n"/>
+      <c r="G17" s="53" t="n"/>
+      <c r="H17" s="53" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="B18" s="52" t="n"/>
-      <c r="C18" s="52" t="n"/>
-      <c r="D18" s="52" t="n"/>
-      <c r="E18" s="52" t="n"/>
-      <c r="F18" s="52" t="n"/>
-      <c r="G18" s="52" t="n"/>
-      <c r="H18" s="52" t="n"/>
+          <t>03:45</t>
+        </is>
+      </c>
+      <c r="B18" s="53" t="n"/>
+      <c r="C18" s="53" t="n"/>
+      <c r="D18" s="53" t="n"/>
+      <c r="E18" s="53" t="n"/>
+      <c r="F18" s="53" t="n"/>
+      <c r="G18" s="53" t="n"/>
+      <c r="H18" s="53" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="B19" s="52" t="n"/>
-      <c r="C19" s="52" t="n"/>
-      <c r="D19" s="52" t="n"/>
-      <c r="E19" s="52" t="n"/>
-      <c r="F19" s="52" t="n"/>
-      <c r="G19" s="52" t="n"/>
-      <c r="H19" s="52" t="n"/>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="B19" s="53" t="n"/>
+      <c r="C19" s="53" t="n"/>
+      <c r="D19" s="53" t="n"/>
+      <c r="E19" s="53" t="n"/>
+      <c r="F19" s="53" t="n"/>
+      <c r="G19" s="53" t="n"/>
+      <c r="H19" s="53" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="B20" s="52" t="n"/>
-      <c r="C20" s="52" t="n"/>
-      <c r="D20" s="52" t="n"/>
-      <c r="E20" s="52" t="n"/>
-      <c r="F20" s="52" t="n"/>
-      <c r="G20" s="52" t="n"/>
-      <c r="H20" s="52" t="n"/>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="B20" s="53" t="n"/>
+      <c r="C20" s="53" t="n"/>
+      <c r="D20" s="53" t="n"/>
+      <c r="E20" s="53" t="n"/>
+      <c r="F20" s="53" t="n"/>
+      <c r="G20" s="53" t="n"/>
+      <c r="H20" s="53" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="B21" s="52" t="n"/>
-      <c r="C21" s="52" t="n"/>
-      <c r="D21" s="52" t="n"/>
-      <c r="E21" s="52" t="n"/>
-      <c r="F21" s="52" t="n"/>
-      <c r="G21" s="52" t="n"/>
-      <c r="H21" s="52" t="n"/>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="B21" s="53" t="n"/>
+      <c r="C21" s="53" t="n"/>
+      <c r="D21" s="53" t="n"/>
+      <c r="E21" s="53" t="n"/>
+      <c r="F21" s="53" t="n"/>
+      <c r="G21" s="53" t="n"/>
+      <c r="H21" s="53" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B22" s="52" t="n"/>
-      <c r="C22" s="52" t="n"/>
-      <c r="D22" s="52" t="n"/>
-      <c r="E22" s="52" t="n"/>
-      <c r="F22" s="52" t="n"/>
-      <c r="G22" s="52" t="n"/>
-      <c r="H22" s="52" t="n"/>
+          <t>04:45</t>
+        </is>
+      </c>
+      <c r="B22" s="53" t="n"/>
+      <c r="C22" s="53" t="n"/>
+      <c r="D22" s="53" t="n"/>
+      <c r="E22" s="53" t="n"/>
+      <c r="F22" s="53" t="n"/>
+      <c r="G22" s="53" t="n"/>
+      <c r="H22" s="53" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B23" s="52" t="n"/>
-      <c r="C23" s="52" t="n"/>
-      <c r="D23" s="52" t="n"/>
-      <c r="E23" s="52" t="n"/>
-      <c r="F23" s="52" t="n"/>
-      <c r="G23" s="52" t="n"/>
-      <c r="H23" s="52" t="n"/>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="B23" s="53" t="n"/>
+      <c r="C23" s="53" t="n"/>
+      <c r="D23" s="53" t="n"/>
+      <c r="E23" s="53" t="n"/>
+      <c r="F23" s="53" t="n"/>
+      <c r="G23" s="53" t="n"/>
+      <c r="H23" s="53" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="B24" s="52" t="n"/>
-      <c r="C24" s="52" t="n"/>
-      <c r="D24" s="52" t="n"/>
-      <c r="E24" s="52" t="n"/>
-      <c r="F24" s="52" t="n"/>
-      <c r="G24" s="52" t="n"/>
-      <c r="H24" s="52" t="n"/>
+          <t>05:15</t>
+        </is>
+      </c>
+      <c r="B24" s="53" t="n"/>
+      <c r="C24" s="53" t="n"/>
+      <c r="D24" s="53" t="n"/>
+      <c r="E24" s="53" t="n"/>
+      <c r="F24" s="53" t="n"/>
+      <c r="G24" s="53" t="n"/>
+      <c r="H24" s="53" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B25" s="52" t="n"/>
-      <c r="C25" s="52" t="n"/>
-      <c r="D25" s="52" t="n"/>
-      <c r="E25" s="52" t="n"/>
-      <c r="F25" s="52" t="n"/>
-      <c r="G25" s="52" t="n"/>
-      <c r="H25" s="52" t="n"/>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="B25" s="53" t="n"/>
+      <c r="C25" s="53" t="n"/>
+      <c r="D25" s="53" t="n"/>
+      <c r="E25" s="53" t="n"/>
+      <c r="F25" s="53" t="n"/>
+      <c r="G25" s="53" t="n"/>
+      <c r="H25" s="53" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B26" s="52" t="n"/>
-      <c r="C26" s="52" t="n"/>
-      <c r="D26" s="52" t="n"/>
-      <c r="E26" s="52" t="n"/>
-      <c r="F26" s="52" t="n"/>
-      <c r="G26" s="52" t="n"/>
-      <c r="H26" s="52" t="n"/>
+          <t>05:45</t>
+        </is>
+      </c>
+      <c r="B26" s="53" t="n"/>
+      <c r="C26" s="53" t="n"/>
+      <c r="D26" s="53" t="n"/>
+      <c r="E26" s="53" t="n"/>
+      <c r="F26" s="53" t="n"/>
+      <c r="G26" s="53" t="n"/>
+      <c r="H26" s="53" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B27" s="52" t="n"/>
-      <c r="C27" s="52" t="n"/>
-      <c r="D27" s="52" t="n"/>
-      <c r="E27" s="52" t="n"/>
-      <c r="F27" s="52" t="n"/>
-      <c r="G27" s="52" t="n"/>
-      <c r="H27" s="52" t="n"/>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="B27" s="53" t="n"/>
+      <c r="C27" s="53" t="n"/>
+      <c r="D27" s="53" t="n"/>
+      <c r="E27" s="53" t="n"/>
+      <c r="F27" s="53" t="n"/>
+      <c r="G27" s="53" t="n"/>
+      <c r="H27" s="53" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="B28" s="52" t="n"/>
-      <c r="C28" s="52" t="n"/>
-      <c r="D28" s="52" t="n"/>
-      <c r="E28" s="52" t="n"/>
-      <c r="F28" s="52" t="n"/>
-      <c r="G28" s="52" t="n"/>
-      <c r="H28" s="52" t="n"/>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="B28" s="53" t="n"/>
+      <c r="C28" s="53" t="n"/>
+      <c r="D28" s="53" t="n"/>
+      <c r="E28" s="53" t="n"/>
+      <c r="F28" s="53" t="n"/>
+      <c r="G28" s="53" t="n"/>
+      <c r="H28" s="53" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="B29" s="52" t="n"/>
-      <c r="C29" s="52" t="n"/>
-      <c r="D29" s="52" t="n"/>
-      <c r="E29" s="52" t="n"/>
-      <c r="F29" s="52" t="n"/>
-      <c r="G29" s="52" t="n"/>
-      <c r="H29" s="52" t="n"/>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="B29" s="53" t="n"/>
+      <c r="C29" s="53" t="n"/>
+      <c r="D29" s="53" t="n"/>
+      <c r="E29" s="53" t="n"/>
+      <c r="F29" s="53" t="n"/>
+      <c r="G29" s="53" t="n"/>
+      <c r="H29" s="53" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="B30" s="52" t="n"/>
-      <c r="C30" s="52" t="n"/>
-      <c r="D30" s="52" t="n"/>
-      <c r="E30" s="52" t="n"/>
-      <c r="F30" s="52" t="n"/>
-      <c r="G30" s="52" t="n"/>
-      <c r="H30" s="52" t="n"/>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="B30" s="53" t="n"/>
+      <c r="C30" s="53" t="n"/>
+      <c r="D30" s="53" t="n"/>
+      <c r="E30" s="53" t="n"/>
+      <c r="F30" s="53" t="n"/>
+      <c r="G30" s="53" t="n"/>
+      <c r="H30" s="53" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="B31" s="52" t="n"/>
-      <c r="C31" s="52" t="n"/>
-      <c r="D31" s="52" t="n"/>
-      <c r="E31" s="52" t="n"/>
-      <c r="F31" s="52" t="n"/>
-      <c r="G31" s="52" t="n"/>
-      <c r="H31" s="52" t="n"/>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="B31" s="53" t="n"/>
+      <c r="C31" s="53" t="n"/>
+      <c r="D31" s="53" t="n"/>
+      <c r="E31" s="53" t="n"/>
+      <c r="F31" s="53" t="n"/>
+      <c r="G31" s="53" t="n"/>
+      <c r="H31" s="53" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="B32" s="52" t="n"/>
-      <c r="C32" s="52" t="n"/>
-      <c r="D32" s="52" t="n"/>
-      <c r="E32" s="52" t="n"/>
-      <c r="F32" s="52" t="n"/>
-      <c r="G32" s="52" t="n"/>
-      <c r="H32" s="52" t="n"/>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="B32" s="53" t="n"/>
+      <c r="C32" s="53" t="n"/>
+      <c r="D32" s="53" t="n"/>
+      <c r="E32" s="53" t="n"/>
+      <c r="F32" s="53" t="n"/>
+      <c r="G32" s="53" t="n"/>
+      <c r="H32" s="53" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="B33" s="52" t="n"/>
-      <c r="C33" s="52" t="n"/>
-      <c r="D33" s="52" t="n"/>
-      <c r="E33" s="52" t="n"/>
-      <c r="F33" s="52" t="n"/>
-      <c r="G33" s="52" t="n"/>
-      <c r="H33" s="52" t="n"/>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="B33" s="53" t="n"/>
+      <c r="C33" s="53" t="n"/>
+      <c r="D33" s="53" t="n"/>
+      <c r="E33" s="53" t="n"/>
+      <c r="F33" s="53" t="n"/>
+      <c r="G33" s="53" t="n"/>
+      <c r="H33" s="53" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="B34" s="52" t="n"/>
-      <c r="C34" s="52" t="n"/>
-      <c r="D34" s="52" t="n"/>
-      <c r="E34" s="52" t="n"/>
-      <c r="F34" s="52" t="n"/>
-      <c r="G34" s="52" t="n"/>
-      <c r="H34" s="52" t="n"/>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="B34" s="53" t="n"/>
+      <c r="C34" s="53" t="n"/>
+      <c r="D34" s="53" t="n"/>
+      <c r="E34" s="53" t="n"/>
+      <c r="F34" s="53" t="n"/>
+      <c r="G34" s="53" t="n"/>
+      <c r="H34" s="53" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="B35" s="52" t="n"/>
-      <c r="C35" s="52" t="n"/>
-      <c r="D35" s="52" t="n"/>
-      <c r="E35" s="52" t="n"/>
-      <c r="F35" s="52" t="n"/>
-      <c r="G35" s="52" t="n"/>
-      <c r="H35" s="52" t="n"/>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B35" s="53" t="n"/>
+      <c r="C35" s="53" t="n"/>
+      <c r="D35" s="53" t="n"/>
+      <c r="E35" s="53" t="n"/>
+      <c r="F35" s="53" t="n"/>
+      <c r="G35" s="53" t="n"/>
+      <c r="H35" s="53" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="B36" s="52" t="n"/>
-      <c r="C36" s="52" t="n"/>
-      <c r="D36" s="52" t="n"/>
-      <c r="E36" s="52" t="n"/>
-      <c r="F36" s="52" t="n"/>
-      <c r="G36" s="52" t="n"/>
-      <c r="H36" s="52" t="n"/>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B36" s="53" t="n"/>
+      <c r="C36" s="53" t="n"/>
+      <c r="D36" s="53" t="n"/>
+      <c r="E36" s="53" t="n"/>
+      <c r="F36" s="53" t="n"/>
+      <c r="G36" s="53" t="n"/>
+      <c r="H36" s="53" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B37" s="52" t="n"/>
-      <c r="C37" s="52" t="n"/>
-      <c r="D37" s="52" t="n"/>
-      <c r="E37" s="52" t="n"/>
-      <c r="F37" s="52" t="n"/>
-      <c r="G37" s="52" t="n"/>
-      <c r="H37" s="52" t="n"/>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B37" s="53" t="n"/>
+      <c r="C37" s="53" t="n"/>
+      <c r="D37" s="53" t="n"/>
+      <c r="E37" s="53" t="n"/>
+      <c r="F37" s="53" t="n"/>
+      <c r="G37" s="53" t="n"/>
+      <c r="H37" s="53" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B38" s="52" t="n"/>
-      <c r="C38" s="52" t="n"/>
-      <c r="D38" s="52" t="n"/>
-      <c r="E38" s="52" t="n"/>
-      <c r="F38" s="52" t="n"/>
-      <c r="G38" s="52" t="n"/>
-      <c r="H38" s="52" t="n"/>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="B38" s="53" t="n"/>
+      <c r="C38" s="53" t="n"/>
+      <c r="D38" s="53" t="n"/>
+      <c r="E38" s="53" t="n"/>
+      <c r="F38" s="53" t="n"/>
+      <c r="G38" s="53" t="n"/>
+      <c r="H38" s="53" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B39" s="52" t="n"/>
-      <c r="C39" s="52" t="n"/>
-      <c r="D39" s="52" t="n"/>
-      <c r="E39" s="52" t="n"/>
-      <c r="F39" s="52" t="n"/>
-      <c r="G39" s="52" t="n"/>
-      <c r="H39" s="52" t="n"/>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B39" s="53" t="n"/>
+      <c r="C39" s="53" t="n"/>
+      <c r="D39" s="53" t="n"/>
+      <c r="E39" s="53" t="n"/>
+      <c r="F39" s="53" t="n"/>
+      <c r="G39" s="53" t="n"/>
+      <c r="H39" s="53" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B40" s="52" t="n"/>
-      <c r="C40" s="52" t="n"/>
-      <c r="D40" s="52" t="n"/>
-      <c r="E40" s="52" t="n"/>
-      <c r="F40" s="52" t="n"/>
-      <c r="G40" s="52" t="n"/>
-      <c r="H40" s="52" t="n"/>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="B40" s="53" t="n"/>
+      <c r="C40" s="53" t="n"/>
+      <c r="D40" s="53" t="n"/>
+      <c r="E40" s="53" t="n"/>
+      <c r="F40" s="53" t="n"/>
+      <c r="G40" s="53" t="n"/>
+      <c r="H40" s="53" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B41" s="52" t="n"/>
-      <c r="C41" s="52" t="n"/>
-      <c r="D41" s="52" t="n"/>
-      <c r="E41" s="52" t="n"/>
-      <c r="F41" s="52" t="n"/>
-      <c r="G41" s="52" t="n"/>
-      <c r="H41" s="52" t="n"/>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B41" s="53" t="n"/>
+      <c r="C41" s="53" t="n"/>
+      <c r="D41" s="53" t="n"/>
+      <c r="E41" s="53" t="n"/>
+      <c r="F41" s="53" t="n"/>
+      <c r="G41" s="53" t="n"/>
+      <c r="H41" s="53" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B42" s="52" t="n"/>
-      <c r="C42" s="52" t="n"/>
-      <c r="D42" s="52" t="n"/>
-      <c r="E42" s="52" t="n"/>
-      <c r="F42" s="52" t="n"/>
-      <c r="G42" s="52" t="n"/>
-      <c r="H42" s="52" t="n"/>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="B42" s="53" t="n"/>
+      <c r="C42" s="53" t="n"/>
+      <c r="D42" s="53" t="n"/>
+      <c r="E42" s="53" t="n"/>
+      <c r="F42" s="53" t="n"/>
+      <c r="G42" s="53" t="n"/>
+      <c r="H42" s="53" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B43" s="52" t="n"/>
-      <c r="C43" s="52" t="n"/>
-      <c r="D43" s="52" t="n"/>
-      <c r="E43" s="52" t="n"/>
-      <c r="F43" s="52" t="n"/>
-      <c r="G43" s="52" t="n"/>
-      <c r="H43" s="52" t="n"/>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B43" s="53" t="n"/>
+      <c r="C43" s="53" t="n"/>
+      <c r="D43" s="53" t="n"/>
+      <c r="E43" s="53" t="n"/>
+      <c r="F43" s="53" t="n"/>
+      <c r="G43" s="53" t="n"/>
+      <c r="H43" s="53" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="B44" s="52" t="n"/>
-      <c r="C44" s="52" t="n"/>
-      <c r="D44" s="52" t="n"/>
-      <c r="E44" s="52" t="n"/>
-      <c r="F44" s="52" t="n"/>
-      <c r="G44" s="52" t="n"/>
-      <c r="H44" s="52" t="n"/>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B44" s="53" t="n"/>
+      <c r="C44" s="53" t="n"/>
+      <c r="D44" s="53" t="n"/>
+      <c r="E44" s="53" t="n"/>
+      <c r="F44" s="53" t="n"/>
+      <c r="G44" s="53" t="n"/>
+      <c r="H44" s="53" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="B45" s="52" t="n"/>
-      <c r="C45" s="52" t="n"/>
-      <c r="D45" s="52" t="n"/>
-      <c r="E45" s="52" t="n"/>
-      <c r="F45" s="52" t="n"/>
-      <c r="G45" s="52" t="n"/>
-      <c r="H45" s="52" t="n"/>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="53" t="n"/>
+      <c r="D45" s="53" t="n"/>
+      <c r="E45" s="53" t="n"/>
+      <c r="F45" s="53" t="n"/>
+      <c r="G45" s="53" t="n"/>
+      <c r="H45" s="53" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="B46" s="52" t="n"/>
-      <c r="C46" s="52" t="n"/>
-      <c r="D46" s="52" t="n"/>
-      <c r="E46" s="52" t="n"/>
-      <c r="F46" s="52" t="n"/>
-      <c r="G46" s="52" t="n"/>
-      <c r="H46" s="52" t="n"/>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="B46" s="53" t="n"/>
+      <c r="C46" s="53" t="n"/>
+      <c r="D46" s="53" t="n"/>
+      <c r="E46" s="53" t="n"/>
+      <c r="F46" s="53" t="n"/>
+      <c r="G46" s="53" t="n"/>
+      <c r="H46" s="53" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B47" s="52" t="n"/>
-      <c r="C47" s="52" t="n"/>
-      <c r="D47" s="52" t="n"/>
-      <c r="E47" s="52" t="n"/>
-      <c r="F47" s="52" t="n"/>
-      <c r="G47" s="52" t="n"/>
-      <c r="H47" s="52" t="n"/>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B47" s="53" t="n"/>
+      <c r="C47" s="53" t="n"/>
+      <c r="D47" s="53" t="n"/>
+      <c r="E47" s="53" t="n"/>
+      <c r="F47" s="53" t="n"/>
+      <c r="G47" s="53" t="n"/>
+      <c r="H47" s="53" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="B48" s="52" t="n"/>
-      <c r="C48" s="52" t="n"/>
-      <c r="D48" s="52" t="n"/>
-      <c r="E48" s="52" t="n"/>
-      <c r="F48" s="52" t="n"/>
-      <c r="G48" s="52" t="n"/>
-      <c r="H48" s="52" t="n"/>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="B48" s="53" t="n"/>
+      <c r="C48" s="53" t="n"/>
+      <c r="D48" s="53" t="n"/>
+      <c r="E48" s="53" t="n"/>
+      <c r="F48" s="53" t="n"/>
+      <c r="G48" s="53" t="n"/>
+      <c r="H48" s="53" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="B49" s="52" t="n"/>
-      <c r="C49" s="52" t="n"/>
-      <c r="D49" s="52" t="n"/>
-      <c r="E49" s="52" t="n"/>
-      <c r="F49" s="52" t="n"/>
-      <c r="G49" s="52" t="n"/>
-      <c r="H49" s="52" t="n"/>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B49" s="53" t="n"/>
+      <c r="C49" s="53" t="n"/>
+      <c r="D49" s="53" t="n"/>
+      <c r="E49" s="53" t="n"/>
+      <c r="F49" s="53" t="n"/>
+      <c r="G49" s="53" t="n"/>
+      <c r="H49" s="53" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="B50" s="53" t="n"/>
+      <c r="C50" s="53" t="n"/>
+      <c r="D50" s="53" t="n"/>
+      <c r="E50" s="53" t="n"/>
+      <c r="F50" s="53" t="n"/>
+      <c r="G50" s="53" t="n"/>
+      <c r="H50" s="53" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B51" s="53" t="n"/>
+      <c r="C51" s="53" t="n"/>
+      <c r="D51" s="53" t="n"/>
+      <c r="E51" s="53" t="n"/>
+      <c r="F51" s="53" t="n"/>
+      <c r="G51" s="53" t="n"/>
+      <c r="H51" s="53" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="B52" s="53" t="n"/>
+      <c r="C52" s="53" t="n"/>
+      <c r="D52" s="53" t="n"/>
+      <c r="E52" s="53" t="n"/>
+      <c r="F52" s="53" t="n"/>
+      <c r="G52" s="53" t="n"/>
+      <c r="H52" s="53" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B53" s="53" t="n"/>
+      <c r="C53" s="53" t="n"/>
+      <c r="D53" s="53" t="n"/>
+      <c r="E53" s="53" t="n"/>
+      <c r="F53" s="53" t="n"/>
+      <c r="G53" s="53" t="n"/>
+      <c r="H53" s="53" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="B54" s="53" t="n"/>
+      <c r="C54" s="53" t="n"/>
+      <c r="D54" s="53" t="n"/>
+      <c r="E54" s="53" t="n"/>
+      <c r="F54" s="53" t="n"/>
+      <c r="G54" s="53" t="n"/>
+      <c r="H54" s="53" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="B55" s="53" t="n"/>
+      <c r="C55" s="53" t="n"/>
+      <c r="D55" s="53" t="n"/>
+      <c r="E55" s="53" t="n"/>
+      <c r="F55" s="53" t="n"/>
+      <c r="G55" s="53" t="n"/>
+      <c r="H55" s="53" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="B56" s="53" t="n"/>
+      <c r="C56" s="53" t="n"/>
+      <c r="D56" s="53" t="n"/>
+      <c r="E56" s="53" t="n"/>
+      <c r="F56" s="53" t="n"/>
+      <c r="G56" s="53" t="n"/>
+      <c r="H56" s="53" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="B57" s="53" t="n"/>
+      <c r="C57" s="53" t="n"/>
+      <c r="D57" s="53" t="n"/>
+      <c r="E57" s="53" t="n"/>
+      <c r="F57" s="53" t="n"/>
+      <c r="G57" s="53" t="n"/>
+      <c r="H57" s="53" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="B58" s="53" t="n"/>
+      <c r="C58" s="53" t="n"/>
+      <c r="D58" s="53" t="n"/>
+      <c r="E58" s="53" t="n"/>
+      <c r="F58" s="53" t="n"/>
+      <c r="G58" s="53" t="n"/>
+      <c r="H58" s="53" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="B59" s="53" t="n"/>
+      <c r="C59" s="53" t="n"/>
+      <c r="D59" s="53" t="n"/>
+      <c r="E59" s="53" t="n"/>
+      <c r="F59" s="53" t="n"/>
+      <c r="G59" s="53" t="n"/>
+      <c r="H59" s="53" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="B60" s="53" t="n"/>
+      <c r="C60" s="53" t="n"/>
+      <c r="D60" s="53" t="n"/>
+      <c r="E60" s="53" t="n"/>
+      <c r="F60" s="53" t="n"/>
+      <c r="G60" s="53" t="n"/>
+      <c r="H60" s="53" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="B61" s="53" t="n"/>
+      <c r="C61" s="53" t="n"/>
+      <c r="D61" s="53" t="n"/>
+      <c r="E61" s="53" t="n"/>
+      <c r="F61" s="53" t="n"/>
+      <c r="G61" s="53" t="n"/>
+      <c r="H61" s="53" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="B62" s="53" t="n"/>
+      <c r="C62" s="53" t="n"/>
+      <c r="D62" s="53" t="n"/>
+      <c r="E62" s="53" t="n"/>
+      <c r="F62" s="53" t="n"/>
+      <c r="G62" s="53" t="n"/>
+      <c r="H62" s="53" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="B63" s="53" t="n"/>
+      <c r="C63" s="53" t="n"/>
+      <c r="D63" s="53" t="n"/>
+      <c r="E63" s="53" t="n"/>
+      <c r="F63" s="53" t="n"/>
+      <c r="G63" s="53" t="n"/>
+      <c r="H63" s="53" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="B64" s="53" t="n"/>
+      <c r="C64" s="53" t="n"/>
+      <c r="D64" s="53" t="n"/>
+      <c r="E64" s="53" t="n"/>
+      <c r="F64" s="53" t="n"/>
+      <c r="G64" s="53" t="n"/>
+      <c r="H64" s="53" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="B65" s="53" t="n"/>
+      <c r="C65" s="53" t="n"/>
+      <c r="D65" s="53" t="n"/>
+      <c r="E65" s="53" t="n"/>
+      <c r="F65" s="53" t="n"/>
+      <c r="G65" s="53" t="n"/>
+      <c r="H65" s="53" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="B66" s="53" t="n"/>
+      <c r="C66" s="53" t="n"/>
+      <c r="D66" s="53" t="n"/>
+      <c r="E66" s="53" t="n"/>
+      <c r="F66" s="53" t="n"/>
+      <c r="G66" s="53" t="n"/>
+      <c r="H66" s="53" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B67" s="53" t="n"/>
+      <c r="C67" s="53" t="n"/>
+      <c r="D67" s="53" t="n"/>
+      <c r="E67" s="53" t="n"/>
+      <c r="F67" s="53" t="n"/>
+      <c r="G67" s="53" t="n"/>
+      <c r="H67" s="53" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="B68" s="53" t="n"/>
+      <c r="C68" s="53" t="n"/>
+      <c r="D68" s="53" t="n"/>
+      <c r="E68" s="53" t="n"/>
+      <c r="F68" s="53" t="n"/>
+      <c r="G68" s="53" t="n"/>
+      <c r="H68" s="53" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B69" s="53" t="n"/>
+      <c r="C69" s="53" t="n"/>
+      <c r="D69" s="53" t="n"/>
+      <c r="E69" s="53" t="n"/>
+      <c r="F69" s="53" t="n"/>
+      <c r="G69" s="53" t="n"/>
+      <c r="H69" s="53" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="B70" s="53" t="n"/>
+      <c r="C70" s="53" t="n"/>
+      <c r="D70" s="53" t="n"/>
+      <c r="E70" s="53" t="n"/>
+      <c r="F70" s="53" t="n"/>
+      <c r="G70" s="53" t="n"/>
+      <c r="H70" s="53" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B71" s="53" t="n"/>
+      <c r="C71" s="53" t="n"/>
+      <c r="D71" s="53" t="n"/>
+      <c r="E71" s="53" t="n"/>
+      <c r="F71" s="53" t="n"/>
+      <c r="G71" s="53" t="n"/>
+      <c r="H71" s="53" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="B72" s="53" t="n"/>
+      <c r="C72" s="53" t="n"/>
+      <c r="D72" s="53" t="n"/>
+      <c r="E72" s="53" t="n"/>
+      <c r="F72" s="53" t="n"/>
+      <c r="G72" s="53" t="n"/>
+      <c r="H72" s="53" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B73" s="53" t="n"/>
+      <c r="C73" s="53" t="n"/>
+      <c r="D73" s="53" t="n"/>
+      <c r="E73" s="53" t="n"/>
+      <c r="F73" s="53" t="n"/>
+      <c r="G73" s="53" t="n"/>
+      <c r="H73" s="53" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B74" s="53" t="n"/>
+      <c r="C74" s="53" t="n"/>
+      <c r="D74" s="53" t="n"/>
+      <c r="E74" s="53" t="n"/>
+      <c r="F74" s="53" t="n"/>
+      <c r="G74" s="53" t="n"/>
+      <c r="H74" s="53" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B75" s="53" t="n"/>
+      <c r="C75" s="53" t="n"/>
+      <c r="D75" s="53" t="n"/>
+      <c r="E75" s="53" t="n"/>
+      <c r="F75" s="53" t="n"/>
+      <c r="G75" s="53" t="n"/>
+      <c r="H75" s="53" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B76" s="53" t="n"/>
+      <c r="C76" s="53" t="n"/>
+      <c r="D76" s="53" t="n"/>
+      <c r="E76" s="53" t="n"/>
+      <c r="F76" s="53" t="n"/>
+      <c r="G76" s="53" t="n"/>
+      <c r="H76" s="53" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B77" s="53" t="n"/>
+      <c r="C77" s="53" t="n"/>
+      <c r="D77" s="53" t="n"/>
+      <c r="E77" s="53" t="n"/>
+      <c r="F77" s="53" t="n"/>
+      <c r="G77" s="53" t="n"/>
+      <c r="H77" s="53" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B78" s="53" t="n"/>
+      <c r="C78" s="53" t="n"/>
+      <c r="D78" s="53" t="n"/>
+      <c r="E78" s="53" t="n"/>
+      <c r="F78" s="53" t="n"/>
+      <c r="G78" s="53" t="n"/>
+      <c r="H78" s="53" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B79" s="53" t="n"/>
+      <c r="C79" s="53" t="n"/>
+      <c r="D79" s="53" t="n"/>
+      <c r="E79" s="53" t="n"/>
+      <c r="F79" s="53" t="n"/>
+      <c r="G79" s="53" t="n"/>
+      <c r="H79" s="53" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B80" s="53" t="n"/>
+      <c r="C80" s="53" t="n"/>
+      <c r="D80" s="53" t="n"/>
+      <c r="E80" s="53" t="n"/>
+      <c r="F80" s="53" t="n"/>
+      <c r="G80" s="53" t="n"/>
+      <c r="H80" s="53" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B81" s="53" t="n"/>
+      <c r="C81" s="53" t="n"/>
+      <c r="D81" s="53" t="n"/>
+      <c r="E81" s="53" t="n"/>
+      <c r="F81" s="53" t="n"/>
+      <c r="G81" s="53" t="n"/>
+      <c r="H81" s="53" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="B82" s="53" t="n"/>
+      <c r="C82" s="53" t="n"/>
+      <c r="D82" s="53" t="n"/>
+      <c r="E82" s="53" t="n"/>
+      <c r="F82" s="53" t="n"/>
+      <c r="G82" s="53" t="n"/>
+      <c r="H82" s="53" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B83" s="53" t="n"/>
+      <c r="C83" s="53" t="n"/>
+      <c r="D83" s="53" t="n"/>
+      <c r="E83" s="53" t="n"/>
+      <c r="F83" s="53" t="n"/>
+      <c r="G83" s="53" t="n"/>
+      <c r="H83" s="53" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="B84" s="53" t="n"/>
+      <c r="C84" s="53" t="n"/>
+      <c r="D84" s="53" t="n"/>
+      <c r="E84" s="53" t="n"/>
+      <c r="F84" s="53" t="n"/>
+      <c r="G84" s="53" t="n"/>
+      <c r="H84" s="53" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="B85" s="53" t="n"/>
+      <c r="C85" s="53" t="n"/>
+      <c r="D85" s="53" t="n"/>
+      <c r="E85" s="53" t="n"/>
+      <c r="F85" s="53" t="n"/>
+      <c r="G85" s="53" t="n"/>
+      <c r="H85" s="53" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="B86" s="53" t="n"/>
+      <c r="C86" s="53" t="n"/>
+      <c r="D86" s="53" t="n"/>
+      <c r="E86" s="53" t="n"/>
+      <c r="F86" s="53" t="n"/>
+      <c r="G86" s="53" t="n"/>
+      <c r="H86" s="53" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B87" s="53" t="n"/>
+      <c r="C87" s="53" t="n"/>
+      <c r="D87" s="53" t="n"/>
+      <c r="E87" s="53" t="n"/>
+      <c r="F87" s="53" t="n"/>
+      <c r="G87" s="53" t="n"/>
+      <c r="H87" s="53" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="B88" s="53" t="n"/>
+      <c r="C88" s="53" t="n"/>
+      <c r="D88" s="53" t="n"/>
+      <c r="E88" s="53" t="n"/>
+      <c r="F88" s="53" t="n"/>
+      <c r="G88" s="53" t="n"/>
+      <c r="H88" s="53" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="B89" s="53" t="n"/>
+      <c r="C89" s="53" t="n"/>
+      <c r="D89" s="53" t="n"/>
+      <c r="E89" s="53" t="n"/>
+      <c r="F89" s="53" t="n"/>
+      <c r="G89" s="53" t="n"/>
+      <c r="H89" s="53" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B90" s="53" t="n"/>
+      <c r="C90" s="53" t="n"/>
+      <c r="D90" s="53" t="n"/>
+      <c r="E90" s="53" t="n"/>
+      <c r="F90" s="53" t="n"/>
+      <c r="G90" s="53" t="n"/>
+      <c r="H90" s="53" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B91" s="53" t="n"/>
+      <c r="C91" s="53" t="n"/>
+      <c r="D91" s="53" t="n"/>
+      <c r="E91" s="53" t="n"/>
+      <c r="F91" s="53" t="n"/>
+      <c r="G91" s="53" t="n"/>
+      <c r="H91" s="53" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="B92" s="53" t="n"/>
+      <c r="C92" s="53" t="n"/>
+      <c r="D92" s="53" t="n"/>
+      <c r="E92" s="53" t="n"/>
+      <c r="F92" s="53" t="n"/>
+      <c r="G92" s="53" t="n"/>
+      <c r="H92" s="53" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="B93" s="53" t="n"/>
+      <c r="C93" s="53" t="n"/>
+      <c r="D93" s="53" t="n"/>
+      <c r="E93" s="53" t="n"/>
+      <c r="F93" s="53" t="n"/>
+      <c r="G93" s="53" t="n"/>
+      <c r="H93" s="53" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="B94" s="53" t="n"/>
+      <c r="C94" s="53" t="n"/>
+      <c r="D94" s="53" t="n"/>
+      <c r="E94" s="53" t="n"/>
+      <c r="F94" s="53" t="n"/>
+      <c r="G94" s="53" t="n"/>
+      <c r="H94" s="53" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="B95" s="53" t="n"/>
+      <c r="C95" s="53" t="n"/>
+      <c r="D95" s="53" t="n"/>
+      <c r="E95" s="53" t="n"/>
+      <c r="F95" s="53" t="n"/>
+      <c r="G95" s="53" t="n"/>
+      <c r="H95" s="53" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="B96" s="53" t="n"/>
+      <c r="C96" s="53" t="n"/>
+      <c r="D96" s="53" t="n"/>
+      <c r="E96" s="53" t="n"/>
+      <c r="F96" s="53" t="n"/>
+      <c r="G96" s="53" t="n"/>
+      <c r="H96" s="53" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="B50" s="52" t="n"/>
-      <c r="C50" s="52" t="n"/>
-      <c r="D50" s="52" t="n"/>
-      <c r="E50" s="52" t="n"/>
-      <c r="F50" s="52" t="n"/>
-      <c r="G50" s="52" t="n"/>
-      <c r="H50" s="52" t="n"/>
+      <c r="B97" s="53" t="n"/>
+      <c r="C97" s="53" t="n"/>
+      <c r="D97" s="53" t="n"/>
+      <c r="E97" s="53" t="n"/>
+      <c r="F97" s="53" t="n"/>
+      <c r="G97" s="53" t="n"/>
+      <c r="H97" s="53" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>23:45</t>
+        </is>
+      </c>
+      <c r="B98" s="53" t="n"/>
+      <c r="C98" s="53" t="n"/>
+      <c r="D98" s="53" t="n"/>
+      <c r="E98" s="53" t="n"/>
+      <c r="F98" s="53" t="n"/>
+      <c r="G98" s="53" t="n"/>
+      <c r="H98" s="53" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H50"/>
+  <autoFilter ref="A1:H98"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B3:H50" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Shrinkage as a ratio (0.08) or percent (8%). Below 100%." prompt="Shrinkage as a ratio (0.08) or percent (8%). Below 100%." type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="B3:H98" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Shrinkage as a ratio (0.08) or percent (8%). Below 100%." prompt="Shrinkage as a ratio (0.08) or percent (8%). Below 100%." type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>0.9999</formula2>
     </dataValidation>
@@ -12361,6 +11968,757 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:H50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="19" min="1" max="1"/>
+    <col width="12" customWidth="1" style="19" min="2" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" s="19">
+      <c r="A1" s="50" t="inlineStr">
+        <is>
+          <t>FT Wise 30 Min — Full-week requirement input</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="49" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="B2" s="49" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C2" s="49" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D2" s="49" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="E2" s="49" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="F2" s="49" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="G2" s="49" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="H2" s="49" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="B3" s="52" t="n"/>
+      <c r="C3" s="52" t="n"/>
+      <c r="D3" s="52" t="n"/>
+      <c r="E3" s="52" t="n"/>
+      <c r="F3" s="52" t="n"/>
+      <c r="G3" s="52" t="n"/>
+      <c r="H3" s="52" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="B4" s="52" t="n"/>
+      <c r="C4" s="52" t="n"/>
+      <c r="D4" s="52" t="n"/>
+      <c r="E4" s="52" t="n"/>
+      <c r="F4" s="52" t="n"/>
+      <c r="G4" s="52" t="n"/>
+      <c r="H4" s="52" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="B5" s="52" t="n"/>
+      <c r="C5" s="52" t="n"/>
+      <c r="D5" s="52" t="n"/>
+      <c r="E5" s="52" t="n"/>
+      <c r="F5" s="52" t="n"/>
+      <c r="G5" s="52" t="n"/>
+      <c r="H5" s="52" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="B6" s="52" t="n"/>
+      <c r="C6" s="52" t="n"/>
+      <c r="D6" s="52" t="n"/>
+      <c r="E6" s="52" t="n"/>
+      <c r="F6" s="52" t="n"/>
+      <c r="G6" s="52" t="n"/>
+      <c r="H6" s="52" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="B7" s="52" t="n"/>
+      <c r="C7" s="52" t="n"/>
+      <c r="D7" s="52" t="n"/>
+      <c r="E7" s="52" t="n"/>
+      <c r="F7" s="52" t="n"/>
+      <c r="G7" s="52" t="n"/>
+      <c r="H7" s="52" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="B8" s="52" t="n"/>
+      <c r="C8" s="52" t="n"/>
+      <c r="D8" s="52" t="n"/>
+      <c r="E8" s="52" t="n"/>
+      <c r="F8" s="52" t="n"/>
+      <c r="G8" s="52" t="n"/>
+      <c r="H8" s="52" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="B9" s="52" t="n"/>
+      <c r="C9" s="52" t="n"/>
+      <c r="D9" s="52" t="n"/>
+      <c r="E9" s="52" t="n"/>
+      <c r="F9" s="52" t="n"/>
+      <c r="G9" s="52" t="n"/>
+      <c r="H9" s="52" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="B10" s="52" t="n"/>
+      <c r="C10" s="52" t="n"/>
+      <c r="D10" s="52" t="n"/>
+      <c r="E10" s="52" t="n"/>
+      <c r="F10" s="52" t="n"/>
+      <c r="G10" s="52" t="n"/>
+      <c r="H10" s="52" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="B11" s="52" t="n"/>
+      <c r="C11" s="52" t="n"/>
+      <c r="D11" s="52" t="n"/>
+      <c r="E11" s="52" t="n"/>
+      <c r="F11" s="52" t="n"/>
+      <c r="G11" s="52" t="n"/>
+      <c r="H11" s="52" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="B12" s="52" t="n"/>
+      <c r="C12" s="52" t="n"/>
+      <c r="D12" s="52" t="n"/>
+      <c r="E12" s="52" t="n"/>
+      <c r="F12" s="52" t="n"/>
+      <c r="G12" s="52" t="n"/>
+      <c r="H12" s="52" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="B13" s="52" t="n"/>
+      <c r="C13" s="52" t="n"/>
+      <c r="D13" s="52" t="n"/>
+      <c r="E13" s="52" t="n"/>
+      <c r="F13" s="52" t="n"/>
+      <c r="G13" s="52" t="n"/>
+      <c r="H13" s="52" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="B14" s="52" t="n"/>
+      <c r="C14" s="52" t="n"/>
+      <c r="D14" s="52" t="n"/>
+      <c r="E14" s="52" t="n"/>
+      <c r="F14" s="52" t="n"/>
+      <c r="G14" s="52" t="n"/>
+      <c r="H14" s="52" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="B15" s="52" t="n"/>
+      <c r="C15" s="52" t="n"/>
+      <c r="D15" s="52" t="n"/>
+      <c r="E15" s="52" t="n"/>
+      <c r="F15" s="52" t="n"/>
+      <c r="G15" s="52" t="n"/>
+      <c r="H15" s="52" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="B16" s="52" t="n"/>
+      <c r="C16" s="52" t="n"/>
+      <c r="D16" s="52" t="n"/>
+      <c r="E16" s="52" t="n"/>
+      <c r="F16" s="52" t="n"/>
+      <c r="G16" s="52" t="n"/>
+      <c r="H16" s="52" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="B17" s="52" t="n"/>
+      <c r="C17" s="52" t="n"/>
+      <c r="D17" s="52" t="n"/>
+      <c r="E17" s="52" t="n"/>
+      <c r="F17" s="52" t="n"/>
+      <c r="G17" s="52" t="n"/>
+      <c r="H17" s="52" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="B18" s="52" t="n"/>
+      <c r="C18" s="52" t="n"/>
+      <c r="D18" s="52" t="n"/>
+      <c r="E18" s="52" t="n"/>
+      <c r="F18" s="52" t="n"/>
+      <c r="G18" s="52" t="n"/>
+      <c r="H18" s="52" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B19" s="52" t="n"/>
+      <c r="C19" s="52" t="n"/>
+      <c r="D19" s="52" t="n"/>
+      <c r="E19" s="52" t="n"/>
+      <c r="F19" s="52" t="n"/>
+      <c r="G19" s="52" t="n"/>
+      <c r="H19" s="52" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B20" s="52" t="n"/>
+      <c r="C20" s="52" t="n"/>
+      <c r="D20" s="52" t="n"/>
+      <c r="E20" s="52" t="n"/>
+      <c r="F20" s="52" t="n"/>
+      <c r="G20" s="52" t="n"/>
+      <c r="H20" s="52" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B21" s="52" t="n"/>
+      <c r="C21" s="52" t="n"/>
+      <c r="D21" s="52" t="n"/>
+      <c r="E21" s="52" t="n"/>
+      <c r="F21" s="52" t="n"/>
+      <c r="G21" s="52" t="n"/>
+      <c r="H21" s="52" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B22" s="52" t="n"/>
+      <c r="C22" s="52" t="n"/>
+      <c r="D22" s="52" t="n"/>
+      <c r="E22" s="52" t="n"/>
+      <c r="F22" s="52" t="n"/>
+      <c r="G22" s="52" t="n"/>
+      <c r="H22" s="52" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B23" s="52" t="n"/>
+      <c r="C23" s="52" t="n"/>
+      <c r="D23" s="52" t="n"/>
+      <c r="E23" s="52" t="n"/>
+      <c r="F23" s="52" t="n"/>
+      <c r="G23" s="52" t="n"/>
+      <c r="H23" s="52" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="B24" s="52" t="n"/>
+      <c r="C24" s="52" t="n"/>
+      <c r="D24" s="52" t="n"/>
+      <c r="E24" s="52" t="n"/>
+      <c r="F24" s="52" t="n"/>
+      <c r="G24" s="52" t="n"/>
+      <c r="H24" s="52" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B25" s="52" t="n"/>
+      <c r="C25" s="52" t="n"/>
+      <c r="D25" s="52" t="n"/>
+      <c r="E25" s="52" t="n"/>
+      <c r="F25" s="52" t="n"/>
+      <c r="G25" s="52" t="n"/>
+      <c r="H25" s="52" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B26" s="52" t="n"/>
+      <c r="C26" s="52" t="n"/>
+      <c r="D26" s="52" t="n"/>
+      <c r="E26" s="52" t="n"/>
+      <c r="F26" s="52" t="n"/>
+      <c r="G26" s="52" t="n"/>
+      <c r="H26" s="52" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B27" s="52" t="n"/>
+      <c r="C27" s="52" t="n"/>
+      <c r="D27" s="52" t="n"/>
+      <c r="E27" s="52" t="n"/>
+      <c r="F27" s="52" t="n"/>
+      <c r="G27" s="52" t="n"/>
+      <c r="H27" s="52" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B28" s="52" t="n"/>
+      <c r="C28" s="52" t="n"/>
+      <c r="D28" s="52" t="n"/>
+      <c r="E28" s="52" t="n"/>
+      <c r="F28" s="52" t="n"/>
+      <c r="G28" s="52" t="n"/>
+      <c r="H28" s="52" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="B29" s="52" t="n"/>
+      <c r="C29" s="52" t="n"/>
+      <c r="D29" s="52" t="n"/>
+      <c r="E29" s="52" t="n"/>
+      <c r="F29" s="52" t="n"/>
+      <c r="G29" s="52" t="n"/>
+      <c r="H29" s="52" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="B30" s="52" t="n"/>
+      <c r="C30" s="52" t="n"/>
+      <c r="D30" s="52" t="n"/>
+      <c r="E30" s="52" t="n"/>
+      <c r="F30" s="52" t="n"/>
+      <c r="G30" s="52" t="n"/>
+      <c r="H30" s="52" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="B31" s="52" t="n"/>
+      <c r="C31" s="52" t="n"/>
+      <c r="D31" s="52" t="n"/>
+      <c r="E31" s="52" t="n"/>
+      <c r="F31" s="52" t="n"/>
+      <c r="G31" s="52" t="n"/>
+      <c r="H31" s="52" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+      <c r="E32" s="52" t="n"/>
+      <c r="F32" s="52" t="n"/>
+      <c r="G32" s="52" t="n"/>
+      <c r="H32" s="52" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+      <c r="E33" s="52" t="n"/>
+      <c r="F33" s="52" t="n"/>
+      <c r="G33" s="52" t="n"/>
+      <c r="H33" s="52" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+      <c r="E34" s="52" t="n"/>
+      <c r="F34" s="52" t="n"/>
+      <c r="G34" s="52" t="n"/>
+      <c r="H34" s="52" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+      <c r="E35" s="52" t="n"/>
+      <c r="F35" s="52" t="n"/>
+      <c r="G35" s="52" t="n"/>
+      <c r="H35" s="52" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+      <c r="E36" s="52" t="n"/>
+      <c r="F36" s="52" t="n"/>
+      <c r="G36" s="52" t="n"/>
+      <c r="H36" s="52" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+      <c r="E37" s="52" t="n"/>
+      <c r="F37" s="52" t="n"/>
+      <c r="G37" s="52" t="n"/>
+      <c r="H37" s="52" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B38" s="52" t="n"/>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+      <c r="E38" s="52" t="n"/>
+      <c r="F38" s="52" t="n"/>
+      <c r="G38" s="52" t="n"/>
+      <c r="H38" s="52" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+      <c r="E39" s="52" t="n"/>
+      <c r="F39" s="52" t="n"/>
+      <c r="G39" s="52" t="n"/>
+      <c r="H39" s="52" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B40" s="52" t="n"/>
+      <c r="C40" s="52" t="n"/>
+      <c r="D40" s="52" t="n"/>
+      <c r="E40" s="52" t="n"/>
+      <c r="F40" s="52" t="n"/>
+      <c r="G40" s="52" t="n"/>
+      <c r="H40" s="52" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B41" s="52" t="n"/>
+      <c r="C41" s="52" t="n"/>
+      <c r="D41" s="52" t="n"/>
+      <c r="E41" s="52" t="n"/>
+      <c r="F41" s="52" t="n"/>
+      <c r="G41" s="52" t="n"/>
+      <c r="H41" s="52" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B42" s="52" t="n"/>
+      <c r="C42" s="52" t="n"/>
+      <c r="D42" s="52" t="n"/>
+      <c r="E42" s="52" t="n"/>
+      <c r="F42" s="52" t="n"/>
+      <c r="G42" s="52" t="n"/>
+      <c r="H42" s="52" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B43" s="52" t="n"/>
+      <c r="C43" s="52" t="n"/>
+      <c r="D43" s="52" t="n"/>
+      <c r="E43" s="52" t="n"/>
+      <c r="F43" s="52" t="n"/>
+      <c r="G43" s="52" t="n"/>
+      <c r="H43" s="52" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="B44" s="52" t="n"/>
+      <c r="C44" s="52" t="n"/>
+      <c r="D44" s="52" t="n"/>
+      <c r="E44" s="52" t="n"/>
+      <c r="F44" s="52" t="n"/>
+      <c r="G44" s="52" t="n"/>
+      <c r="H44" s="52" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B45" s="52" t="n"/>
+      <c r="C45" s="52" t="n"/>
+      <c r="D45" s="52" t="n"/>
+      <c r="E45" s="52" t="n"/>
+      <c r="F45" s="52" t="n"/>
+      <c r="G45" s="52" t="n"/>
+      <c r="H45" s="52" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="B46" s="52" t="n"/>
+      <c r="C46" s="52" t="n"/>
+      <c r="D46" s="52" t="n"/>
+      <c r="E46" s="52" t="n"/>
+      <c r="F46" s="52" t="n"/>
+      <c r="G46" s="52" t="n"/>
+      <c r="H46" s="52" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B47" s="52" t="n"/>
+      <c r="C47" s="52" t="n"/>
+      <c r="D47" s="52" t="n"/>
+      <c r="E47" s="52" t="n"/>
+      <c r="F47" s="52" t="n"/>
+      <c r="G47" s="52" t="n"/>
+      <c r="H47" s="52" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="B48" s="52" t="n"/>
+      <c r="C48" s="52" t="n"/>
+      <c r="D48" s="52" t="n"/>
+      <c r="E48" s="52" t="n"/>
+      <c r="F48" s="52" t="n"/>
+      <c r="G48" s="52" t="n"/>
+      <c r="H48" s="52" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="B49" s="52" t="n"/>
+      <c r="C49" s="52" t="n"/>
+      <c r="D49" s="52" t="n"/>
+      <c r="E49" s="52" t="n"/>
+      <c r="F49" s="52" t="n"/>
+      <c r="G49" s="52" t="n"/>
+      <c r="H49" s="52" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="B50" s="52" t="n"/>
+      <c r="C50" s="52" t="n"/>
+      <c r="D50" s="52" t="n"/>
+      <c r="E50" s="52" t="n"/>
+      <c r="F50" s="52" t="n"/>
+      <c r="G50" s="52" t="n"/>
+      <c r="H50" s="52" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H50"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B3:H50" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Required FTE for this interval. 0 or more; blank = no demand." prompt="Required FTE for this interval. 0 or more; blank = no demand." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>100000</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -12423,25 +12781,25 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="B3" s="52" t="n">
+      <c r="B3" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="C3" s="52" t="n">
+      <c r="C3" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="D3" s="52" t="n">
+      <c r="D3" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="E3" s="52" t="n">
+      <c r="E3" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="F3" s="52" t="n">
+      <c r="F3" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="G3" s="52" t="n">
+      <c r="G3" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="H3" s="52" t="n">
+      <c r="H3" s="53" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -12451,25 +12809,25 @@
           <t>01:00</t>
         </is>
       </c>
-      <c r="B4" s="52" t="n">
+      <c r="B4" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="C4" s="52" t="n">
+      <c r="C4" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="D4" s="52" t="n">
+      <c r="D4" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="E4" s="52" t="n">
+      <c r="E4" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="F4" s="52" t="n">
+      <c r="F4" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="G4" s="52" t="n">
+      <c r="G4" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="H4" s="52" t="n">
+      <c r="H4" s="53" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -12479,25 +12837,25 @@
           <t>02:00</t>
         </is>
       </c>
-      <c r="B5" s="52" t="n">
+      <c r="B5" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="C5" s="52" t="n">
+      <c r="C5" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="D5" s="52" t="n">
+      <c r="D5" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="E5" s="52" t="n">
+      <c r="E5" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="F5" s="52" t="n">
+      <c r="F5" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="G5" s="52" t="n">
+      <c r="G5" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="H5" s="52" t="n">
+      <c r="H5" s="53" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -12507,25 +12865,25 @@
           <t>03:00</t>
         </is>
       </c>
-      <c r="B6" s="52" t="n">
+      <c r="B6" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="C6" s="52" t="n">
+      <c r="C6" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="D6" s="52" t="n">
+      <c r="D6" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="E6" s="52" t="n">
+      <c r="E6" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="F6" s="52" t="n">
+      <c r="F6" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="G6" s="52" t="n">
+      <c r="G6" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="H6" s="52" t="n">
+      <c r="H6" s="53" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -12535,21 +12893,21 @@
           <t>04:00</t>
         </is>
       </c>
-      <c r="B7" s="52" t="n"/>
-      <c r="C7" s="52" t="n"/>
-      <c r="D7" s="52" t="n">
+      <c r="B7" s="53" t="n"/>
+      <c r="C7" s="53" t="n"/>
+      <c r="D7" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="E7" s="52" t="n">
+      <c r="E7" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="F7" s="52" t="n">
+      <c r="F7" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="G7" s="52" t="n">
+      <c r="G7" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="H7" s="52" t="n">
+      <c r="H7" s="53" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -12559,21 +12917,21 @@
           <t>05:00</t>
         </is>
       </c>
-      <c r="B8" s="52" t="n"/>
-      <c r="C8" s="52" t="n"/>
-      <c r="D8" s="52" t="n">
+      <c r="B8" s="53" t="n"/>
+      <c r="C8" s="53" t="n"/>
+      <c r="D8" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="E8" s="52" t="n">
+      <c r="E8" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="F8" s="52" t="n">
+      <c r="F8" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="G8" s="52" t="n">
+      <c r="G8" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="H8" s="52" t="n">
+      <c r="H8" s="53" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -12583,21 +12941,21 @@
           <t>06:00</t>
         </is>
       </c>
-      <c r="B9" s="52" t="n"/>
-      <c r="C9" s="52" t="n"/>
-      <c r="D9" s="52" t="n">
+      <c r="B9" s="53" t="n"/>
+      <c r="C9" s="53" t="n"/>
+      <c r="D9" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="E9" s="52" t="n">
+      <c r="E9" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="F9" s="52" t="n">
+      <c r="F9" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="G9" s="52" t="n">
+      <c r="G9" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="H9" s="52" t="n">
+      <c r="H9" s="53" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -12607,13 +12965,13 @@
           <t>07:00</t>
         </is>
       </c>
-      <c r="B10" s="52" t="n"/>
-      <c r="C10" s="52" t="n"/>
-      <c r="D10" s="52" t="n"/>
-      <c r="E10" s="52" t="n"/>
-      <c r="F10" s="52" t="n"/>
-      <c r="G10" s="52" t="n"/>
-      <c r="H10" s="52" t="n"/>
+      <c r="B10" s="53" t="n"/>
+      <c r="C10" s="53" t="n"/>
+      <c r="D10" s="53" t="n"/>
+      <c r="E10" s="53" t="n"/>
+      <c r="F10" s="53" t="n"/>
+      <c r="G10" s="53" t="n"/>
+      <c r="H10" s="53" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -12621,13 +12979,13 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B11" s="52" t="n"/>
-      <c r="C11" s="52" t="n"/>
-      <c r="D11" s="52" t="n"/>
-      <c r="E11" s="52" t="n"/>
-      <c r="F11" s="52" t="n"/>
-      <c r="G11" s="52" t="n"/>
-      <c r="H11" s="52" t="n"/>
+      <c r="B11" s="53" t="n"/>
+      <c r="C11" s="53" t="n"/>
+      <c r="D11" s="53" t="n"/>
+      <c r="E11" s="53" t="n"/>
+      <c r="F11" s="53" t="n"/>
+      <c r="G11" s="53" t="n"/>
+      <c r="H11" s="53" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -12635,13 +12993,13 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B12" s="52" t="n"/>
-      <c r="C12" s="52" t="n"/>
-      <c r="D12" s="52" t="n"/>
-      <c r="E12" s="52" t="n"/>
-      <c r="F12" s="52" t="n"/>
-      <c r="G12" s="52" t="n"/>
-      <c r="H12" s="52" t="n"/>
+      <c r="B12" s="53" t="n"/>
+      <c r="C12" s="53" t="n"/>
+      <c r="D12" s="53" t="n"/>
+      <c r="E12" s="53" t="n"/>
+      <c r="F12" s="53" t="n"/>
+      <c r="G12" s="53" t="n"/>
+      <c r="H12" s="53" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -12649,13 +13007,13 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B13" s="52" t="n"/>
-      <c r="C13" s="52" t="n"/>
-      <c r="D13" s="52" t="n"/>
-      <c r="E13" s="52" t="n"/>
-      <c r="F13" s="52" t="n"/>
-      <c r="G13" s="52" t="n"/>
-      <c r="H13" s="52" t="n"/>
+      <c r="B13" s="53" t="n"/>
+      <c r="C13" s="53" t="n"/>
+      <c r="D13" s="53" t="n"/>
+      <c r="E13" s="53" t="n"/>
+      <c r="F13" s="53" t="n"/>
+      <c r="G13" s="53" t="n"/>
+      <c r="H13" s="53" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -12663,13 +13021,13 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B14" s="52" t="n"/>
-      <c r="C14" s="52" t="n"/>
-      <c r="D14" s="52" t="n"/>
-      <c r="E14" s="52" t="n"/>
-      <c r="F14" s="52" t="n"/>
-      <c r="G14" s="52" t="n"/>
-      <c r="H14" s="52" t="n"/>
+      <c r="B14" s="53" t="n"/>
+      <c r="C14" s="53" t="n"/>
+      <c r="D14" s="53" t="n"/>
+      <c r="E14" s="53" t="n"/>
+      <c r="F14" s="53" t="n"/>
+      <c r="G14" s="53" t="n"/>
+      <c r="H14" s="53" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -12677,13 +13035,13 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="B15" s="52" t="n"/>
-      <c r="C15" s="52" t="n"/>
-      <c r="D15" s="52" t="n"/>
-      <c r="E15" s="52" t="n"/>
-      <c r="F15" s="52" t="n"/>
-      <c r="G15" s="52" t="n"/>
-      <c r="H15" s="52" t="n"/>
+      <c r="B15" s="53" t="n"/>
+      <c r="C15" s="53" t="n"/>
+      <c r="D15" s="53" t="n"/>
+      <c r="E15" s="53" t="n"/>
+      <c r="F15" s="53" t="n"/>
+      <c r="G15" s="53" t="n"/>
+      <c r="H15" s="53" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -12691,13 +13049,13 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="B16" s="52" t="n"/>
-      <c r="C16" s="52" t="n"/>
-      <c r="D16" s="52" t="n"/>
-      <c r="E16" s="52" t="n"/>
-      <c r="F16" s="52" t="n"/>
-      <c r="G16" s="52" t="n"/>
-      <c r="H16" s="52" t="n"/>
+      <c r="B16" s="53" t="n"/>
+      <c r="C16" s="53" t="n"/>
+      <c r="D16" s="53" t="n"/>
+      <c r="E16" s="53" t="n"/>
+      <c r="F16" s="53" t="n"/>
+      <c r="G16" s="53" t="n"/>
+      <c r="H16" s="53" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -12705,13 +13063,13 @@
           <t>14:00</t>
         </is>
       </c>
-      <c r="B17" s="52" t="n"/>
-      <c r="C17" s="52" t="n"/>
-      <c r="D17" s="52" t="n"/>
-      <c r="E17" s="52" t="n"/>
-      <c r="F17" s="52" t="n"/>
-      <c r="G17" s="52" t="n"/>
-      <c r="H17" s="52" t="n"/>
+      <c r="B17" s="53" t="n"/>
+      <c r="C17" s="53" t="n"/>
+      <c r="D17" s="53" t="n"/>
+      <c r="E17" s="53" t="n"/>
+      <c r="F17" s="53" t="n"/>
+      <c r="G17" s="53" t="n"/>
+      <c r="H17" s="53" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -12719,13 +13077,13 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="B18" s="52" t="n"/>
-      <c r="C18" s="52" t="n"/>
-      <c r="D18" s="52" t="n"/>
-      <c r="E18" s="52" t="n"/>
-      <c r="F18" s="52" t="n"/>
-      <c r="G18" s="52" t="n"/>
-      <c r="H18" s="52" t="n"/>
+      <c r="B18" s="53" t="n"/>
+      <c r="C18" s="53" t="n"/>
+      <c r="D18" s="53" t="n"/>
+      <c r="E18" s="53" t="n"/>
+      <c r="F18" s="53" t="n"/>
+      <c r="G18" s="53" t="n"/>
+      <c r="H18" s="53" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -12733,25 +13091,25 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B19" s="52" t="n">
+      <c r="B19" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="C19" s="52" t="n">
+      <c r="C19" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="D19" s="52" t="n">
+      <c r="D19" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="E19" s="52" t="n">
+      <c r="E19" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="F19" s="52" t="n">
+      <c r="F19" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="G19" s="52" t="n">
+      <c r="G19" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="H19" s="52" t="n">
+      <c r="H19" s="53" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -12761,25 +13119,25 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="B20" s="52" t="n">
+      <c r="B20" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="C20" s="52" t="n">
+      <c r="C20" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="D20" s="52" t="n">
+      <c r="D20" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="E20" s="52" t="n">
+      <c r="E20" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="F20" s="52" t="n">
+      <c r="F20" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="G20" s="52" t="n">
+      <c r="G20" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="H20" s="52" t="n">
+      <c r="H20" s="53" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -12789,25 +13147,25 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B21" s="52" t="n">
+      <c r="B21" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="C21" s="52" t="n">
+      <c r="C21" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="D21" s="52" t="n">
+      <c r="D21" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="E21" s="52" t="n">
+      <c r="E21" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="F21" s="52" t="n">
+      <c r="F21" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="G21" s="52" t="n">
+      <c r="G21" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="H21" s="52" t="n">
+      <c r="H21" s="53" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -12817,25 +13175,25 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="B22" s="52" t="n">
+      <c r="B22" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="C22" s="52" t="n">
+      <c r="C22" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="D22" s="52" t="n">
+      <c r="D22" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="E22" s="52" t="n">
+      <c r="E22" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="F22" s="52" t="n">
+      <c r="F22" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="G22" s="52" t="n">
+      <c r="G22" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="H22" s="52" t="n">
+      <c r="H22" s="53" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -12845,25 +13203,25 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="B23" s="52" t="n">
+      <c r="B23" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="C23" s="52" t="n">
+      <c r="C23" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="D23" s="52" t="n">
+      <c r="D23" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="E23" s="52" t="n">
+      <c r="E23" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="F23" s="52" t="n">
+      <c r="F23" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="G23" s="52" t="n">
+      <c r="G23" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="H23" s="52" t="n">
+      <c r="H23" s="53" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -12873,25 +13231,25 @@
           <t>21:00</t>
         </is>
       </c>
-      <c r="B24" s="52" t="n">
+      <c r="B24" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="C24" s="52" t="n">
+      <c r="C24" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="D24" s="52" t="n">
+      <c r="D24" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="E24" s="52" t="n">
+      <c r="E24" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="F24" s="52" t="n">
+      <c r="F24" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="G24" s="52" t="n">
+      <c r="G24" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="H24" s="52" t="n">
+      <c r="H24" s="53" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -12901,25 +13259,25 @@
           <t>22:00</t>
         </is>
       </c>
-      <c r="B25" s="52" t="n">
+      <c r="B25" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="C25" s="52" t="n">
+      <c r="C25" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="D25" s="52" t="n">
+      <c r="D25" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="E25" s="52" t="n">
+      <c r="E25" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="F25" s="52" t="n">
+      <c r="F25" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="G25" s="52" t="n">
+      <c r="G25" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="H25" s="52" t="n">
+      <c r="H25" s="53" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -12929,25 +13287,25 @@
           <t>23:00</t>
         </is>
       </c>
-      <c r="B26" s="52" t="n">
+      <c r="B26" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="C26" s="52" t="n">
+      <c r="C26" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="D26" s="52" t="n">
+      <c r="D26" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="E26" s="52" t="n">
+      <c r="E26" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="F26" s="52" t="n">
+      <c r="F26" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="G26" s="52" t="n">
+      <c r="G26" s="53" t="n">
         <v>0.12</v>
       </c>
-      <c r="H26" s="52" t="n">
+      <c r="H26" s="53" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -12967,7 +13325,758 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="19" min="1" max="1"/>
+    <col width="12" customWidth="1" style="19" min="2" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" s="19">
+      <c r="A1" s="50" t="inlineStr">
+        <is>
+          <t>Shrinkage 30 Min — Matching shrinkage grid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="49" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="B2" s="49" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C2" s="49" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D2" s="49" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="E2" s="49" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="F2" s="49" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="G2" s="49" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="H2" s="49" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="B3" s="53" t="n"/>
+      <c r="C3" s="53" t="n"/>
+      <c r="D3" s="53" t="n"/>
+      <c r="E3" s="53" t="n"/>
+      <c r="F3" s="53" t="n"/>
+      <c r="G3" s="53" t="n"/>
+      <c r="H3" s="53" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="B4" s="53" t="n"/>
+      <c r="C4" s="53" t="n"/>
+      <c r="D4" s="53" t="n"/>
+      <c r="E4" s="53" t="n"/>
+      <c r="F4" s="53" t="n"/>
+      <c r="G4" s="53" t="n"/>
+      <c r="H4" s="53" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="B5" s="53" t="n"/>
+      <c r="C5" s="53" t="n"/>
+      <c r="D5" s="53" t="n"/>
+      <c r="E5" s="53" t="n"/>
+      <c r="F5" s="53" t="n"/>
+      <c r="G5" s="53" t="n"/>
+      <c r="H5" s="53" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="B6" s="53" t="n"/>
+      <c r="C6" s="53" t="n"/>
+      <c r="D6" s="53" t="n"/>
+      <c r="E6" s="53" t="n"/>
+      <c r="F6" s="53" t="n"/>
+      <c r="G6" s="53" t="n"/>
+      <c r="H6" s="53" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="B7" s="53" t="n"/>
+      <c r="C7" s="53" t="n"/>
+      <c r="D7" s="53" t="n"/>
+      <c r="E7" s="53" t="n"/>
+      <c r="F7" s="53" t="n"/>
+      <c r="G7" s="53" t="n"/>
+      <c r="H7" s="53" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="B8" s="53" t="n"/>
+      <c r="C8" s="53" t="n"/>
+      <c r="D8" s="53" t="n"/>
+      <c r="E8" s="53" t="n"/>
+      <c r="F8" s="53" t="n"/>
+      <c r="G8" s="53" t="n"/>
+      <c r="H8" s="53" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="B9" s="53" t="n"/>
+      <c r="C9" s="53" t="n"/>
+      <c r="D9" s="53" t="n"/>
+      <c r="E9" s="53" t="n"/>
+      <c r="F9" s="53" t="n"/>
+      <c r="G9" s="53" t="n"/>
+      <c r="H9" s="53" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="B10" s="53" t="n"/>
+      <c r="C10" s="53" t="n"/>
+      <c r="D10" s="53" t="n"/>
+      <c r="E10" s="53" t="n"/>
+      <c r="F10" s="53" t="n"/>
+      <c r="G10" s="53" t="n"/>
+      <c r="H10" s="53" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="B11" s="53" t="n"/>
+      <c r="C11" s="53" t="n"/>
+      <c r="D11" s="53" t="n"/>
+      <c r="E11" s="53" t="n"/>
+      <c r="F11" s="53" t="n"/>
+      <c r="G11" s="53" t="n"/>
+      <c r="H11" s="53" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="B12" s="53" t="n"/>
+      <c r="C12" s="53" t="n"/>
+      <c r="D12" s="53" t="n"/>
+      <c r="E12" s="53" t="n"/>
+      <c r="F12" s="53" t="n"/>
+      <c r="G12" s="53" t="n"/>
+      <c r="H12" s="53" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="B13" s="53" t="n"/>
+      <c r="C13" s="53" t="n"/>
+      <c r="D13" s="53" t="n"/>
+      <c r="E13" s="53" t="n"/>
+      <c r="F13" s="53" t="n"/>
+      <c r="G13" s="53" t="n"/>
+      <c r="H13" s="53" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="B14" s="53" t="n"/>
+      <c r="C14" s="53" t="n"/>
+      <c r="D14" s="53" t="n"/>
+      <c r="E14" s="53" t="n"/>
+      <c r="F14" s="53" t="n"/>
+      <c r="G14" s="53" t="n"/>
+      <c r="H14" s="53" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="B15" s="53" t="n"/>
+      <c r="C15" s="53" t="n"/>
+      <c r="D15" s="53" t="n"/>
+      <c r="E15" s="53" t="n"/>
+      <c r="F15" s="53" t="n"/>
+      <c r="G15" s="53" t="n"/>
+      <c r="H15" s="53" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="B16" s="53" t="n"/>
+      <c r="C16" s="53" t="n"/>
+      <c r="D16" s="53" t="n"/>
+      <c r="E16" s="53" t="n"/>
+      <c r="F16" s="53" t="n"/>
+      <c r="G16" s="53" t="n"/>
+      <c r="H16" s="53" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="B17" s="53" t="n"/>
+      <c r="C17" s="53" t="n"/>
+      <c r="D17" s="53" t="n"/>
+      <c r="E17" s="53" t="n"/>
+      <c r="F17" s="53" t="n"/>
+      <c r="G17" s="53" t="n"/>
+      <c r="H17" s="53" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="B18" s="53" t="n"/>
+      <c r="C18" s="53" t="n"/>
+      <c r="D18" s="53" t="n"/>
+      <c r="E18" s="53" t="n"/>
+      <c r="F18" s="53" t="n"/>
+      <c r="G18" s="53" t="n"/>
+      <c r="H18" s="53" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B19" s="53" t="n"/>
+      <c r="C19" s="53" t="n"/>
+      <c r="D19" s="53" t="n"/>
+      <c r="E19" s="53" t="n"/>
+      <c r="F19" s="53" t="n"/>
+      <c r="G19" s="53" t="n"/>
+      <c r="H19" s="53" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B20" s="53" t="n"/>
+      <c r="C20" s="53" t="n"/>
+      <c r="D20" s="53" t="n"/>
+      <c r="E20" s="53" t="n"/>
+      <c r="F20" s="53" t="n"/>
+      <c r="G20" s="53" t="n"/>
+      <c r="H20" s="53" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B21" s="53" t="n"/>
+      <c r="C21" s="53" t="n"/>
+      <c r="D21" s="53" t="n"/>
+      <c r="E21" s="53" t="n"/>
+      <c r="F21" s="53" t="n"/>
+      <c r="G21" s="53" t="n"/>
+      <c r="H21" s="53" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B22" s="53" t="n"/>
+      <c r="C22" s="53" t="n"/>
+      <c r="D22" s="53" t="n"/>
+      <c r="E22" s="53" t="n"/>
+      <c r="F22" s="53" t="n"/>
+      <c r="G22" s="53" t="n"/>
+      <c r="H22" s="53" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B23" s="53" t="n"/>
+      <c r="C23" s="53" t="n"/>
+      <c r="D23" s="53" t="n"/>
+      <c r="E23" s="53" t="n"/>
+      <c r="F23" s="53" t="n"/>
+      <c r="G23" s="53" t="n"/>
+      <c r="H23" s="53" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="B24" s="53" t="n"/>
+      <c r="C24" s="53" t="n"/>
+      <c r="D24" s="53" t="n"/>
+      <c r="E24" s="53" t="n"/>
+      <c r="F24" s="53" t="n"/>
+      <c r="G24" s="53" t="n"/>
+      <c r="H24" s="53" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B25" s="53" t="n"/>
+      <c r="C25" s="53" t="n"/>
+      <c r="D25" s="53" t="n"/>
+      <c r="E25" s="53" t="n"/>
+      <c r="F25" s="53" t="n"/>
+      <c r="G25" s="53" t="n"/>
+      <c r="H25" s="53" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B26" s="53" t="n"/>
+      <c r="C26" s="53" t="n"/>
+      <c r="D26" s="53" t="n"/>
+      <c r="E26" s="53" t="n"/>
+      <c r="F26" s="53" t="n"/>
+      <c r="G26" s="53" t="n"/>
+      <c r="H26" s="53" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B27" s="53" t="n"/>
+      <c r="C27" s="53" t="n"/>
+      <c r="D27" s="53" t="n"/>
+      <c r="E27" s="53" t="n"/>
+      <c r="F27" s="53" t="n"/>
+      <c r="G27" s="53" t="n"/>
+      <c r="H27" s="53" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B28" s="53" t="n"/>
+      <c r="C28" s="53" t="n"/>
+      <c r="D28" s="53" t="n"/>
+      <c r="E28" s="53" t="n"/>
+      <c r="F28" s="53" t="n"/>
+      <c r="G28" s="53" t="n"/>
+      <c r="H28" s="53" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="B29" s="53" t="n"/>
+      <c r="C29" s="53" t="n"/>
+      <c r="D29" s="53" t="n"/>
+      <c r="E29" s="53" t="n"/>
+      <c r="F29" s="53" t="n"/>
+      <c r="G29" s="53" t="n"/>
+      <c r="H29" s="53" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="B30" s="53" t="n"/>
+      <c r="C30" s="53" t="n"/>
+      <c r="D30" s="53" t="n"/>
+      <c r="E30" s="53" t="n"/>
+      <c r="F30" s="53" t="n"/>
+      <c r="G30" s="53" t="n"/>
+      <c r="H30" s="53" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="B31" s="53" t="n"/>
+      <c r="C31" s="53" t="n"/>
+      <c r="D31" s="53" t="n"/>
+      <c r="E31" s="53" t="n"/>
+      <c r="F31" s="53" t="n"/>
+      <c r="G31" s="53" t="n"/>
+      <c r="H31" s="53" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="B32" s="53" t="n"/>
+      <c r="C32" s="53" t="n"/>
+      <c r="D32" s="53" t="n"/>
+      <c r="E32" s="53" t="n"/>
+      <c r="F32" s="53" t="n"/>
+      <c r="G32" s="53" t="n"/>
+      <c r="H32" s="53" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="B33" s="53" t="n"/>
+      <c r="C33" s="53" t="n"/>
+      <c r="D33" s="53" t="n"/>
+      <c r="E33" s="53" t="n"/>
+      <c r="F33" s="53" t="n"/>
+      <c r="G33" s="53" t="n"/>
+      <c r="H33" s="53" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="B34" s="53" t="n"/>
+      <c r="C34" s="53" t="n"/>
+      <c r="D34" s="53" t="n"/>
+      <c r="E34" s="53" t="n"/>
+      <c r="F34" s="53" t="n"/>
+      <c r="G34" s="53" t="n"/>
+      <c r="H34" s="53" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B35" s="53" t="n"/>
+      <c r="C35" s="53" t="n"/>
+      <c r="D35" s="53" t="n"/>
+      <c r="E35" s="53" t="n"/>
+      <c r="F35" s="53" t="n"/>
+      <c r="G35" s="53" t="n"/>
+      <c r="H35" s="53" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B36" s="53" t="n"/>
+      <c r="C36" s="53" t="n"/>
+      <c r="D36" s="53" t="n"/>
+      <c r="E36" s="53" t="n"/>
+      <c r="F36" s="53" t="n"/>
+      <c r="G36" s="53" t="n"/>
+      <c r="H36" s="53" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B37" s="53" t="n"/>
+      <c r="C37" s="53" t="n"/>
+      <c r="D37" s="53" t="n"/>
+      <c r="E37" s="53" t="n"/>
+      <c r="F37" s="53" t="n"/>
+      <c r="G37" s="53" t="n"/>
+      <c r="H37" s="53" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B38" s="53" t="n"/>
+      <c r="C38" s="53" t="n"/>
+      <c r="D38" s="53" t="n"/>
+      <c r="E38" s="53" t="n"/>
+      <c r="F38" s="53" t="n"/>
+      <c r="G38" s="53" t="n"/>
+      <c r="H38" s="53" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B39" s="53" t="n"/>
+      <c r="C39" s="53" t="n"/>
+      <c r="D39" s="53" t="n"/>
+      <c r="E39" s="53" t="n"/>
+      <c r="F39" s="53" t="n"/>
+      <c r="G39" s="53" t="n"/>
+      <c r="H39" s="53" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B40" s="53" t="n"/>
+      <c r="C40" s="53" t="n"/>
+      <c r="D40" s="53" t="n"/>
+      <c r="E40" s="53" t="n"/>
+      <c r="F40" s="53" t="n"/>
+      <c r="G40" s="53" t="n"/>
+      <c r="H40" s="53" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B41" s="53" t="n"/>
+      <c r="C41" s="53" t="n"/>
+      <c r="D41" s="53" t="n"/>
+      <c r="E41" s="53" t="n"/>
+      <c r="F41" s="53" t="n"/>
+      <c r="G41" s="53" t="n"/>
+      <c r="H41" s="53" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B42" s="53" t="n"/>
+      <c r="C42" s="53" t="n"/>
+      <c r="D42" s="53" t="n"/>
+      <c r="E42" s="53" t="n"/>
+      <c r="F42" s="53" t="n"/>
+      <c r="G42" s="53" t="n"/>
+      <c r="H42" s="53" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B43" s="53" t="n"/>
+      <c r="C43" s="53" t="n"/>
+      <c r="D43" s="53" t="n"/>
+      <c r="E43" s="53" t="n"/>
+      <c r="F43" s="53" t="n"/>
+      <c r="G43" s="53" t="n"/>
+      <c r="H43" s="53" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="B44" s="53" t="n"/>
+      <c r="C44" s="53" t="n"/>
+      <c r="D44" s="53" t="n"/>
+      <c r="E44" s="53" t="n"/>
+      <c r="F44" s="53" t="n"/>
+      <c r="G44" s="53" t="n"/>
+      <c r="H44" s="53" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="53" t="n"/>
+      <c r="D45" s="53" t="n"/>
+      <c r="E45" s="53" t="n"/>
+      <c r="F45" s="53" t="n"/>
+      <c r="G45" s="53" t="n"/>
+      <c r="H45" s="53" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="B46" s="53" t="n"/>
+      <c r="C46" s="53" t="n"/>
+      <c r="D46" s="53" t="n"/>
+      <c r="E46" s="53" t="n"/>
+      <c r="F46" s="53" t="n"/>
+      <c r="G46" s="53" t="n"/>
+      <c r="H46" s="53" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B47" s="53" t="n"/>
+      <c r="C47" s="53" t="n"/>
+      <c r="D47" s="53" t="n"/>
+      <c r="E47" s="53" t="n"/>
+      <c r="F47" s="53" t="n"/>
+      <c r="G47" s="53" t="n"/>
+      <c r="H47" s="53" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="B48" s="53" t="n"/>
+      <c r="C48" s="53" t="n"/>
+      <c r="D48" s="53" t="n"/>
+      <c r="E48" s="53" t="n"/>
+      <c r="F48" s="53" t="n"/>
+      <c r="G48" s="53" t="n"/>
+      <c r="H48" s="53" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="B49" s="53" t="n"/>
+      <c r="C49" s="53" t="n"/>
+      <c r="D49" s="53" t="n"/>
+      <c r="E49" s="53" t="n"/>
+      <c r="F49" s="53" t="n"/>
+      <c r="G49" s="53" t="n"/>
+      <c r="H49" s="53" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="B50" s="53" t="n"/>
+      <c r="C50" s="53" t="n"/>
+      <c r="D50" s="53" t="n"/>
+      <c r="E50" s="53" t="n"/>
+      <c r="F50" s="53" t="n"/>
+      <c r="G50" s="53" t="n"/>
+      <c r="H50" s="53" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H50"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B3:H50" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Shrinkage as a ratio (0.08) or percent (8%). Below 100%." prompt="Shrinkage as a ratio (0.08) or percent (8%). Below 100%." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>0.9999</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00ED7D31"/>
@@ -13043,339 +14152,339 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="53" t="n"/>
+      <c r="A3" s="54" t="n"/>
       <c r="B3" s="4" t="n"/>
-      <c r="C3" s="53" t="n"/>
-      <c r="D3" s="53" t="n"/>
-      <c r="E3" s="53" t="n"/>
-      <c r="F3" s="53" t="n"/>
-      <c r="G3" s="53" t="n"/>
-      <c r="H3" s="53" t="n"/>
-      <c r="I3" s="53" t="n"/>
+      <c r="C3" s="54" t="n"/>
+      <c r="D3" s="54" t="n"/>
+      <c r="E3" s="54" t="n"/>
+      <c r="F3" s="54" t="n"/>
+      <c r="G3" s="54" t="n"/>
+      <c r="H3" s="54" t="n"/>
+      <c r="I3" s="54" t="n"/>
       <c r="J3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="53" t="n"/>
+      <c r="A4" s="54" t="n"/>
       <c r="B4" s="4" t="n"/>
-      <c r="C4" s="53" t="n"/>
-      <c r="D4" s="53" t="n"/>
-      <c r="E4" s="53" t="n"/>
-      <c r="F4" s="53" t="n"/>
-      <c r="G4" s="53" t="n"/>
-      <c r="H4" s="53" t="n"/>
-      <c r="I4" s="53" t="n"/>
+      <c r="C4" s="54" t="n"/>
+      <c r="D4" s="54" t="n"/>
+      <c r="E4" s="54" t="n"/>
+      <c r="F4" s="54" t="n"/>
+      <c r="G4" s="54" t="n"/>
+      <c r="H4" s="54" t="n"/>
+      <c r="I4" s="54" t="n"/>
       <c r="J4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="53" t="n"/>
+      <c r="A5" s="54" t="n"/>
       <c r="B5" s="4" t="n"/>
-      <c r="C5" s="53" t="n"/>
-      <c r="D5" s="53" t="n"/>
-      <c r="E5" s="53" t="n"/>
-      <c r="F5" s="53" t="n"/>
-      <c r="G5" s="53" t="n"/>
-      <c r="H5" s="53" t="n"/>
-      <c r="I5" s="53" t="n"/>
+      <c r="C5" s="54" t="n"/>
+      <c r="D5" s="54" t="n"/>
+      <c r="E5" s="54" t="n"/>
+      <c r="F5" s="54" t="n"/>
+      <c r="G5" s="54" t="n"/>
+      <c r="H5" s="54" t="n"/>
+      <c r="I5" s="54" t="n"/>
       <c r="J5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="53" t="n"/>
+      <c r="A6" s="54" t="n"/>
       <c r="B6" s="4" t="n"/>
-      <c r="C6" s="53" t="n"/>
-      <c r="D6" s="53" t="n"/>
-      <c r="E6" s="53" t="n"/>
-      <c r="F6" s="53" t="n"/>
-      <c r="G6" s="53" t="n"/>
-      <c r="H6" s="53" t="n"/>
-      <c r="I6" s="53" t="n"/>
+      <c r="C6" s="54" t="n"/>
+      <c r="D6" s="54" t="n"/>
+      <c r="E6" s="54" t="n"/>
+      <c r="F6" s="54" t="n"/>
+      <c r="G6" s="54" t="n"/>
+      <c r="H6" s="54" t="n"/>
+      <c r="I6" s="54" t="n"/>
       <c r="J6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="53" t="n"/>
+      <c r="A7" s="54" t="n"/>
       <c r="B7" s="4" t="n"/>
-      <c r="C7" s="53" t="n"/>
-      <c r="D7" s="53" t="n"/>
-      <c r="E7" s="53" t="n"/>
-      <c r="F7" s="53" t="n"/>
-      <c r="G7" s="53" t="n"/>
-      <c r="H7" s="53" t="n"/>
-      <c r="I7" s="53" t="n"/>
+      <c r="C7" s="54" t="n"/>
+      <c r="D7" s="54" t="n"/>
+      <c r="E7" s="54" t="n"/>
+      <c r="F7" s="54" t="n"/>
+      <c r="G7" s="54" t="n"/>
+      <c r="H7" s="54" t="n"/>
+      <c r="I7" s="54" t="n"/>
       <c r="J7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="53" t="n"/>
+      <c r="A8" s="54" t="n"/>
       <c r="B8" s="4" t="n"/>
-      <c r="C8" s="53" t="n"/>
-      <c r="D8" s="53" t="n"/>
-      <c r="E8" s="53" t="n"/>
-      <c r="F8" s="53" t="n"/>
-      <c r="G8" s="53" t="n"/>
-      <c r="H8" s="53" t="n"/>
-      <c r="I8" s="53" t="n"/>
+      <c r="C8" s="54" t="n"/>
+      <c r="D8" s="54" t="n"/>
+      <c r="E8" s="54" t="n"/>
+      <c r="F8" s="54" t="n"/>
+      <c r="G8" s="54" t="n"/>
+      <c r="H8" s="54" t="n"/>
+      <c r="I8" s="54" t="n"/>
       <c r="J8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="53" t="n"/>
+      <c r="A9" s="54" t="n"/>
       <c r="B9" s="4" t="n"/>
-      <c r="C9" s="53" t="n"/>
-      <c r="D9" s="53" t="n"/>
-      <c r="E9" s="53" t="n"/>
-      <c r="F9" s="53" t="n"/>
-      <c r="G9" s="53" t="n"/>
-      <c r="H9" s="53" t="n"/>
-      <c r="I9" s="53" t="n"/>
+      <c r="C9" s="54" t="n"/>
+      <c r="D9" s="54" t="n"/>
+      <c r="E9" s="54" t="n"/>
+      <c r="F9" s="54" t="n"/>
+      <c r="G9" s="54" t="n"/>
+      <c r="H9" s="54" t="n"/>
+      <c r="I9" s="54" t="n"/>
       <c r="J9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="53" t="n"/>
+      <c r="A10" s="54" t="n"/>
       <c r="B10" s="4" t="n"/>
-      <c r="C10" s="53" t="n"/>
-      <c r="D10" s="53" t="n"/>
-      <c r="E10" s="53" t="n"/>
-      <c r="F10" s="53" t="n"/>
-      <c r="G10" s="53" t="n"/>
-      <c r="H10" s="53" t="n"/>
-      <c r="I10" s="53" t="n"/>
+      <c r="C10" s="54" t="n"/>
+      <c r="D10" s="54" t="n"/>
+      <c r="E10" s="54" t="n"/>
+      <c r="F10" s="54" t="n"/>
+      <c r="G10" s="54" t="n"/>
+      <c r="H10" s="54" t="n"/>
+      <c r="I10" s="54" t="n"/>
       <c r="J10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="53" t="n"/>
+      <c r="A11" s="54" t="n"/>
       <c r="B11" s="4" t="n"/>
-      <c r="C11" s="53" t="n"/>
-      <c r="D11" s="53" t="n"/>
-      <c r="E11" s="53" t="n"/>
-      <c r="F11" s="53" t="n"/>
-      <c r="G11" s="53" t="n"/>
-      <c r="H11" s="53" t="n"/>
-      <c r="I11" s="53" t="n"/>
+      <c r="C11" s="54" t="n"/>
+      <c r="D11" s="54" t="n"/>
+      <c r="E11" s="54" t="n"/>
+      <c r="F11" s="54" t="n"/>
+      <c r="G11" s="54" t="n"/>
+      <c r="H11" s="54" t="n"/>
+      <c r="I11" s="54" t="n"/>
       <c r="J11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="53" t="n"/>
+      <c r="A12" s="54" t="n"/>
       <c r="B12" s="4" t="n"/>
-      <c r="C12" s="53" t="n"/>
-      <c r="D12" s="53" t="n"/>
-      <c r="E12" s="53" t="n"/>
-      <c r="F12" s="53" t="n"/>
-      <c r="G12" s="53" t="n"/>
-      <c r="H12" s="53" t="n"/>
-      <c r="I12" s="53" t="n"/>
+      <c r="C12" s="54" t="n"/>
+      <c r="D12" s="54" t="n"/>
+      <c r="E12" s="54" t="n"/>
+      <c r="F12" s="54" t="n"/>
+      <c r="G12" s="54" t="n"/>
+      <c r="H12" s="54" t="n"/>
+      <c r="I12" s="54" t="n"/>
       <c r="J12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="53" t="n"/>
+      <c r="A13" s="54" t="n"/>
       <c r="B13" s="4" t="n"/>
-      <c r="C13" s="53" t="n"/>
-      <c r="D13" s="53" t="n"/>
-      <c r="E13" s="53" t="n"/>
-      <c r="F13" s="53" t="n"/>
-      <c r="G13" s="53" t="n"/>
-      <c r="H13" s="53" t="n"/>
-      <c r="I13" s="53" t="n"/>
+      <c r="C13" s="54" t="n"/>
+      <c r="D13" s="54" t="n"/>
+      <c r="E13" s="54" t="n"/>
+      <c r="F13" s="54" t="n"/>
+      <c r="G13" s="54" t="n"/>
+      <c r="H13" s="54" t="n"/>
+      <c r="I13" s="54" t="n"/>
       <c r="J13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="53" t="n"/>
+      <c r="A14" s="54" t="n"/>
       <c r="B14" s="4" t="n"/>
-      <c r="C14" s="53" t="n"/>
-      <c r="D14" s="53" t="n"/>
-      <c r="E14" s="53" t="n"/>
-      <c r="F14" s="53" t="n"/>
-      <c r="G14" s="53" t="n"/>
-      <c r="H14" s="53" t="n"/>
-      <c r="I14" s="53" t="n"/>
+      <c r="C14" s="54" t="n"/>
+      <c r="D14" s="54" t="n"/>
+      <c r="E14" s="54" t="n"/>
+      <c r="F14" s="54" t="n"/>
+      <c r="G14" s="54" t="n"/>
+      <c r="H14" s="54" t="n"/>
+      <c r="I14" s="54" t="n"/>
       <c r="J14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="53" t="n"/>
+      <c r="A15" s="54" t="n"/>
       <c r="B15" s="4" t="n"/>
-      <c r="C15" s="53" t="n"/>
-      <c r="D15" s="53" t="n"/>
-      <c r="E15" s="53" t="n"/>
-      <c r="F15" s="53" t="n"/>
-      <c r="G15" s="53" t="n"/>
-      <c r="H15" s="53" t="n"/>
-      <c r="I15" s="53" t="n"/>
+      <c r="C15" s="54" t="n"/>
+      <c r="D15" s="54" t="n"/>
+      <c r="E15" s="54" t="n"/>
+      <c r="F15" s="54" t="n"/>
+      <c r="G15" s="54" t="n"/>
+      <c r="H15" s="54" t="n"/>
+      <c r="I15" s="54" t="n"/>
       <c r="J15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="53" t="n"/>
+      <c r="A16" s="54" t="n"/>
       <c r="B16" s="4" t="n"/>
-      <c r="C16" s="53" t="n"/>
-      <c r="D16" s="53" t="n"/>
-      <c r="E16" s="53" t="n"/>
-      <c r="F16" s="53" t="n"/>
-      <c r="G16" s="53" t="n"/>
-      <c r="H16" s="53" t="n"/>
-      <c r="I16" s="53" t="n"/>
+      <c r="C16" s="54" t="n"/>
+      <c r="D16" s="54" t="n"/>
+      <c r="E16" s="54" t="n"/>
+      <c r="F16" s="54" t="n"/>
+      <c r="G16" s="54" t="n"/>
+      <c r="H16" s="54" t="n"/>
+      <c r="I16" s="54" t="n"/>
       <c r="J16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="53" t="n"/>
+      <c r="A17" s="54" t="n"/>
       <c r="B17" s="4" t="n"/>
-      <c r="C17" s="53" t="n"/>
-      <c r="D17" s="53" t="n"/>
-      <c r="E17" s="53" t="n"/>
-      <c r="F17" s="53" t="n"/>
-      <c r="G17" s="53" t="n"/>
-      <c r="H17" s="53" t="n"/>
-      <c r="I17" s="53" t="n"/>
+      <c r="C17" s="54" t="n"/>
+      <c r="D17" s="54" t="n"/>
+      <c r="E17" s="54" t="n"/>
+      <c r="F17" s="54" t="n"/>
+      <c r="G17" s="54" t="n"/>
+      <c r="H17" s="54" t="n"/>
+      <c r="I17" s="54" t="n"/>
       <c r="J17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="53" t="n"/>
+      <c r="A18" s="54" t="n"/>
       <c r="B18" s="4" t="n"/>
-      <c r="C18" s="53" t="n"/>
-      <c r="D18" s="53" t="n"/>
-      <c r="E18" s="53" t="n"/>
-      <c r="F18" s="53" t="n"/>
-      <c r="G18" s="53" t="n"/>
-      <c r="H18" s="53" t="n"/>
-      <c r="I18" s="53" t="n"/>
+      <c r="C18" s="54" t="n"/>
+      <c r="D18" s="54" t="n"/>
+      <c r="E18" s="54" t="n"/>
+      <c r="F18" s="54" t="n"/>
+      <c r="G18" s="54" t="n"/>
+      <c r="H18" s="54" t="n"/>
+      <c r="I18" s="54" t="n"/>
       <c r="J18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="53" t="n"/>
+      <c r="A19" s="54" t="n"/>
       <c r="B19" s="4" t="n"/>
-      <c r="C19" s="53" t="n"/>
-      <c r="D19" s="53" t="n"/>
-      <c r="E19" s="53" t="n"/>
-      <c r="F19" s="53" t="n"/>
-      <c r="G19" s="53" t="n"/>
-      <c r="H19" s="53" t="n"/>
-      <c r="I19" s="53" t="n"/>
+      <c r="C19" s="54" t="n"/>
+      <c r="D19" s="54" t="n"/>
+      <c r="E19" s="54" t="n"/>
+      <c r="F19" s="54" t="n"/>
+      <c r="G19" s="54" t="n"/>
+      <c r="H19" s="54" t="n"/>
+      <c r="I19" s="54" t="n"/>
       <c r="J19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="53" t="n"/>
+      <c r="A20" s="54" t="n"/>
       <c r="B20" s="4" t="n"/>
-      <c r="C20" s="53" t="n"/>
-      <c r="D20" s="53" t="n"/>
-      <c r="E20" s="53" t="n"/>
-      <c r="F20" s="53" t="n"/>
-      <c r="G20" s="53" t="n"/>
-      <c r="H20" s="53" t="n"/>
-      <c r="I20" s="53" t="n"/>
+      <c r="C20" s="54" t="n"/>
+      <c r="D20" s="54" t="n"/>
+      <c r="E20" s="54" t="n"/>
+      <c r="F20" s="54" t="n"/>
+      <c r="G20" s="54" t="n"/>
+      <c r="H20" s="54" t="n"/>
+      <c r="I20" s="54" t="n"/>
       <c r="J20" s="2" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="53" t="n"/>
+      <c r="A21" s="54" t="n"/>
       <c r="B21" s="4" t="n"/>
-      <c r="C21" s="53" t="n"/>
-      <c r="D21" s="53" t="n"/>
-      <c r="E21" s="53" t="n"/>
-      <c r="F21" s="53" t="n"/>
-      <c r="G21" s="53" t="n"/>
-      <c r="H21" s="53" t="n"/>
-      <c r="I21" s="53" t="n"/>
+      <c r="C21" s="54" t="n"/>
+      <c r="D21" s="54" t="n"/>
+      <c r="E21" s="54" t="n"/>
+      <c r="F21" s="54" t="n"/>
+      <c r="G21" s="54" t="n"/>
+      <c r="H21" s="54" t="n"/>
+      <c r="I21" s="54" t="n"/>
       <c r="J21" s="2" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="53" t="n"/>
+      <c r="A22" s="54" t="n"/>
       <c r="B22" s="4" t="n"/>
-      <c r="C22" s="53" t="n"/>
-      <c r="D22" s="53" t="n"/>
-      <c r="E22" s="53" t="n"/>
-      <c r="F22" s="53" t="n"/>
-      <c r="G22" s="53" t="n"/>
-      <c r="H22" s="53" t="n"/>
-      <c r="I22" s="53" t="n"/>
+      <c r="C22" s="54" t="n"/>
+      <c r="D22" s="54" t="n"/>
+      <c r="E22" s="54" t="n"/>
+      <c r="F22" s="54" t="n"/>
+      <c r="G22" s="54" t="n"/>
+      <c r="H22" s="54" t="n"/>
+      <c r="I22" s="54" t="n"/>
       <c r="J22" s="2" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="53" t="n"/>
+      <c r="A23" s="54" t="n"/>
       <c r="B23" s="4" t="n"/>
-      <c r="C23" s="53" t="n"/>
-      <c r="D23" s="53" t="n"/>
-      <c r="E23" s="53" t="n"/>
-      <c r="F23" s="53" t="n"/>
-      <c r="G23" s="53" t="n"/>
-      <c r="H23" s="53" t="n"/>
-      <c r="I23" s="53" t="n"/>
+      <c r="C23" s="54" t="n"/>
+      <c r="D23" s="54" t="n"/>
+      <c r="E23" s="54" t="n"/>
+      <c r="F23" s="54" t="n"/>
+      <c r="G23" s="54" t="n"/>
+      <c r="H23" s="54" t="n"/>
+      <c r="I23" s="54" t="n"/>
       <c r="J23" s="2" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="53" t="n"/>
+      <c r="A24" s="54" t="n"/>
       <c r="B24" s="4" t="n"/>
-      <c r="C24" s="53" t="n"/>
-      <c r="D24" s="53" t="n"/>
-      <c r="E24" s="53" t="n"/>
-      <c r="F24" s="53" t="n"/>
-      <c r="G24" s="53" t="n"/>
-      <c r="H24" s="53" t="n"/>
-      <c r="I24" s="53" t="n"/>
+      <c r="C24" s="54" t="n"/>
+      <c r="D24" s="54" t="n"/>
+      <c r="E24" s="54" t="n"/>
+      <c r="F24" s="54" t="n"/>
+      <c r="G24" s="54" t="n"/>
+      <c r="H24" s="54" t="n"/>
+      <c r="I24" s="54" t="n"/>
       <c r="J24" s="2" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="53" t="n"/>
+      <c r="A25" s="54" t="n"/>
       <c r="B25" s="4" t="n"/>
-      <c r="C25" s="53" t="n"/>
-      <c r="D25" s="53" t="n"/>
-      <c r="E25" s="53" t="n"/>
-      <c r="F25" s="53" t="n"/>
-      <c r="G25" s="53" t="n"/>
-      <c r="H25" s="53" t="n"/>
-      <c r="I25" s="53" t="n"/>
+      <c r="C25" s="54" t="n"/>
+      <c r="D25" s="54" t="n"/>
+      <c r="E25" s="54" t="n"/>
+      <c r="F25" s="54" t="n"/>
+      <c r="G25" s="54" t="n"/>
+      <c r="H25" s="54" t="n"/>
+      <c r="I25" s="54" t="n"/>
       <c r="J25" s="2" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="53" t="n"/>
+      <c r="A26" s="54" t="n"/>
       <c r="B26" s="4" t="n"/>
-      <c r="C26" s="53" t="n"/>
-      <c r="D26" s="53" t="n"/>
-      <c r="E26" s="53" t="n"/>
-      <c r="F26" s="53" t="n"/>
-      <c r="G26" s="53" t="n"/>
-      <c r="H26" s="53" t="n"/>
-      <c r="I26" s="53" t="n"/>
+      <c r="C26" s="54" t="n"/>
+      <c r="D26" s="54" t="n"/>
+      <c r="E26" s="54" t="n"/>
+      <c r="F26" s="54" t="n"/>
+      <c r="G26" s="54" t="n"/>
+      <c r="H26" s="54" t="n"/>
+      <c r="I26" s="54" t="n"/>
       <c r="J26" s="2" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="53" t="n"/>
+      <c r="A27" s="54" t="n"/>
       <c r="B27" s="4" t="n"/>
-      <c r="C27" s="53" t="n"/>
-      <c r="D27" s="53" t="n"/>
-      <c r="E27" s="53" t="n"/>
-      <c r="F27" s="53" t="n"/>
-      <c r="G27" s="53" t="n"/>
-      <c r="H27" s="53" t="n"/>
-      <c r="I27" s="53" t="n"/>
+      <c r="C27" s="54" t="n"/>
+      <c r="D27" s="54" t="n"/>
+      <c r="E27" s="54" t="n"/>
+      <c r="F27" s="54" t="n"/>
+      <c r="G27" s="54" t="n"/>
+      <c r="H27" s="54" t="n"/>
+      <c r="I27" s="54" t="n"/>
       <c r="J27" s="2" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="53" t="n"/>
+      <c r="A28" s="54" t="n"/>
       <c r="B28" s="4" t="n"/>
-      <c r="C28" s="53" t="n"/>
-      <c r="D28" s="53" t="n"/>
-      <c r="E28" s="53" t="n"/>
-      <c r="F28" s="53" t="n"/>
-      <c r="G28" s="53" t="n"/>
-      <c r="H28" s="53" t="n"/>
-      <c r="I28" s="53" t="n"/>
+      <c r="C28" s="54" t="n"/>
+      <c r="D28" s="54" t="n"/>
+      <c r="E28" s="54" t="n"/>
+      <c r="F28" s="54" t="n"/>
+      <c r="G28" s="54" t="n"/>
+      <c r="H28" s="54" t="n"/>
+      <c r="I28" s="54" t="n"/>
       <c r="J28" s="2" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="53" t="n"/>
+      <c r="A29" s="54" t="n"/>
       <c r="B29" s="4" t="n"/>
-      <c r="C29" s="53" t="n"/>
-      <c r="D29" s="53" t="n"/>
-      <c r="E29" s="53" t="n"/>
-      <c r="F29" s="53" t="n"/>
-      <c r="G29" s="53" t="n"/>
-      <c r="H29" s="53" t="n"/>
-      <c r="I29" s="53" t="n"/>
+      <c r="C29" s="54" t="n"/>
+      <c r="D29" s="54" t="n"/>
+      <c r="E29" s="54" t="n"/>
+      <c r="F29" s="54" t="n"/>
+      <c r="G29" s="54" t="n"/>
+      <c r="H29" s="54" t="n"/>
+      <c r="I29" s="54" t="n"/>
       <c r="J29" s="2" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="53" t="n"/>
+      <c r="A30" s="54" t="n"/>
       <c r="B30" s="4" t="n"/>
-      <c r="C30" s="53" t="n"/>
-      <c r="D30" s="53" t="n"/>
-      <c r="E30" s="53" t="n"/>
-      <c r="F30" s="53" t="n"/>
-      <c r="G30" s="53" t="n"/>
-      <c r="H30" s="53" t="n"/>
-      <c r="I30" s="53" t="n"/>
+      <c r="C30" s="54" t="n"/>
+      <c r="D30" s="54" t="n"/>
+      <c r="E30" s="54" t="n"/>
+      <c r="F30" s="54" t="n"/>
+      <c r="G30" s="54" t="n"/>
+      <c r="H30" s="54" t="n"/>
+      <c r="I30" s="54" t="n"/>
       <c r="J30" s="2" t="n"/>
     </row>
   </sheetData>
@@ -13407,7 +14516,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00ED7D31"/>
@@ -13494,15 +14603,15 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B3" s="53" t="n"/>
+      <c r="B3" s="54" t="n"/>
       <c r="C3" s="3" t="n"/>
-      <c r="D3" s="53" t="n"/>
-      <c r="E3" s="53" t="n"/>
-      <c r="F3" s="53" t="n"/>
-      <c r="G3" s="53" t="n"/>
-      <c r="H3" s="53" t="n"/>
-      <c r="I3" s="53" t="n"/>
-      <c r="J3" s="53" t="n"/>
+      <c r="D3" s="54" t="n"/>
+      <c r="E3" s="54" t="n"/>
+      <c r="F3" s="54" t="n"/>
+      <c r="G3" s="54" t="n"/>
+      <c r="H3" s="54" t="n"/>
+      <c r="I3" s="54" t="n"/>
+      <c r="J3" s="54" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Fixed Request Use = No; no exact/flexible requests supplied for this 28HC test.</t>
@@ -13511,63 +14620,63 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
-      <c r="B4" s="54" t="n"/>
+      <c r="B4" s="55" t="n"/>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="54" t="n"/>
-      <c r="E4" s="54" t="n"/>
-      <c r="F4" s="54" t="n"/>
-      <c r="G4" s="54" t="n"/>
-      <c r="H4" s="54" t="n"/>
-      <c r="I4" s="54" t="n"/>
-      <c r="J4" s="54" t="n"/>
+      <c r="D4" s="55" t="n"/>
+      <c r="E4" s="55" t="n"/>
+      <c r="F4" s="55" t="n"/>
+      <c r="G4" s="55" t="n"/>
+      <c r="H4" s="55" t="n"/>
+      <c r="I4" s="55" t="n"/>
+      <c r="J4" s="55" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="54" t="n"/>
+      <c r="B5" s="55" t="n"/>
       <c r="C5" s="3" t="n"/>
-      <c r="D5" s="54" t="n"/>
-      <c r="E5" s="54" t="n"/>
-      <c r="F5" s="54" t="n"/>
-      <c r="G5" s="54" t="n"/>
-      <c r="H5" s="54" t="n"/>
-      <c r="I5" s="54" t="n"/>
-      <c r="J5" s="54" t="n"/>
+      <c r="D5" s="55" t="n"/>
+      <c r="E5" s="55" t="n"/>
+      <c r="F5" s="55" t="n"/>
+      <c r="G5" s="55" t="n"/>
+      <c r="H5" s="55" t="n"/>
+      <c r="I5" s="55" t="n"/>
+      <c r="J5" s="55" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
-      <c r="B6" s="54" t="n"/>
+      <c r="B6" s="55" t="n"/>
       <c r="C6" s="3" t="n"/>
-      <c r="D6" s="54" t="n"/>
-      <c r="E6" s="54" t="n"/>
-      <c r="F6" s="54" t="n"/>
-      <c r="G6" s="54" t="n"/>
-      <c r="H6" s="54" t="n"/>
-      <c r="I6" s="54" t="n"/>
-      <c r="J6" s="54" t="n"/>
+      <c r="D6" s="55" t="n"/>
+      <c r="E6" s="55" t="n"/>
+      <c r="F6" s="55" t="n"/>
+      <c r="G6" s="55" t="n"/>
+      <c r="H6" s="55" t="n"/>
+      <c r="I6" s="55" t="n"/>
+      <c r="J6" s="55" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
-      <c r="B7" s="54" t="n"/>
+      <c r="B7" s="55" t="n"/>
       <c r="C7" s="3" t="n"/>
-      <c r="D7" s="54" t="n"/>
-      <c r="E7" s="54" t="n"/>
-      <c r="F7" s="54" t="n"/>
-      <c r="G7" s="54" t="n"/>
-      <c r="H7" s="54" t="n"/>
-      <c r="I7" s="54" t="n"/>
-      <c r="J7" s="54" t="n"/>
+      <c r="D7" s="55" t="n"/>
+      <c r="E7" s="55" t="n"/>
+      <c r="F7" s="55" t="n"/>
+      <c r="G7" s="55" t="n"/>
+      <c r="H7" s="55" t="n"/>
+      <c r="I7" s="55" t="n"/>
+      <c r="J7" s="55" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
-      <c r="B8" s="54" t="n"/>
+      <c r="B8" s="55" t="n"/>
       <c r="C8" s="3" t="n"/>
-      <c r="D8" s="54" t="n"/>
-      <c r="E8" s="54" t="n"/>
-      <c r="F8" s="54" t="n"/>
-      <c r="G8" s="54" t="n"/>
-      <c r="H8" s="54" t="n"/>
-      <c r="I8" s="54" t="n"/>
-      <c r="J8" s="54" t="n"/>
+      <c r="D8" s="55" t="n"/>
+      <c r="E8" s="55" t="n"/>
+      <c r="F8" s="55" t="n"/>
+      <c r="G8" s="55" t="n"/>
+      <c r="H8" s="55" t="n"/>
+      <c r="I8" s="55" t="n"/>
+      <c r="J8" s="55" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -13598,1113 +14707,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00ED7D31"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" style="19" min="1" max="1"/>
-    <col width="28" customWidth="1" style="19" min="2" max="2"/>
-    <col width="15" customWidth="1" style="19" min="3" max="3"/>
-    <col width="24" customWidth="1" style="19" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1" s="19">
-      <c r="A1" s="50" t="inlineStr">
-        <is>
-          <t>Previous Saturday Schedule — Cyclic Carry-in</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="49" t="inlineStr">
-        <is>
-          <t>Slot</t>
-        </is>
-      </c>
-      <c r="B2" s="49" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C2" s="49" t="inlineStr">
-        <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="D2" s="49" t="inlineStr">
-        <is>
-          <t>Previous Saturday Shift</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="53" t="inlineStr">
-        <is>
-          <t>Esraa Abdelhadi</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="D3" s="53" t="inlineStr">
-        <is>
-          <t>10:00 - 19:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="53" t="inlineStr">
-        <is>
-          <t>Seif Eleman</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Bilingual</t>
-        </is>
-      </c>
-      <c r="D4" s="53" t="inlineStr">
-        <is>
-          <t>16:00 - 01:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="53" t="inlineStr">
-        <is>
-          <t>Mohamed Elsayed</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="D5" s="53" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="53" t="inlineStr">
-        <is>
-          <t>Mennatullah Abdelhamid</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="D6" s="53" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="53" t="inlineStr">
-        <is>
-          <t>Awni Ali</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>French</t>
-        </is>
-      </c>
-      <c r="D7" s="53" t="inlineStr">
-        <is>
-          <t>19:00 - 04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="53" t="inlineStr">
-        <is>
-          <t>Jana Rabeey</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Bilingual</t>
-        </is>
-      </c>
-      <c r="D8" s="53" t="inlineStr">
-        <is>
-          <t>16:00 - 01:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="53" t="inlineStr">
-        <is>
-          <t>Wagih Ibrahim</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="D9" s="53" t="inlineStr">
-        <is>
-          <t>19:00 - 04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="53" t="inlineStr">
-        <is>
-          <t>Youssef Eltembari</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="D10" s="53" t="inlineStr">
-        <is>
-          <t>14:00 - 23:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="53" t="inlineStr">
-        <is>
-          <t>Adam Ahmed</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="D11" s="53" t="inlineStr">
-        <is>
-          <t>19:00 - 04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="53" t="inlineStr">
-        <is>
-          <t>Juliana Amgad</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>French</t>
-        </is>
-      </c>
-      <c r="D12" s="53" t="inlineStr">
-        <is>
-          <t>16:00 - 01:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="53" t="inlineStr">
-        <is>
-          <t>Mazen Moustafa</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="D13" s="53" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="53" t="inlineStr">
-        <is>
-          <t>Mohamed Habib</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="D14" s="53" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" s="53" t="inlineStr">
-        <is>
-          <t>Ahmed Ebied</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="D15" s="53" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="53" t="inlineStr">
-        <is>
-          <t>Abdelrahman Mahmoud</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="D16" s="53" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="53" t="inlineStr">
-        <is>
-          <t>Nourhan Abdelsalam</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="D17" s="53" t="inlineStr">
-        <is>
-          <t>19:00 - 04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="53" t="inlineStr">
-        <is>
-          <t>Lujaine Mohamed</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Bilingual</t>
-        </is>
-      </c>
-      <c r="D18" s="53" t="inlineStr">
-        <is>
-          <t>19:00 - 04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" s="53" t="inlineStr">
-        <is>
-          <t>Aseya Hamdy</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Bilingual</t>
-        </is>
-      </c>
-      <c r="D19" s="53" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" s="53" t="inlineStr">
-        <is>
-          <t>Mennatullah Abdo</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="D20" s="53" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" s="53" t="inlineStr">
-        <is>
-          <t>Mohamed Kamal</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Bilingual</t>
-        </is>
-      </c>
-      <c r="D21" s="53" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="53" t="inlineStr">
-        <is>
-          <t>Youssef Ali</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="D22" s="53" t="inlineStr">
-        <is>
-          <t>19:00 - 04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="53" t="inlineStr">
-        <is>
-          <t>Farida Ahmed</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Bilingual</t>
-        </is>
-      </c>
-      <c r="D23" s="53" t="inlineStr">
-        <is>
-          <t>19:00 - 04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" s="53" t="inlineStr">
-        <is>
-          <t>Lojaine Khaled</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="D24" s="53" t="inlineStr">
-        <is>
-          <t>16:00 - 01:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="53" t="inlineStr">
-        <is>
-          <t>Shahd Hesham</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="D25" s="53" t="inlineStr">
-        <is>
-          <t>16:00 - 01:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" s="53" t="inlineStr">
-        <is>
-          <t>Sara Elshannat</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="D26" s="53" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="53" t="inlineStr">
-        <is>
-          <t>Kenzie Farid</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="D27" s="53" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="53" t="inlineStr">
-        <is>
-          <t>Hazem Yasser</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="D28" s="53" t="inlineStr">
-        <is>
-          <t>18:00 - 03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="53" t="inlineStr">
-        <is>
-          <t>Habiba Mahmoud</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Bilingual</t>
-        </is>
-      </c>
-      <c r="D29" s="53" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" s="53" t="inlineStr">
-        <is>
-          <t>Rana Mohamed</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Bilingual</t>
-        </is>
-      </c>
-      <c r="D30" s="53" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="54" t="inlineStr">
-        <is>
-          <t>Salma Ahmed</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="D31" s="54" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="D3:D302">
-    <cfRule type="expression" priority="1" dxfId="5">
-      <formula>UPPER(TRIM(D3))="OFF"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="6">
-      <formula>UPPER(TRIM(D3))="LEAVE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation sqref="B3:B302" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Please check this value" error="This name is not on this week's roster. If the person has left, also list them in Instructions &gt; Known Departed Associates." prompt="Pick a name from this week's roster." type="list" errorStyle="warning">
-      <formula1>'Schedule'!$D$3:$D$302</formula1>
-    </dataValidation>
-    <dataValidation sqref="C3:C302" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Please check this value" error="This language is not on the Language Setup tab. Keep it only if that is intended." type="list" errorStyle="warning">
-      <formula1>'Language Setup'!$A$3:$A$42</formula1>
-    </dataValidation>
-    <dataValidation sqref="D3:D302" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Please check this value" error="Not in this week's Shift Library. Keep it only if it really was last Saturday's shift (HH:MM - HH:MM)." prompt="OFF, Leave or a shift from the Shift Library." type="list" errorStyle="warning">
-      <formula1>'Validation Lists'!$C$3:$C$69</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="007F7F7F"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" style="19" min="1" max="1"/>
-    <col width="14" customWidth="1" style="19" min="2" max="3"/>
-    <col width="28" customWidth="1" style="19" min="4" max="4"/>
-    <col width="12" customWidth="1" style="19" min="5" max="5"/>
-    <col width="22" customWidth="1" style="19" min="6" max="6"/>
-    <col width="20" customWidth="1" style="19" min="7" max="7"/>
-    <col width="56" customWidth="1" style="19" min="8" max="8"/>
-    <col width="16" customWidth="1" style="19" min="9" max="9"/>
-    <col width="20" customWidth="1" style="19" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1" s="19">
-      <c r="A1" s="50" t="inlineStr">
-        <is>
-          <t>Language / Skill Setup — Directional Coverage</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" s="19">
-      <c r="A2" s="49" t="inlineStr">
-        <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="B2" s="49" t="inlineStr">
-        <is>
-          <t>Coverage Start</t>
-        </is>
-      </c>
-      <c r="C2" s="49" t="inlineStr">
-        <is>
-          <t>Coverage End</t>
-        </is>
-      </c>
-      <c r="D2" s="49" t="inlineStr">
-        <is>
-          <t>Can Cover Languages</t>
-        </is>
-      </c>
-      <c r="E2" s="49" t="inlineStr">
-        <is>
-          <t>Active?</t>
-        </is>
-      </c>
-      <c r="F2" s="49" t="inlineStr">
-        <is>
-          <t>Coverage Group</t>
-        </is>
-      </c>
-      <c r="G2" s="49" t="inlineStr">
-        <is>
-          <t>Minimum Per Interval</t>
-        </is>
-      </c>
-      <c r="H2" s="49" t="inlineStr">
-        <is>
-          <t>Priority / Notes</t>
-        </is>
-      </c>
-      <c r="I2" s="49" t="inlineStr">
-        <is>
-          <t>Cross-skilled?</t>
-        </is>
-      </c>
-      <c r="J2" s="49" t="inlineStr">
-        <is>
-          <t>Coverage Days</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="B3" s="55" t="n">
-        <v>0.2916666666666667</v>
-      </c>
-      <c r="C3" s="55" t="inlineStr">
-        <is>
-          <t>02:00</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>UK, English</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Source language covers itself and English.</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Bilingual</t>
-        </is>
-      </c>
-      <c r="B4" s="55" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C4" s="55" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Bilingual, French, English</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Bilingual/French</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Source language covers itself plus French and English.</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>French</t>
-        </is>
-      </c>
-      <c r="B5" s="55" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C5" s="55" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>French</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Bilingual/French</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>French only.</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="B6" s="55" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C6" s="55" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>No minimum-per-interval language requirement.</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="56" t="n"/>
-      <c r="C7" s="56" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="56" t="n"/>
-      <c r="C8" s="56" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="56" t="n"/>
-      <c r="C9" s="56" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="56" t="n"/>
-      <c r="C10" s="56" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="56" t="n"/>
-      <c r="C11" s="56" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="56" t="n"/>
-      <c r="C12" s="56" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="56" t="n"/>
-      <c r="C13" s="56" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="56" t="n"/>
-      <c r="C14" s="56" t="n"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="56" t="n"/>
-      <c r="C15" s="56" t="n"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="56" t="n"/>
-      <c r="C16" s="56" t="n"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="56" t="n"/>
-      <c r="C17" s="56" t="n"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="56" t="n"/>
-      <c r="C18" s="56" t="n"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="56" t="n"/>
-      <c r="C19" s="56" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="56" t="n"/>
-      <c r="C20" s="56" t="n"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="56" t="n"/>
-      <c r="C21" s="56" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="56" t="n"/>
-      <c r="C22" s="56" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="56" t="n"/>
-      <c r="C23" s="56" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="56" t="n"/>
-      <c r="C24" s="56" t="n"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="56" t="n"/>
-      <c r="C25" s="56" t="n"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="56" t="n"/>
-      <c r="C26" s="56" t="n"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="56" t="n"/>
-      <c r="C27" s="56" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="56" t="n"/>
-      <c r="C28" s="56" t="n"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="56" t="n"/>
-      <c r="C29" s="56" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="56" t="n"/>
-      <c r="C30" s="56" t="n"/>
-    </row>
-    <row r="31">
-      <c r="B31" s="56" t="n"/>
-      <c r="C31" s="56" t="n"/>
-    </row>
-    <row r="32">
-      <c r="B32" s="56" t="n"/>
-      <c r="C32" s="56" t="n"/>
-    </row>
-    <row r="33">
-      <c r="B33" s="56" t="n"/>
-      <c r="C33" s="56" t="n"/>
-    </row>
-    <row r="34">
-      <c r="B34" s="56" t="n"/>
-      <c r="C34" s="56" t="n"/>
-    </row>
-    <row r="35">
-      <c r="B35" s="56" t="n"/>
-      <c r="C35" s="56" t="n"/>
-    </row>
-    <row r="36">
-      <c r="B36" s="56" t="n"/>
-      <c r="C36" s="56" t="n"/>
-    </row>
-    <row r="37">
-      <c r="B37" s="56" t="n"/>
-      <c r="C37" s="56" t="n"/>
-    </row>
-    <row r="38">
-      <c r="B38" s="56" t="n"/>
-      <c r="C38" s="56" t="n"/>
-    </row>
-    <row r="39">
-      <c r="B39" s="56" t="n"/>
-      <c r="C39" s="56" t="n"/>
-    </row>
-    <row r="40">
-      <c r="B40" s="56" t="n"/>
-      <c r="C40" s="56" t="n"/>
-    </row>
-    <row r="41">
-      <c r="B41" s="56" t="n"/>
-      <c r="C41" s="56" t="n"/>
-    </row>
-    <row r="42">
-      <c r="B42" s="56" t="n"/>
-      <c r="C42" s="56" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I6"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
-  <dataValidations count="6">
-    <dataValidation sqref="J3 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid coverage days" error="Choose a listed day or range, or type a supported value such as Sun-Thu." type="list" errorStyle="stop">
-      <formula1>"All,Weekdays,Weekends,Sun-Thu,Mon-Fri,Sun,Mon,Tue,Wed,Thu,Fri,Sat"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B3:B42" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. A time such as 08:00. The window may cross midnight." prompt="A time such as 08:00. The window may cross midnight." type="time" errorStyle="stop" operator="between">
-      <formula1>0</formula1>
-      <formula2>0.999988426</formula2>
-    </dataValidation>
-    <dataValidation sqref="C3:C42" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. A time such as 08:00. The window may cross midnight." prompt="A time such as 08:00. The window may cross midnight." type="time" errorStyle="stop" operator="between">
-      <formula1>0</formula1>
-      <formula2>0.999988426</formula2>
-    </dataValidation>
-    <dataValidation sqref="E3:E42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." type="list" errorStyle="stop">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G3:G42" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. People of this language needed at all times in the window (whole number)." prompt="People of this language needed at all times in the window (whole number)." type="whole" errorStyle="stop" operator="between">
-      <formula1>0</formula1>
-      <formula2>500</formula2>
-    </dataValidation>
-    <dataValidation sqref="I3:I42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." type="list" errorStyle="stop">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
 </file>
--- a/packages/rc9_2_2_production/inputs/ready_to_edit/GDI_28HC_24_7_WEEKLY_INPUT.xlsx
+++ b/packages/rc9_2_2_production/inputs/ready_to_edit/GDI_28HC_24_7_WEEKLY_INPUT.xlsx
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="E10" s="24">
-        <f>IF(Instructions!C35&lt;&gt;"Yes","Not used (Fixed Request Use = No)",IF(SUMPRODUCT(('Fixed Request'!$B$3:$B$302&lt;&gt;"")*(COUNTIF('Schedule'!$D$3:$D$302,'Fixed Request'!$B$3:$B$302)=0))=0,"OK  every name is on the roster","! "&amp;SUMPRODUCT(('Fixed Request'!$B$3:$B$302&lt;&gt;"")*(COUNTIF('Schedule'!$D$3:$D$302,'Fixed Request'!$B$3:$B$302)=0))&amp;" name(s) not on the roster"))</f>
+        <f>IF(Instructions!C37&lt;&gt;"Yes","Not used (Fixed Request Use = No)",IF(SUMPRODUCT(('Fixed Request'!$B$3:$B$302&lt;&gt;"")*(COUNTIF('Schedule'!$D$3:$D$302,'Fixed Request'!$B$3:$B$302)=0))=0,"OK  every name is on the roster","! "&amp;SUMPRODUCT(('Fixed Request'!$B$3:$B$302&lt;&gt;"")*(COUNTIF('Schedule'!$D$3:$D$302,'Fixed Request'!$B$3:$B$302)=0))&amp;" name(s) not on the roster"))</f>
         <v/>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="E11" s="24">
-        <f>IF(SUMPRODUCT(('Previous week scheduled'!$B$3:$B$302&lt;&gt;"")*(COUNTIF('Schedule'!$D$3:$D$302,'Previous week scheduled'!$B$3:$B$302)=0)*ISERROR(SEARCH('Previous week scheduled'!$B$3:$B$302,"|"&amp;Instructions!C39&amp;"|")))=0,"OK  every name is on the roster or listed as departed","! "&amp;SUMPRODUCT(('Previous week scheduled'!$B$3:$B$302&lt;&gt;"")*(COUNTIF('Schedule'!$D$3:$D$302,'Previous week scheduled'!$B$3:$B$302)=0)*ISERROR(SEARCH('Previous week scheduled'!$B$3:$B$302,"|"&amp;Instructions!C39&amp;"|")))&amp;" name(s) not on the roster: list them in Known Departed Associates if they left")</f>
+        <f>IF(SUMPRODUCT(('Previous week scheduled'!$B$3:$B$302&lt;&gt;"")*(COUNTIF('Schedule'!$D$3:$D$302,'Previous week scheduled'!$B$3:$B$302)=0)*ISERROR(SEARCH('Previous week scheduled'!$B$3:$B$302,"|"&amp;Instructions!C41&amp;"|")))=0,"OK  every name is on the roster or listed as departed","! "&amp;SUMPRODUCT(('Previous week scheduled'!$B$3:$B$302&lt;&gt;"")*(COUNTIF('Schedule'!$D$3:$D$302,'Previous week scheduled'!$B$3:$B$302)=0)*ISERROR(SEARCH('Previous week scheduled'!$B$3:$B$302,"|"&amp;Instructions!C41&amp;"|")))&amp;" name(s) not on the roster: list them in Known Departed Associates if they left")</f>
         <v/>
       </c>
     </row>
@@ -1810,8 +1810,23 @@
     <cfRule type="expression" priority="2" dxfId="6">
       <formula>UPPER(TRIM(D3))="LEAVE"</formula>
     </cfRule>
+    <cfRule type="expression" priority="3" dxfId="5">
+      <formula>UPPER(TRIM(D3))="OFF"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="6">
+      <formula>UPPER(TRIM(D3))="LEAVE"</formula>
+    </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
+  <dataValidations count="6">
+    <dataValidation sqref="B3:B302" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Please check this value" error="This name is not on this week's roster. If the person has left, also list them in Instructions &gt; Known Departed Associates." prompt="Pick a name from this week's roster." type="list" errorStyle="warning">
+      <formula1>'Schedule'!$D$3:$D$302</formula1>
+    </dataValidation>
+    <dataValidation sqref="C3:C302" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Please check this value" error="This language is not on the Language Setup tab. Keep it only if that is intended." type="list" errorStyle="warning">
+      <formula1>'Language Setup'!$A$3:$A$42</formula1>
+    </dataValidation>
+    <dataValidation sqref="D3:D302" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Please check this value" error="Not in this week's Shift Library. Keep it only if it really was last Saturday's shift (HH:MM - HH:MM)." prompt="OFF, Leave or a shift from the Shift Library." type="list" errorStyle="warning">
+      <formula1>'Validation Lists'!$C$3:$C$69</formula1>
+    </dataValidation>
     <dataValidation sqref="B3:B302" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Please check this value" error="This name is not on this week's roster. If the person has left, also list them in Instructions &gt; Known Departed Associates." prompt="Pick a name from this week's roster." type="list" errorStyle="warning">
       <formula1>'Schedule'!$D$3:$D$302</formula1>
     </dataValidation>
@@ -2254,8 +2269,29 @@
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <dataValidations count="6">
+  <dataValidations count="12">
     <dataValidation sqref="J3 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid coverage days" error="Choose a listed day or range, or type a supported value such as Sun-Thu." type="list" errorStyle="stop">
+      <formula1>"All,Weekdays,Weekends,Sun-Thu,Mon-Fri,Sun,Mon,Tue,Wed,Thu,Fri,Sat"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B3:B42" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. A time such as 08:00. The window may cross midnight." prompt="A time such as 08:00. The window may cross midnight." type="time" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>0.999988426</formula2>
+    </dataValidation>
+    <dataValidation sqref="C3:C42" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. A time such as 08:00. The window may cross midnight." prompt="A time such as 08:00. The window may cross midnight." type="time" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>0.999988426</formula2>
+    </dataValidation>
+    <dataValidation sqref="E3:E42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." type="list" errorStyle="stop">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G3:G42" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. People of this language needed at all times in the window (whole number)." prompt="People of this language needed at all times in the window (whole number)." type="whole" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>500</formula2>
+    </dataValidation>
+    <dataValidation sqref="I3:I42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." type="list" errorStyle="stop">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J3 J4 J5 J6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid coverage days" error="Choose a listed day or range, or type a supported value such as Sun-Thu." type="list" errorStyle="stop">
       <formula1>"All,Weekdays,Weekends,Sun-Thu,Mon-Fri,Sun,Mon,Tue,Wed,Thu,Fri,Sat"</formula1>
     </dataValidation>
     <dataValidation sqref="B3:B42" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. A time such as 08:00. The window may cross midnight." prompt="A time such as 08:00. The window may cross midnight." type="time" errorStyle="stop" operator="between">
@@ -5513,7 +5549,11 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation sqref="B3:H98" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Required FTE for this interval. 0 or more; blank = no demand." prompt="Required FTE for this interval. 0 or more; blank = no demand." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>100000</formula2>
+    </dataValidation>
     <dataValidation sqref="B3:H98" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Required FTE for this interval. 0 or more; blank = no demand." prompt="Required FTE for this interval. 0 or more; blank = no demand." type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>100000</formula2>
@@ -6936,7 +6976,11 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation sqref="B3:H98" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Shrinkage as a ratio (0.08) or percent (8%). Below 100%." prompt="Shrinkage as a ratio (0.08) or percent (8%). Below 100%." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>0.9999</formula2>
+    </dataValidation>
     <dataValidation sqref="B3:H98" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Shrinkage as a ratio (0.08) or percent (8%). Below 100%." prompt="Shrinkage as a ratio (0.08) or percent (8%). Below 100%." type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>0.9999</formula2>
@@ -7968,7 +8012,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" style="19" min="1" max="1"/>
@@ -8329,132 +8373,124 @@
     <row r="29" ht="20" customHeight="1" s="19">
       <c r="B29" s="42" t="inlineStr">
         <is>
-          <t>Strict OFF Count</t>
-        </is>
-      </c>
-      <c r="C29" s="43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Max 11H/3OFF Associates</t>
+        </is>
+      </c>
+      <c r="C29" s="45" t="inlineStr"/>
       <c r="D29" s="44" t="inlineStr">
         <is>
-          <t>Yes = exactly two OFF days (three with 11H/3OFF) per person.</t>
+          <t>Blank = engine default. Used only when Use 11H/3OFF is Yes: the most associates who may work the 11-hour, three-OFF-day pattern this week (e.g. 2). Blank = no limit.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" s="19">
       <c r="B30" s="42" t="inlineStr">
         <is>
-          <t>Separate OFF Days</t>
+          <t>Strict OFF Count</t>
         </is>
       </c>
       <c r="C30" s="43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D30" s="44" t="inlineStr">
         <is>
-          <t>Yes = a person's OFF days may be apart. No = they must be together.</t>
+          <t>Yes = exactly two OFF days (three with 11H/3OFF) per person.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1" s="19">
       <c r="B31" s="42" t="inlineStr">
         <is>
-          <t>Rest Gap Hours</t>
-        </is>
-      </c>
-      <c r="C31" s="47" t="n">
-        <v>12</v>
+          <t>Separate OFF Days</t>
+        </is>
+      </c>
+      <c r="C31" s="43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="D31" s="44" t="inlineStr">
         <is>
-          <t>Minimum hours between the end of one shift and the start of the next.</t>
+          <t>Yes = a person's OFF days may be apart. No = they must be together.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1" s="19">
       <c r="B32" s="42" t="inlineStr">
         <is>
+          <t>Rest Gap Hours</t>
+        </is>
+      </c>
+      <c r="C32" s="47" t="n">
+        <v>12</v>
+      </c>
+      <c r="D32" s="44" t="inlineStr">
+        <is>
+          <t>Minimum hours between the end of one shift and the start of the next.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1" s="19">
+      <c r="B33" s="42" t="inlineStr">
+        <is>
           <t>Count of Different Shifts Per week</t>
         </is>
       </c>
-      <c r="C32" s="45" t="n">
+      <c r="C33" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="44" t="inlineStr">
+      <c r="D33" s="44" t="inlineStr">
         <is>
           <t>Most different shifts one person may get in a week (1 to 7).</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="40" t="inlineStr">
+    <row r="34" ht="20" customHeight="1" s="19">
+      <c r="B34" s="42" t="inlineStr">
+        <is>
+          <t>Allow Half-Hour Starts</t>
+        </is>
+      </c>
+      <c r="C34" s="43" t="inlineStr"/>
+      <c r="D34" s="44" t="inlineStr">
+        <is>
+          <t>Blank = engine default. Yes = each shift may also start 30 minutes later, used only where full-hour starts cannot cover demand; marked in the output. Blank or No = full-hour starts only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="40" t="inlineStr">
         <is>
           <t>Requests</t>
         </is>
       </c>
-      <c r="B34" s="41" t="n"/>
-      <c r="C34" s="41" t="n"/>
-      <c r="D34" s="41" t="n"/>
-    </row>
-    <row r="35" ht="20" customHeight="1" s="19">
-      <c r="B35" s="42" t="inlineStr">
-        <is>
-          <t>Fixed Request Use</t>
-        </is>
-      </c>
-      <c r="C35" s="43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D35" s="44" t="inlineStr">
-        <is>
-          <t>Yes = apply the Fixed Request tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1" s="19">
-      <c r="B36" s="42" t="inlineStr">
-        <is>
-          <t>Hard OFF Preferences</t>
-        </is>
-      </c>
-      <c r="C36" s="43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D36" s="44" t="inlineStr">
-        <is>
-          <t>Yes = OFF requests on the Preference tab are always granted.</t>
-        </is>
-      </c>
+      <c r="B36" s="41" t="n"/>
+      <c r="C36" s="41" t="n"/>
+      <c r="D36" s="41" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1" s="19">
       <c r="B37" s="42" t="inlineStr">
         <is>
-          <t>Leave Enabled</t>
+          <t>Fixed Request Use</t>
         </is>
       </c>
       <c r="C37" s="43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D37" s="44" t="inlineStr">
         <is>
-          <t>Yes = Leave on the Preference tab is honoured.</t>
+          <t>Yes = apply the Fixed Request tab.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1" s="19">
       <c r="B38" s="42" t="inlineStr">
         <is>
-          <t>Use Preferences</t>
+          <t>Hard OFF Preferences</t>
         </is>
       </c>
       <c r="C38" s="43" t="inlineStr">
@@ -8464,338 +8500,372 @@
       </c>
       <c r="D38" s="44" t="inlineStr">
         <is>
-          <t>Yes = try to give people their preferred shifts.</t>
+          <t>Yes = OFF requests on the Preference tab are always granted.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1" s="19">
       <c r="B39" s="42" t="inlineStr">
         <is>
+          <t>Leave Enabled</t>
+        </is>
+      </c>
+      <c r="C39" s="43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D39" s="44" t="inlineStr">
+        <is>
+          <t>Yes = Leave on the Preference tab is honoured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1" s="19">
+      <c r="B40" s="42" t="inlineStr">
+        <is>
+          <t>Use Preferences</t>
+        </is>
+      </c>
+      <c r="C40" s="43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D40" s="44" t="inlineStr">
+        <is>
+          <t>Yes = try to give people their preferred shifts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1" s="19">
+      <c r="B41" s="42" t="inlineStr">
+        <is>
           <t>Known Departed Associates</t>
         </is>
       </c>
-      <c r="C39" s="43" t="inlineStr"/>
-      <c r="D39" s="44" t="inlineStr">
+      <c r="C41" s="43" t="inlineStr"/>
+      <c r="D41" s="44" t="inlineStr">
         <is>
           <t>Blank = engine default. Names on last week's tab who have left, separated by ; (Start Here lists any missing).</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="40" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="40" t="inlineStr">
         <is>
           <t>Opening Guard   (click + on the left to open)</t>
         </is>
       </c>
-      <c r="B41" s="41" t="n"/>
-      <c r="C41" s="41" t="n"/>
-      <c r="D41" s="41" t="n"/>
-    </row>
-    <row r="42" hidden="1" outlineLevel="1" ht="20" customHeight="1" s="19">
-      <c r="B42" s="42" t="inlineStr">
-        <is>
-          <t>Opening Guard Enabled</t>
-        </is>
-      </c>
-      <c r="C42" s="43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D42" s="44" t="inlineStr">
-        <is>
-          <t>Yes = keep enough people on at the start of each day.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" hidden="1" outlineLevel="1" ht="20" customHeight="1" s="19">
-      <c r="B43" s="42" t="inlineStr">
-        <is>
-          <t>Opening Minimum FTE</t>
-        </is>
-      </c>
-      <c r="C43" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="44" t="inlineStr">
-        <is>
-          <t>People needed at opening (whole number).</t>
-        </is>
-      </c>
+      <c r="B43" s="41" t="n"/>
+      <c r="C43" s="41" t="n"/>
+      <c r="D43" s="41" t="n"/>
     </row>
     <row r="44" hidden="1" outlineLevel="1" ht="20" customHeight="1" s="19">
       <c r="B44" s="42" t="inlineStr">
         <is>
+          <t>Opening Guard Enabled</t>
+        </is>
+      </c>
+      <c r="C44" s="43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D44" s="44" t="inlineStr">
+        <is>
+          <t>Yes = keep enough people on at the start of each day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" hidden="1" outlineLevel="1" ht="20" customHeight="1" s="19">
+      <c r="B45" s="42" t="inlineStr">
+        <is>
+          <t>Opening Minimum FTE</t>
+        </is>
+      </c>
+      <c r="C45" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="44" t="inlineStr">
+        <is>
+          <t>People needed at opening (whole number).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" hidden="1" outlineLevel="1" ht="20" customHeight="1" s="19">
+      <c r="B46" s="42" t="inlineStr">
+        <is>
           <t>Opening Guard Intervals</t>
         </is>
       </c>
-      <c r="C44" s="45" t="n">
+      <c r="C46" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="44" t="inlineStr">
+      <c r="D46" s="44" t="inlineStr">
         <is>
           <t>How many opening intervals the guard covers.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="40" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="40" t="inlineStr">
         <is>
           <t>Breaks</t>
         </is>
       </c>
-      <c r="B46" s="41" t="n"/>
-      <c r="C46" s="41" t="n"/>
-      <c r="D46" s="41" t="n"/>
-    </row>
-    <row r="47" ht="20" customHeight="1" s="19">
-      <c r="B47" s="42" t="inlineStr">
-        <is>
-          <t>Short Break Count</t>
-        </is>
-      </c>
-      <c r="C47" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="D47" s="44" t="inlineStr">
-        <is>
-          <t>Short breaks per shift.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1" s="19">
-      <c r="B48" s="42" t="inlineStr">
-        <is>
-          <t>Short Break Duration Minutes</t>
-        </is>
-      </c>
-      <c r="C48" s="43" t="n">
-        <v>15</v>
-      </c>
-      <c r="D48" s="44" t="inlineStr">
-        <is>
-          <t>Length of each short break.</t>
-        </is>
-      </c>
+      <c r="B48" s="41" t="n"/>
+      <c r="C48" s="41" t="n"/>
+      <c r="D48" s="41" t="n"/>
     </row>
     <row r="49" ht="20" customHeight="1" s="19">
       <c r="B49" s="42" t="inlineStr">
         <is>
-          <t>Lunch Count</t>
+          <t>Short Break Count</t>
         </is>
       </c>
       <c r="C49" s="43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" s="44" t="inlineStr">
         <is>
-          <t>Lunches per shift.</t>
+          <t>Short breaks per shift.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1" s="19">
       <c r="B50" s="42" t="inlineStr">
         <is>
-          <t>Lunch Duration Minutes</t>
+          <t>Short Break Duration Minutes</t>
         </is>
       </c>
       <c r="C50" s="43" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D50" s="44" t="inlineStr">
         <is>
-          <t>Length of each lunch.</t>
+          <t>Length of each short break.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1" s="19">
       <c r="B51" s="42" t="inlineStr">
         <is>
-          <t>Break Preferred Gap Minutes</t>
-        </is>
-      </c>
-      <c r="C51" s="45" t="n">
-        <v>120</v>
+          <t>Lunch Count</t>
+        </is>
+      </c>
+      <c r="C51" s="43" t="n">
+        <v>1</v>
       </c>
       <c r="D51" s="44" t="inlineStr">
         <is>
-          <t>Ideal minutes between two breaks.</t>
+          <t>Lunches per shift.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1" s="19">
       <c r="B52" s="42" t="inlineStr">
         <is>
-          <t>Break Absolute Minimum Gap Minutes</t>
-        </is>
-      </c>
-      <c r="C52" s="45" t="n">
-        <v>60</v>
+          <t>Lunch Duration Minutes</t>
+        </is>
+      </c>
+      <c r="C52" s="43" t="n">
+        <v>30</v>
       </c>
       <c r="D52" s="44" t="inlineStr">
         <is>
-          <t>Two breaks are never closer than this.</t>
+          <t>Length of each lunch.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1" s="19">
       <c r="B53" s="42" t="inlineStr">
         <is>
-          <t>Break Normal Maximum Gap Minutes</t>
+          <t>Break Preferred Gap Minutes</t>
         </is>
       </c>
       <c r="C53" s="45" t="n">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="D53" s="44" t="inlineStr">
         <is>
-          <t>Two breaks are normally no further apart than this.</t>
+          <t>Ideal minutes between two breaks.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1" s="19">
       <c r="B54" s="42" t="inlineStr">
         <is>
+          <t>Break Absolute Minimum Gap Minutes</t>
+        </is>
+      </c>
+      <c r="C54" s="45" t="n">
+        <v>60</v>
+      </c>
+      <c r="D54" s="44" t="inlineStr">
+        <is>
+          <t>Two breaks are never closer than this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1" s="19">
+      <c r="B55" s="42" t="inlineStr">
+        <is>
+          <t>Break Normal Maximum Gap Minutes</t>
+        </is>
+      </c>
+      <c r="C55" s="45" t="n">
+        <v>210</v>
+      </c>
+      <c r="D55" s="44" t="inlineStr">
+        <is>
+          <t>Two breaks are normally no further apart than this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1" s="19">
+      <c r="B56" s="42" t="inlineStr">
+        <is>
           <t>Allow Back-to-Back Breaks</t>
         </is>
       </c>
-      <c r="C54" s="43" t="inlineStr">
+      <c r="C56" s="43" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D54" s="44" t="inlineStr">
+      <c r="D56" s="44" t="inlineStr">
         <is>
           <t>Yes = a break may directly follow another.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="40" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="40" t="inlineStr">
         <is>
           <t>Language / Skill</t>
         </is>
       </c>
-      <c r="B56" s="41" t="n"/>
-      <c r="C56" s="41" t="n"/>
-      <c r="D56" s="41" t="n"/>
-    </row>
-    <row r="57" ht="20" customHeight="1" s="19">
-      <c r="B57" s="42" t="inlineStr">
+      <c r="B58" s="41" t="n"/>
+      <c r="C58" s="41" t="n"/>
+      <c r="D58" s="41" t="n"/>
+    </row>
+    <row r="59" ht="20" customHeight="1" s="19">
+      <c r="B59" s="42" t="inlineStr">
         <is>
           <t>Language Working Window</t>
         </is>
       </c>
-      <c r="C57" s="43" t="inlineStr"/>
-      <c r="D57" s="44" t="inlineStr">
+      <c r="C59" s="43" t="inlineStr"/>
+      <c r="D59" s="44" t="inlineStr">
         <is>
           <t>Blank = engine default. OFF = language hours set minimums only. The other choices also limit when each language may work (guide 3.7).</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="40" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="40" t="inlineStr">
         <is>
           <t>Exception Policy</t>
         </is>
       </c>
-      <c r="B59" s="41" t="n"/>
-      <c r="C59" s="41" t="n"/>
-      <c r="D59" s="41" t="n"/>
-    </row>
-    <row r="60" ht="20" customHeight="1" s="19">
-      <c r="B60" s="42" t="inlineStr">
+      <c r="B61" s="41" t="n"/>
+      <c r="C61" s="41" t="n"/>
+      <c r="D61" s="41" t="n"/>
+    </row>
+    <row r="62" ht="20" customHeight="1" s="19">
+      <c r="B62" s="42" t="inlineStr">
         <is>
           <t>Critical Coverage No-Break Exception Enabled</t>
         </is>
       </c>
-      <c r="C60" s="43" t="inlineStr">
+      <c r="C62" s="43" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D60" s="44" t="inlineStr">
+      <c r="D62" s="44" t="inlineStr">
         <is>
           <t>Yes = a person may skip a break when coverage is critical (set a limit below).</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="20" customHeight="1" s="19">
-      <c r="B61" s="42" t="inlineStr">
+    <row r="63" ht="20" customHeight="1" s="19">
+      <c r="B63" s="42" t="inlineStr">
         <is>
           <t>Critical Coverage No-Break Max Associate-Days</t>
         </is>
       </c>
-      <c r="C61" s="45" t="n">
+      <c r="C63" s="45" t="n">
         <v>7</v>
       </c>
-      <c r="D61" s="44" t="inlineStr">
+      <c r="D63" s="44" t="inlineStr">
         <is>
           <t>Most person-days that may skip a break. Above 0 when enabled.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="40" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="40" t="inlineStr">
         <is>
           <t>Release Quality   (click + on the left to open)</t>
         </is>
       </c>
-      <c r="B63" s="41" t="n"/>
-      <c r="C63" s="41" t="n"/>
-      <c r="D63" s="41" t="n"/>
-    </row>
-    <row r="64" hidden="1" outlineLevel="1" ht="20" customHeight="1" s="19">
-      <c r="B64" s="42" t="inlineStr">
-        <is>
-          <t>Production Quality Gate Mode</t>
-        </is>
-      </c>
-      <c r="C64" s="43" t="inlineStr">
-        <is>
-          <t>Warn</t>
-        </is>
-      </c>
-      <c r="D64" s="44" t="inlineStr">
-        <is>
-          <t>Warn = report quality issues. Fail = block release. Off = ignore.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" hidden="1" outlineLevel="1" ht="20" customHeight="1" s="19">
-      <c r="B65" s="42" t="inlineStr">
-        <is>
-          <t>Minimum After Break Target Ratio</t>
-        </is>
-      </c>
-      <c r="C65" s="46" t="inlineStr"/>
-      <c r="D65" s="44" t="inlineStr">
-        <is>
-          <t>Blank = engine default. Optional. Lowest share of intervals at target after breaks.</t>
-        </is>
-      </c>
+      <c r="B65" s="41" t="n"/>
+      <c r="C65" s="41" t="n"/>
+      <c r="D65" s="41" t="n"/>
     </row>
     <row r="66" hidden="1" outlineLevel="1" ht="20" customHeight="1" s="19">
       <c r="B66" s="42" t="inlineStr">
         <is>
-          <t>Protected Before80 Minimum Intervals</t>
-        </is>
-      </c>
-      <c r="C66" s="45" t="inlineStr"/>
+          <t>Production Quality Gate Mode</t>
+        </is>
+      </c>
+      <c r="C66" s="43" t="inlineStr">
+        <is>
+          <t>Warn</t>
+        </is>
+      </c>
       <c r="D66" s="44" t="inlineStr">
         <is>
-          <t>Blank = engine default. Optional. Intervals that must reach 80% before breaks.</t>
+          <t>Warn = report quality issues. Fail = block release. Off = ignore.</t>
         </is>
       </c>
     </row>
     <row r="67" hidden="1" outlineLevel="1" ht="20" customHeight="1" s="19">
       <c r="B67" s="42" t="inlineStr">
         <is>
+          <t>Minimum After Break Target Ratio</t>
+        </is>
+      </c>
+      <c r="C67" s="46" t="inlineStr"/>
+      <c r="D67" s="44" t="inlineStr">
+        <is>
+          <t>Blank = engine default. Optional. Lowest share of intervals at target after breaks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" hidden="1" outlineLevel="1" ht="20" customHeight="1" s="19">
+      <c r="B68" s="42" t="inlineStr">
+        <is>
+          <t>Protected Before80 Minimum Intervals</t>
+        </is>
+      </c>
+      <c r="C68" s="45" t="inlineStr"/>
+      <c r="D68" s="44" t="inlineStr">
+        <is>
+          <t>Blank = engine default. Optional. Intervals that must reach 80% before breaks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" hidden="1" outlineLevel="1" ht="20" customHeight="1" s="19">
+      <c r="B69" s="42" t="inlineStr">
+        <is>
           <t>Protected After80 Minimum Intervals</t>
         </is>
       </c>
-      <c r="C67" s="45" t="inlineStr"/>
-      <c r="D67" s="44" t="inlineStr">
+      <c r="C69" s="45" t="inlineStr"/>
+      <c r="D69" s="44" t="inlineStr">
         <is>
           <t>Blank = engine default. Optional. Intervals that must reach 80% after breaks.</t>
         </is>
@@ -8806,7 +8876,7 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <dataValidations count="30">
+  <dataValidations count="31">
     <dataValidation sqref="C6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Up to 80 characters." prompt="Up to 80 characters." type="textLength" errorStyle="stop" operator="lessThanOrEqual">
       <formula1>80</formula1>
     </dataValidation>
@@ -8814,7 +8884,7 @@
       <formula1>1</formula1>
       <formula2>5000</formula2>
     </dataValidation>
-    <dataValidation sqref="C8 C16 C20 C22 C28 C29 C30 C35 C36 C37 C38 C42 C54 C60" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." type="list" errorStyle="stop">
+    <dataValidation sqref="C8 C16 C20 C22 C28 C30 C31 C34 C37 C38 C39 C40 C44 C56 C62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." type="list" errorStyle="stop">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation sqref="C9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." type="list" errorStyle="stop">
@@ -8849,65 +8919,69 @@
     <dataValidation sqref="C27" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." prompt="Shift lengths allowed. 10.5 h or more needs Use 11H/3OFF = Yes." type="list" errorStyle="stop">
       <formula1>'Validation Lists'!$A$3:$A$33</formula1>
     </dataValidation>
-    <dataValidation sqref="C31" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Enter a number from 0 to 24." prompt="Enter a number from 0 to 24." type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="C29" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Enter a whole number from 1 to 5000." prompt="Enter a whole number from 1 to 5000." type="whole" errorStyle="stop" operator="between">
+      <formula1>1</formula1>
+      <formula2>5000</formula2>
+    </dataValidation>
+    <dataValidation sqref="C32" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Enter a number from 0 to 24." prompt="Enter a number from 0 to 24." type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>24</formula2>
     </dataValidation>
-    <dataValidation sqref="C32" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Enter a whole number from 1 to 7." prompt="Enter a whole number from 1 to 7." type="whole" errorStyle="stop" operator="between">
+    <dataValidation sqref="C33" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Enter a whole number from 1 to 7." prompt="Enter a whole number from 1 to 7." type="whole" errorStyle="stop" operator="between">
       <formula1>1</formula1>
       <formula2>7</formula2>
     </dataValidation>
-    <dataValidation sqref="C39" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Up to 2000 characters." prompt="Up to 2000 characters." type="textLength" errorStyle="stop" operator="lessThanOrEqual">
+    <dataValidation sqref="C41" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Up to 2000 characters." prompt="Up to 2000 characters." type="textLength" errorStyle="stop" operator="lessThanOrEqual">
       <formula1>2000</formula1>
     </dataValidation>
-    <dataValidation sqref="C43" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Enter a whole number from 0 to 500." prompt="Enter a whole number from 0 to 500." type="whole" errorStyle="stop" operator="between">
+    <dataValidation sqref="C45" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Enter a whole number from 0 to 500." prompt="Enter a whole number from 0 to 500." type="whole" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>500</formula2>
     </dataValidation>
-    <dataValidation sqref="C44" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Enter a whole number from 0 to 96." prompt="Enter a whole number from 0 to 96." type="whole" errorStyle="stop" operator="between">
+    <dataValidation sqref="C46" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Enter a whole number from 0 to 96." prompt="Enter a whole number from 0 to 96." type="whole" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>96</formula2>
     </dataValidation>
-    <dataValidation sqref="C47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." type="list" errorStyle="stop">
+    <dataValidation sqref="C49" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." type="list" errorStyle="stop">
       <formula1>"0,1,2,3,4"</formula1>
     </dataValidation>
-    <dataValidation sqref="C48 C50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." type="list" errorStyle="stop">
+    <dataValidation sqref="C50 C52" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." type="list" errorStyle="stop">
       <formula1>"15,30,45,60"</formula1>
     </dataValidation>
-    <dataValidation sqref="C49" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." type="list" errorStyle="stop">
+    <dataValidation sqref="C51" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." type="list" errorStyle="stop">
       <formula1>"0,1,2"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C51" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Enter a whole number from 0 to 720." prompt="Enter a whole number from 0 to 720." type="whole" errorStyle="stop" operator="between">
-      <formula1>0</formula1>
-      <formula2>720</formula2>
-    </dataValidation>
-    <dataValidation sqref="C52" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Enter a whole number from 0 to 720." prompt="Enter a whole number from 0 to 720." type="whole" errorStyle="stop" operator="between">
-      <formula1>0</formula1>
-      <formula2>720</formula2>
     </dataValidation>
     <dataValidation sqref="C53" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Enter a whole number from 0 to 720." prompt="Enter a whole number from 0 to 720." type="whole" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>720</formula2>
     </dataValidation>
-    <dataValidation sqref="C57" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." type="list" errorStyle="stop">
+    <dataValidation sqref="C54" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Enter a whole number from 0 to 720." prompt="Enter a whole number from 0 to 720." type="whole" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>720</formula2>
+    </dataValidation>
+    <dataValidation sqref="C55" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Enter a whole number from 0 to 720." prompt="Enter a whole number from 0 to 720." type="whole" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>720</formula2>
+    </dataValidation>
+    <dataValidation sqref="C59" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." type="list" errorStyle="stop">
       <formula1>"OFF,MINIMUM_ROWS,ALL_ROWS,REQUIRED_LANGUAGE_ONLY"</formula1>
     </dataValidation>
-    <dataValidation sqref="C61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Enter a whole number from 0 to 5000." prompt="Enter a whole number from 0 to 5000." type="whole" errorStyle="stop" operator="between">
+    <dataValidation sqref="C63" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Enter a whole number from 0 to 5000." prompt="Enter a whole number from 0 to 5000." type="whole" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>5000</formula2>
     </dataValidation>
-    <dataValidation sqref="C64" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." type="list" errorStyle="stop">
+    <dataValidation sqref="C66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." type="list" errorStyle="stop">
       <formula1>"Warn,Fail,Off"</formula1>
     </dataValidation>
-    <dataValidation sqref="C65" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Enter a number from 0% to 100%." prompt="Enter a number from 0% to 100%." type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="C67" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Enter a number from 0% to 100%." prompt="Enter a number from 0% to 100%." type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation sqref="C66" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Enter a whole number from 0 to 672." prompt="Enter a whole number from 0 to 672." type="whole" errorStyle="stop" operator="between">
+    <dataValidation sqref="C68" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Enter a whole number from 0 to 672." prompt="Enter a whole number from 0 to 672." type="whole" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>672</formula2>
     </dataValidation>
-    <dataValidation sqref="C67" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Enter a whole number from 0 to 672." prompt="Enter a whole number from 0 to 672." type="whole" errorStyle="stop" operator="between">
+    <dataValidation sqref="C69" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Enter a whole number from 0 to 672." prompt="Enter a whole number from 0 to 672." type="whole" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>672</formula2>
     </dataValidation>
@@ -11215,7 +11289,19 @@
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="8">
+    <dataValidation sqref="D3:D302" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This name is already on the roster. One row per person." prompt="One row per person. Names must match the other tabs." type="custom" errorStyle="stop">
+      <formula1>COUNTIF($D$3:$D$302,D3)&lt;=1</formula1>
+    </dataValidation>
+    <dataValidation sqref="B3:B302" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This employee ID is already on the roster." prompt="Employee ID, once per person." type="custom" errorStyle="stop">
+      <formula1>COUNTIF($B$3:$B$302,B3)&lt;=1</formula1>
+    </dataValidation>
+    <dataValidation sqref="F3:F302" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Please check this value" error="This language is not on the Language Setup tab. Keep it only if that is intended." prompt="Pick the language from Language Setup." type="list" errorStyle="warning">
+      <formula1>'Language Setup'!$A$3:$A$42</formula1>
+    </dataValidation>
+    <dataValidation sqref="G3:G302 H3:H302 I3:I302 J3:J302 K3:K302 L3:L302 M3:M302" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." prompt="OFF, Leave or a shift from the Shift Library." type="list" errorStyle="stop">
+      <formula1>'Validation Lists'!$B$3:$B$68</formula1>
+    </dataValidation>
     <dataValidation sqref="D3:D302" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This name is already on the roster. One row per person." prompt="One row per person. Names must match the other tabs." type="custom" errorStyle="stop">
       <formula1>COUNTIF($D$3:$D$302,D3)&lt;=1</formula1>
     </dataValidation>
@@ -11950,7 +12036,11 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation sqref="B3:H26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Required FTE for this interval. 0 or more; blank = no demand." prompt="Required FTE for this interval. 0 or more; blank = no demand." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>100000</formula2>
+    </dataValidation>
     <dataValidation sqref="B3:H26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Required FTE for this interval. 0 or more; blank = no demand." prompt="Required FTE for this interval. 0 or more; blank = no demand." type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>100000</formula2>
@@ -12701,7 +12791,11 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation sqref="B3:H50" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Required FTE for this interval. 0 or more; blank = no demand." prompt="Required FTE for this interval. 0 or more; blank = no demand." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>100000</formula2>
+    </dataValidation>
     <dataValidation sqref="B3:H50" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Required FTE for this interval. 0 or more; blank = no demand." prompt="Required FTE for this interval. 0 or more; blank = no demand." type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>100000</formula2>
@@ -13314,7 +13408,11 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation sqref="B3:H26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Shrinkage as a ratio (0.08) or percent (8%). Below 100%." prompt="Shrinkage as a ratio (0.08) or percent (8%). Below 100%." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>0.9999</formula2>
+    </dataValidation>
     <dataValidation sqref="B3:H26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Shrinkage as a ratio (0.08) or percent (8%). Below 100%." prompt="Shrinkage as a ratio (0.08) or percent (8%). Below 100%." type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>0.9999</formula2>
@@ -14065,7 +14163,11 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation sqref="B3:H50" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Shrinkage as a ratio (0.08) or percent (8%). Below 100%." prompt="Shrinkage as a ratio (0.08) or percent (8%). Below 100%." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>0.9999</formula2>
+    </dataValidation>
     <dataValidation sqref="B3:H50" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Shrinkage as a ratio (0.08) or percent (8%). Below 100%." prompt="Shrinkage as a ratio (0.08) or percent (8%). Below 100%." type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>0.9999</formula2>
@@ -14499,8 +14601,23 @@
     <cfRule type="expression" priority="2" dxfId="6">
       <formula>UPPER(TRIM(C3))="LEAVE"</formula>
     </cfRule>
+    <cfRule type="expression" priority="3" dxfId="5">
+      <formula>UPPER(TRIM(C3))="OFF"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="6">
+      <formula>UPPER(TRIM(C3))="LEAVE"</formula>
+    </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
+  <dataValidations count="6">
+    <dataValidation sqref="A3:A302" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." prompt="Pick a name from this week's roster." type="list" errorStyle="stop">
+      <formula1>'Schedule'!$D$3:$D$302</formula1>
+    </dataValidation>
+    <dataValidation sqref="B3:B302" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Please check this value" error="This language is not on the Language Setup tab. Keep it only if that is intended." type="list" errorStyle="warning">
+      <formula1>'Language Setup'!$A$3:$A$42</formula1>
+    </dataValidation>
+    <dataValidation sqref="C3:C302 D3:D302 E3:E302 F3:F302 G3:G302 H3:H302 I3:I302" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." prompt="OFF, Leave or a shift from the Shift Library." type="list" errorStyle="stop">
+      <formula1>'Validation Lists'!$B$3:$B$68</formula1>
+    </dataValidation>
     <dataValidation sqref="A3:A302" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." prompt="Pick a name from this week's roster." type="list" errorStyle="stop">
       <formula1>'Schedule'!$D$3:$D$302</formula1>
     </dataValidation>
@@ -14689,8 +14806,26 @@
     <cfRule type="expression" priority="2" dxfId="6">
       <formula>UPPER(TRIM(D3))="LEAVE"</formula>
     </cfRule>
+    <cfRule type="expression" priority="3" dxfId="5">
+      <formula>UPPER(TRIM(D3))="OFF"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="6">
+      <formula>UPPER(TRIM(D3))="LEAVE"</formula>
+    </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations count="8">
+    <dataValidation sqref="B3:B302" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." prompt="Pick a name from this week's roster." type="list" errorStyle="stop">
+      <formula1>'Schedule'!$D$3:$D$302</formula1>
+    </dataValidation>
+    <dataValidation sqref="D3:D302 E3:E302 F3:F302 G3:G302 H3:H302 I3:I302 J3:J302" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." prompt="OFF, Leave or a shift from the Shift Library." type="list" errorStyle="stop">
+      <formula1>'Validation Lists'!$B$3:$B$68</formula1>
+    </dataValidation>
+    <dataValidation sqref="A3:A302" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." prompt="Yes = apply this row. No = ignore it." type="list" errorStyle="stop">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C3:C302" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="This value is outside what the scheduler accepts. Optional. People with the same group number work the same shifts." prompt="Optional. People with the same group number work the same shifts." type="textLength" errorStyle="stop" operator="lessThanOrEqual">
+      <formula1>50</formula1>
+    </dataValidation>
     <dataValidation sqref="B3:B302" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted." prompt="Pick a name from this week's roster." type="list" errorStyle="stop">
       <formula1>'Schedule'!$D$3:$D$302</formula1>
     </dataValidation>
